--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53226,6 +53226,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2299">
+      <c r="A2299" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2299" t="n">
+        <v>22455</v>
+      </c>
+      <c r="C2299" t="n">
+        <v>6.34000015258789</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53249,6 +53249,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2300">
+      <c r="A2300" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2300" t="n">
+        <v>16698</v>
+      </c>
+      <c r="C2300" t="n">
+        <v>6.34000015258789</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="G2300" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53272,6 +53272,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2301">
+      <c r="A2301" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2301" t="n">
+        <v>64113</v>
+      </c>
+      <c r="C2301" t="n">
+        <v>6.76000022888184</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G2301" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53280,7 +53280,7 @@
         <v>64113</v>
       </c>
       <c r="C2301" t="n">
-        <v>6.76000022888184</v>
+        <v>6.80000019073486</v>
       </c>
       <c r="D2301" t="n">
         <v>6.15999984741211</v>
@@ -53292,6 +53292,29 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2301" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2302" t="n">
+        <v>220138</v>
+      </c>
+      <c r="C2302" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>6.71999979019165</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="G2302" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53136,22 +53136,22 @@
     </row>
     <row r="2295">
       <c r="A2295" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2295" t="n">
-        <v>23965</v>
+        <v>31270</v>
       </c>
       <c r="C2295" t="n">
         <v>5.30000019073486</v>
       </c>
       <c r="D2295" t="n">
-        <v>5.21999979019165</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="E2295" t="n">
-        <v>5.21999979019165</v>
+        <v>5.30000019073486</v>
       </c>
       <c r="F2295" t="n">
-        <v>5.23999977111816</v>
+        <v>5.30000019073486</v>
       </c>
       <c r="G2295" t="s">
         <v>7</v>
@@ -53159,13 +53159,13 @@
     </row>
     <row r="2296">
       <c r="A2296" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2296" t="n">
-        <v>62018</v>
+        <v>23965</v>
       </c>
       <c r="C2296" t="n">
-        <v>5.69999980926514</v>
+        <v>5.30000019073486</v>
       </c>
       <c r="D2296" t="n">
         <v>5.21999979019165</v>
@@ -53174,7 +53174,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="F2296" t="n">
-        <v>5.69999980926514</v>
+        <v>5.23999977111816</v>
       </c>
       <c r="G2296" t="s">
         <v>7</v>
@@ -53182,22 +53182,22 @@
     </row>
     <row r="2297">
       <c r="A2297" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2297" t="n">
-        <v>3052327</v>
+        <v>62018</v>
       </c>
       <c r="C2297" t="n">
-        <v>6</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="D2297" t="n">
-        <v>5.57999992370605</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="E2297" t="n">
-        <v>5.82000017166138</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="F2297" t="n">
-        <v>5.94000005722046</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="G2297" t="s">
         <v>7</v>
@@ -53205,22 +53205,22 @@
     </row>
     <row r="2298">
       <c r="A2298" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2298" t="n">
-        <v>33812</v>
+        <v>3052327</v>
       </c>
       <c r="C2298" t="n">
-        <v>6.28000020980835</v>
+        <v>6</v>
       </c>
       <c r="D2298" t="n">
-        <v>5.96000003814697</v>
+        <v>5.57999992370605</v>
       </c>
       <c r="E2298" t="n">
-        <v>5.96000003814697</v>
+        <v>5.82000017166138</v>
       </c>
       <c r="F2298" t="n">
-        <v>6.05999994277954</v>
+        <v>5.94000005722046</v>
       </c>
       <c r="G2298" t="s">
         <v>7</v>
@@ -53228,22 +53228,22 @@
     </row>
     <row r="2299">
       <c r="A2299" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2299" t="n">
-        <v>22455</v>
+        <v>33812</v>
       </c>
       <c r="C2299" t="n">
-        <v>6.34000015258789</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="D2299" t="n">
-        <v>6.01999998092651</v>
+        <v>5.96000003814697</v>
       </c>
       <c r="E2299" t="n">
-        <v>6.1399998664856</v>
+        <v>5.96000003814697</v>
       </c>
       <c r="F2299" t="n">
-        <v>6.01999998092651</v>
+        <v>6.05999994277954</v>
       </c>
       <c r="G2299" t="s">
         <v>7</v>
@@ -53251,22 +53251,22 @@
     </row>
     <row r="2300">
       <c r="A2300" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2300" t="n">
-        <v>16698</v>
+        <v>22455</v>
       </c>
       <c r="C2300" t="n">
         <v>6.34000015258789</v>
       </c>
       <c r="D2300" t="n">
-        <v>5.98000001907349</v>
+        <v>6.01999998092651</v>
       </c>
       <c r="E2300" t="n">
-        <v>6.03999996185303</v>
+        <v>6.1399998664856</v>
       </c>
       <c r="F2300" t="n">
-        <v>6.26000022888184</v>
+        <v>6.01999998092651</v>
       </c>
       <c r="G2300" t="s">
         <v>7</v>
@@ -53274,22 +53274,22 @@
     </row>
     <row r="2301">
       <c r="A2301" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2301" t="n">
-        <v>64113</v>
+        <v>16698</v>
       </c>
       <c r="C2301" t="n">
-        <v>6.80000019073486</v>
+        <v>6.34000015258789</v>
       </c>
       <c r="D2301" t="n">
-        <v>6.15999984741211</v>
+        <v>5.98000001907349</v>
       </c>
       <c r="E2301" t="n">
-        <v>6.15999984741211</v>
+        <v>6.03999996185303</v>
       </c>
       <c r="F2301" t="n">
-        <v>6.80000019073486</v>
+        <v>6.26000022888184</v>
       </c>
       <c r="G2301" t="s">
         <v>7</v>
@@ -53297,24 +53297,47 @@
     </row>
     <row r="2302">
       <c r="A2302" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2302" t="n">
-        <v>220138</v>
+        <v>64113</v>
       </c>
       <c r="C2302" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G2302" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2303" t="n">
+        <v>31674</v>
+      </c>
+      <c r="C2303" t="n">
         <v>7.19999980926514</v>
       </c>
-      <c r="D2302" t="n">
-        <v>6.71999979019165</v>
-      </c>
-      <c r="E2302" t="n">
-        <v>6.80000019073486</v>
-      </c>
-      <c r="F2302" t="n">
-        <v>7.19999980926514</v>
-      </c>
-      <c r="G2302" t="s">
+      <c r="D2303" t="n">
+        <v>6.98000001907349</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="G2303" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G2" t="n">
-        <v>2.27459788322449</v>
+        <v>2.27459764480591</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28400421142578</v>
+        <v>2.28400492668152</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G6" t="n">
-        <v>2.27459788322449</v>
+        <v>2.27459764480591</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G7" t="n">
-        <v>2.27459788322449</v>
+        <v>2.27459764480591</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G14" t="n">
-        <v>2.33103942871094</v>
+        <v>2.33103919029236</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G19" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28400421142578</v>
+        <v>2.28400492668152</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G22" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G23" t="n">
-        <v>2.26519107818604</v>
+        <v>2.26519060134888</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>2.25578379631042</v>
+        <v>2.255784034729</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>2.30093741416931</v>
+        <v>2.30093717575073</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G28" t="n">
-        <v>2.25578379631042</v>
+        <v>2.255784034729</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G29" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>2.28400421142578</v>
+        <v>2.28400492668152</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3348023891449</v>
+        <v>2.33480215072632</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G36" t="n">
-        <v>2.30846261978149</v>
+        <v>2.30846309661865</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.31034398078918</v>
+        <v>2.31034445762634</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G39" t="n">
-        <v>2.31975126266479</v>
+        <v>2.31975102424622</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G42" t="n">
-        <v>2.29153037071228</v>
+        <v>2.2915301322937</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G43" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.5</v>
       </c>
       <c r="G45" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G47" t="n">
-        <v>2.35549736022949</v>
+        <v>2.35549759864807</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G50" t="n">
-        <v>2.39312505722046</v>
+        <v>2.39312481880188</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G51" t="n">
-        <v>2.38748121261597</v>
+        <v>2.38748097419739</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G52" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G53" t="n">
-        <v>2.39124345779419</v>
+        <v>2.39124369621277</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G54" t="n">
-        <v>2.39124345779419</v>
+        <v>2.39124369621277</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.5</v>
       </c>
       <c r="G56" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G57" t="n">
-        <v>2.34609055519104</v>
+        <v>2.34609007835388</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G58" t="n">
-        <v>2.34609055519104</v>
+        <v>2.34609007835388</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G59" t="n">
-        <v>2.34609055519104</v>
+        <v>2.34609007835388</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G65" t="n">
-        <v>2.24261426925659</v>
+        <v>2.24261403083801</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>2.2294442653656</v>
+        <v>2.22944450378418</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G67" t="n">
-        <v>2.27459788322449</v>
+        <v>2.27459764480591</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G70" t="n">
-        <v>2.30846261978149</v>
+        <v>2.30846309661865</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G72" t="n">
-        <v>2.31598806381226</v>
+        <v>2.31598782539368</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G73" t="n">
-        <v>2.30281829833984</v>
+        <v>2.302818775177</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G74" t="n">
-        <v>2.30093741416931</v>
+        <v>2.30093717575073</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G78" t="n">
-        <v>2.35737824440002</v>
+        <v>2.35737872123718</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34985303878784</v>
+        <v>2.34985327720642</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G84" t="n">
-        <v>2.3348023891449</v>
+        <v>2.33480215072632</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G85" t="n">
-        <v>2.34797167778015</v>
+        <v>2.34797191619873</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G86" t="n">
-        <v>2.34420895576477</v>
+        <v>2.34420919418335</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G88" t="n">
-        <v>2.31975126266479</v>
+        <v>2.31975102424622</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G89" t="n">
-        <v>2.31598806381226</v>
+        <v>2.31598782539368</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5</v>
       </c>
       <c r="G90" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G93" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.5</v>
       </c>
       <c r="G100" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G101" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G103" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.5</v>
       </c>
       <c r="G104" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G106" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.50224590301514</v>
+        <v>2.50224542617798</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>2.60572171211243</v>
+        <v>2.60572195053101</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60572171211243</v>
+        <v>2.60572195053101</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G117" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>2.54928016662598</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G119" t="n">
-        <v>2.55868721008301</v>
+        <v>2.55868744850159</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>2.51165270805359</v>
+        <v>2.51165294647217</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>2.54928016662598</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.54928016662598</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>2.62453579902649</v>
+        <v>2.62453556060791</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.53987336158752</v>
+        <v>2.5398736000061</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G132" t="n">
-        <v>2.51165270805359</v>
+        <v>2.51165294647217</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.41758322715759</v>
+        <v>2.41758298873901</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G140" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G141" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G142" t="n">
-        <v>2.51165270805359</v>
+        <v>2.51165294647217</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G152" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G162" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G169" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.5</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.5</v>
       </c>
       <c r="G177" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G179" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G182" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G187" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G188" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G189" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G196" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.5</v>
       </c>
       <c r="G207" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G209" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G219" t="n">
-        <v>2.48343181610107</v>
+        <v>2.4834315776825</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402477264404</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>2.19181680679321</v>
+        <v>2.19181656837463</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.21063041687012</v>
+        <v>2.21063017845154</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>2.19181680679321</v>
+        <v>2.19181656837463</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003722190857</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21063041687012</v>
+        <v>2.21063017845154</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.21063041687012</v>
+        <v>2.21063017845154</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003722190857</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>2.2294442653656</v>
+        <v>2.22944450378418</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G244" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.5</v>
       </c>
       <c r="G246" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.5</v>
       </c>
       <c r="G247" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G252" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.5</v>
       </c>
       <c r="G254" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.5</v>
       </c>
       <c r="G256" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.5</v>
       </c>
       <c r="G257" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.5</v>
       </c>
       <c r="G258" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G259" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G262" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.5</v>
       </c>
       <c r="G269" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G272" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G274" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G276" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G284" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G285" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G286" t="n">
-        <v>2.1824095249176</v>
+        <v>2.18241000175476</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>2.15418887138367</v>
+        <v>2.15418910980225</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G289" t="n">
-        <v>2.05071258544922</v>
+        <v>2.0507128238678</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>1.95664322376251</v>
+        <v>1.95664310455322</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G291" t="n">
-        <v>2.00367784500122</v>
+        <v>2.0036780834198</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="n">
-        <v>2.16359567642212</v>
+        <v>2.16359543800354</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>2.21063041687012</v>
+        <v>2.21063017845154</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.5</v>
       </c>
       <c r="G297" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G305" t="n">
-        <v>2.1824095249176</v>
+        <v>2.18241000175476</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>2.21063041687012</v>
+        <v>2.21063017845154</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G323" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G335" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G336" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G337" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G338" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G339" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G346" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G348" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G354" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G356" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G357" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G359" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G361" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G362" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G366" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>2.2294442653656</v>
+        <v>2.22944450378418</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G374" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G381" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003722190857</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003722190857</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G385" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G389" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G394" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G395" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G397" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G399" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>2.23885178565979</v>
+        <v>2.23885130882263</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G415" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25766539573669</v>
+        <v>2.25766515731812</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G417" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G418" t="n">
-        <v>2.28588604927063</v>
+        <v>2.28588628768921</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G421" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G430" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G431" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G432" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>2.27647876739502</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G443" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G444" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32351398468018</v>
+        <v>2.3235137462616</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.5</v>
       </c>
       <c r="G447" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.41758322715759</v>
+        <v>2.41758298873901</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G449" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G451" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.5</v>
       </c>
       <c r="G452" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.37054824829102</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G455" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.5</v>
       </c>
       <c r="G456" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G461" t="n">
-        <v>2.30470013618469</v>
+        <v>2.30469965934753</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G464" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G467" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G468" t="n">
-        <v>2.41758322715759</v>
+        <v>2.41758298873901</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G470" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G474" t="n">
-        <v>2.41758322715759</v>
+        <v>2.41758298873901</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G478" t="n">
-        <v>2.41758322715759</v>
+        <v>2.41758298873901</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>2.37995529174805</v>
+        <v>2.37995553016663</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.5</v>
       </c>
       <c r="G484" t="n">
-        <v>2.35173463821411</v>
+        <v>2.35173439979553</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.36114120483398</v>
+        <v>2.36114168167114</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.3893620967865</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G494" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G496" t="n">
-        <v>2.41758322715759</v>
+        <v>2.41758298873901</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G497" t="n">
-        <v>2.41758322715759</v>
+        <v>2.41758298873901</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.39876890182495</v>
+        <v>2.39876914024353</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53987336158752</v>
+        <v>2.5398736000061</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G502" t="n">
-        <v>2.53987336158752</v>
+        <v>2.5398736000061</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>2.56809425354004</v>
+        <v>2.56809401512146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G504" t="n">
-        <v>2.55868721008301</v>
+        <v>2.55868744850159</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G505" t="n">
-        <v>2.56809425354004</v>
+        <v>2.56809401512146</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G506" t="n">
-        <v>2.56809425354004</v>
+        <v>2.56809401512146</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G509" t="n">
-        <v>2.64334964752197</v>
+        <v>2.64334988594055</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.68097734451294</v>
+        <v>2.68097758293152</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.7656397819519</v>
+        <v>2.76564002037048</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G516" t="n">
-        <v>2.793860912323</v>
+        <v>2.79386067390442</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.793860912323</v>
+        <v>2.79386067390442</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.793860912323</v>
+        <v>2.79386067390442</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.793860912323</v>
+        <v>2.79386067390442</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>2.81267499923706</v>
+        <v>2.81267428398132</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>2.7656397819519</v>
+        <v>2.76564002037048</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.81267499923706</v>
+        <v>2.81267428398132</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3</v>
       </c>
       <c r="G527" t="n">
-        <v>2.82208180427551</v>
+        <v>2.82208156585693</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3</v>
       </c>
       <c r="G528" t="n">
-        <v>2.82208180427551</v>
+        <v>2.82208156585693</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3</v>
       </c>
       <c r="G529" t="n">
-        <v>2.82208180427551</v>
+        <v>2.82208156585693</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3</v>
       </c>
       <c r="G530" t="n">
-        <v>2.82208180427551</v>
+        <v>2.82208156585693</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3</v>
       </c>
       <c r="G531" t="n">
-        <v>2.82208180427551</v>
+        <v>2.82208156585693</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3</v>
       </c>
       <c r="G532" t="n">
-        <v>2.82208180427551</v>
+        <v>2.82208156585693</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G533" t="n">
-        <v>2.84089541435242</v>
+        <v>2.84089517593384</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G534" t="n">
-        <v>2.92555785179138</v>
+        <v>2.9255576133728</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G537" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>3.07606887817383</v>
+        <v>3.07606863975525</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>3.01962733268738</v>
+        <v>3.0196270942688</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>3.01962733268738</v>
+        <v>3.0196270942688</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>3.03844118118286</v>
+        <v>3.03844094276428</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97259259223938</v>
+        <v>2.9725923538208</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G550" t="n">
-        <v>2.95377898216248</v>
+        <v>2.9537787437439</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.97259259223938</v>
+        <v>2.9725923538208</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>3.01962733268738</v>
+        <v>3.0196270942688</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>3.07606887817383</v>
+        <v>3.07606863975525</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G561" t="n">
-        <v>2.95377898216248</v>
+        <v>2.9537787437439</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89733672142029</v>
+        <v>2.89733695983887</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>2.85030198097229</v>
+        <v>2.85030245780945</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.82208180427551</v>
+        <v>2.82208156585693</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>2.85030198097229</v>
+        <v>2.85030245780945</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>2.85030198097229</v>
+        <v>2.85030245780945</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G571" t="n">
-        <v>2.91615056991577</v>
+        <v>2.91615080833435</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.88792967796326</v>
+        <v>2.88792991638184</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G573" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G574" t="n">
-        <v>3.13251066207886</v>
+        <v>3.13251042366028</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G576" t="n">
-        <v>3.34887003898621</v>
+        <v>3.34886980056763</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>3.42412567138672</v>
+        <v>3.42412543296814</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="n">
-        <v>3.42412567138672</v>
+        <v>3.42412543296814</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G580" t="n">
-        <v>3.42412567138672</v>
+        <v>3.42412543296814</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>3.42412567138672</v>
+        <v>3.42412543296814</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G582" t="n">
-        <v>3.43353295326233</v>
+        <v>3.43353247642517</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>3.47115993499756</v>
+        <v>3.4711606502533</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G588" t="n">
-        <v>3.47115993499756</v>
+        <v>3.4711606502533</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>3.43353295326233</v>
+        <v>3.43353247642517</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>3.6969268321991</v>
+        <v>3.69692707061768</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G598" t="n">
-        <v>3.57463622093201</v>
+        <v>3.57463669776917</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G599" t="n">
-        <v>3.59345030784607</v>
+        <v>3.59345006942749</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G602" t="n">
-        <v>3.55582284927368</v>
+        <v>3.5558226108551</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.55582284927368</v>
+        <v>3.5558226108551</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G605" t="n">
-        <v>3.49938130378723</v>
+        <v>3.49938106536865</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G611" t="n">
-        <v>3.51819491386414</v>
+        <v>3.51819515228271</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>3.42412567138672</v>
+        <v>3.42412543296814</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G614" t="n">
-        <v>3.42412567138672</v>
+        <v>3.42412543296814</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.5</v>
       </c>
       <c r="G615" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>3.35827708244324</v>
+        <v>3.35827732086182</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.62167119979858</v>
+        <v>3.62167143821716</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>3.68751978874207</v>
+        <v>3.68751955032349</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G621" t="n">
-        <v>3.59345030784607</v>
+        <v>3.59345006942749</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.51819491386414</v>
+        <v>3.51819515228271</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>3.42412567138672</v>
+        <v>3.42412543296814</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>3.43353295326233</v>
+        <v>3.43353247642517</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G630" t="n">
-        <v>3.34887003898621</v>
+        <v>3.34886980056763</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>3.37709093093872</v>
+        <v>3.37709069252014</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G634" t="n">
-        <v>3.20776581764221</v>
+        <v>3.20776629447937</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>3.25480055809021</v>
+        <v>3.25480079650879</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G638" t="n">
-        <v>3.20776581764221</v>
+        <v>3.20776629447937</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G639" t="n">
-        <v>3.15132403373718</v>
+        <v>3.15132427215576</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.14191746711731</v>
+        <v>3.14191722869873</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>3.13251066207886</v>
+        <v>3.13251042366028</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.91615056991577</v>
+        <v>2.91615080833435</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G643" t="n">
-        <v>2.81267499923706</v>
+        <v>2.81267428398132</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>2.793860912323</v>
+        <v>2.79386067390442</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.89733672142029</v>
+        <v>2.89733695983887</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>2.54928016662598</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G647" t="n">
-        <v>2.793860912323</v>
+        <v>2.79386067390442</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>2.91615056991577</v>
+        <v>2.91615080833435</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G650" t="n">
-        <v>2.88792967796326</v>
+        <v>2.88792991638184</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G652" t="n">
-        <v>3.10428953170776</v>
+        <v>3.10428977012634</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.5</v>
       </c>
       <c r="G654" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.5</v>
       </c>
       <c r="G655" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G657" t="n">
-        <v>3.24539375305176</v>
+        <v>3.24539351463318</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.5</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.5</v>
       </c>
       <c r="G660" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G661" t="n">
-        <v>3.2830216884613</v>
+        <v>3.28302145004272</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.5</v>
       </c>
       <c r="G662" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>3.49938130378723</v>
+        <v>3.49938106536865</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G677" t="n">
-        <v>3.57463622093201</v>
+        <v>3.57463669776917</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>3.61226415634155</v>
+        <v>3.61226439476013</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>3.51819491386414</v>
+        <v>3.51819515228271</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G685" t="n">
-        <v>3.49938130378723</v>
+        <v>3.49938106536865</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>3.62167119979858</v>
+        <v>3.62167143821716</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G688" t="n">
-        <v>3.57463622093201</v>
+        <v>3.57463669776917</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>3.55582284927368</v>
+        <v>3.5558226108551</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>3.62167119979858</v>
+        <v>3.62167143821716</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.34887003898621</v>
+        <v>3.34886980056763</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.5</v>
       </c>
       <c r="G693" t="n">
-        <v>3.29242849349976</v>
+        <v>3.29242873191833</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G694" t="n">
-        <v>3.16073107719421</v>
+        <v>3.16073131561279</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>3.15132403373718</v>
+        <v>3.15132427215576</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>3.04784822463989</v>
+        <v>3.04784846305847</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.19835925102234</v>
+        <v>3.19835901260376</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G701" t="n">
-        <v>3.20776581764221</v>
+        <v>3.20776629447937</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G702" t="n">
-        <v>3.19835925102234</v>
+        <v>3.19835901260376</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.17954540252686</v>
+        <v>3.17954516410828</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G704" t="n">
-        <v>3.2265796661377</v>
+        <v>3.22657990455627</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G705" t="n">
-        <v>3.2265796661377</v>
+        <v>3.22657990455627</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G706" t="n">
-        <v>3.2265796661377</v>
+        <v>3.22657990455627</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>3.13251066207886</v>
+        <v>3.13251042366028</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>2.96318554878235</v>
+        <v>2.96318578720093</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G710" t="n">
-        <v>2.97259259223938</v>
+        <v>2.9725923538208</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>3.01962733268738</v>
+        <v>3.0196270942688</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>3.15132403373718</v>
+        <v>3.15132427215576</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G719" t="n">
-        <v>3.21064114570618</v>
+        <v>3.21064138412476</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G722" t="n">
-        <v>3.2200562953949</v>
+        <v>3.22005653381348</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>3.2200562953949</v>
+        <v>3.22005653381348</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>3.13531827926636</v>
+        <v>3.13531804084778</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G728" t="n">
-        <v>3.17297983169556</v>
+        <v>3.17297959327698</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>3.2200562953949</v>
+        <v>3.22005653381348</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G737" t="n">
-        <v>3.2200562953949</v>
+        <v>3.22005653381348</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G742" t="n">
-        <v>3.32362508773804</v>
+        <v>3.32362532615662</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G746" t="n">
-        <v>3.41777968406677</v>
+        <v>3.41777944564819</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187149047852</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>3.40836405754089</v>
+        <v>3.40836381912231</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G752" t="n">
-        <v>3.44602513313293</v>
+        <v>3.44602537155151</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G756" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.75</v>
       </c>
       <c r="G758" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.47427153587341</v>
+        <v>3.47427177429199</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G767" t="n">
-        <v>3.41777968406677</v>
+        <v>3.41777944564819</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G768" t="n">
-        <v>3.44602513313293</v>
+        <v>3.44602537155151</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G769" t="n">
-        <v>3.39894819259644</v>
+        <v>3.39894843101501</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G773" t="n">
-        <v>3.44602513313293</v>
+        <v>3.44602537155151</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G775" t="n">
-        <v>3.39894819259644</v>
+        <v>3.39894843101501</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>3.37070226669312</v>
+        <v>3.37070250511169</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>3.41777968406677</v>
+        <v>3.41777944564819</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G788" t="n">
-        <v>3.41777968406677</v>
+        <v>3.41777944564819</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>3.37070226669312</v>
+        <v>3.37070250511169</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G790" t="n">
-        <v>3.41777968406677</v>
+        <v>3.41777944564819</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G793" t="n">
-        <v>3.3330409526825</v>
+        <v>3.33304071426392</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G794" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G795" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G797" t="n">
-        <v>3.32362508773804</v>
+        <v>3.32362532615662</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>3.40836405754089</v>
+        <v>3.40836381912231</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G803" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G805" t="n">
-        <v>3.36128711700439</v>
+        <v>3.36128735542297</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G807" t="n">
-        <v>3.32362508773804</v>
+        <v>3.32362532615662</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187149047852</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G811" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>3.37070226669312</v>
+        <v>3.37070250511169</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187149047852</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.37070226669312</v>
+        <v>3.37070250511169</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36128711700439</v>
+        <v>3.36128735542297</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G827" t="n">
-        <v>3.39894819259644</v>
+        <v>3.39894843101501</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G828" t="n">
-        <v>3.36128711700439</v>
+        <v>3.36128735542297</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.3330409526825</v>
+        <v>3.33304071426392</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G833" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187149047852</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>3.37070226669312</v>
+        <v>3.37070250511169</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G837" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>3.37070226669312</v>
+        <v>3.37070250511169</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>3.3330409526825</v>
+        <v>3.33304071426392</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G842" t="n">
-        <v>3.34245634078979</v>
+        <v>3.34245610237122</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G843" t="n">
-        <v>3.32362508773804</v>
+        <v>3.32362532615662</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>3.37070226669312</v>
+        <v>3.37070250511169</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>3.3330409526825</v>
+        <v>3.33304071426392</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G849" t="n">
-        <v>3.39894819259644</v>
+        <v>3.39894843101501</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G850" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>3.49310231208801</v>
+        <v>3.49310207366943</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.75</v>
       </c>
       <c r="G855" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.75</v>
       </c>
       <c r="G859" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.75</v>
       </c>
       <c r="G862" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.75</v>
       </c>
       <c r="G863" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G864" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G865" t="n">
-        <v>3.50251793861389</v>
+        <v>3.50251746177673</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G866" t="n">
-        <v>3.50251793861389</v>
+        <v>3.50251746177673</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.49310231208801</v>
+        <v>3.49310207366943</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>3.61550188064575</v>
+        <v>3.61550211906433</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G875" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>3.72848677635193</v>
+        <v>3.72848653793335</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>3.72848677635193</v>
+        <v>3.72848653793335</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G880" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G881" t="n">
-        <v>3.70024037361145</v>
+        <v>3.70024061203003</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G882" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G884" t="n">
-        <v>3.70024037361145</v>
+        <v>3.70024061203003</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G886" t="n">
-        <v>3.63433241844177</v>
+        <v>3.63433265686035</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G887" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.72848677635193</v>
+        <v>3.72848653793335</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>3.72848677635193</v>
+        <v>3.72848653793335</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>3.72848677635193</v>
+        <v>3.72848653793335</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G893" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>3.72848677635193</v>
+        <v>3.72848653793335</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G908" t="n">
-        <v>3.70024037361145</v>
+        <v>3.70024061203003</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G911" t="n">
-        <v>3.70965552330017</v>
+        <v>3.70965576171875</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G912" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>3.72848677635193</v>
+        <v>3.72848653793335</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G915" t="n">
-        <v>3.70024037361145</v>
+        <v>3.70024061203003</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>3.70024037361145</v>
+        <v>3.70024061203003</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G918" t="n">
-        <v>3.70024037361145</v>
+        <v>3.70024061203003</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G919" t="n">
-        <v>3.71907114982605</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>3.64374804496765</v>
+        <v>3.64374780654907</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G921" t="n">
-        <v>3.70965552330017</v>
+        <v>3.70965576171875</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>3.62491726875305</v>
+        <v>3.62491750717163</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>3.63433241844177</v>
+        <v>3.63433265686035</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>3.59667110443115</v>
+        <v>3.59667086601257</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.60608673095703</v>
+        <v>3.60608649253845</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.62491726875305</v>
+        <v>3.62491750717163</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G929" t="n">
-        <v>3.50251793861389</v>
+        <v>3.50251746177673</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G931" t="n">
-        <v>3.50251793861389</v>
+        <v>3.50251746177673</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.75</v>
       </c>
       <c r="G934" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>3.49310231208801</v>
+        <v>3.49310207366943</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>3.48368668556213</v>
+        <v>3.48368692398071</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>3.55900955200195</v>
+        <v>3.55900979042053</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.75</v>
       </c>
       <c r="G941" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>3.75</v>
       </c>
       <c r="G942" t="n">
-        <v>3.53076362609863</v>
+        <v>3.53076386451721</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50251793861389</v>
+        <v>3.50251746177673</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G945" t="n">
-        <v>3.50251793861389</v>
+        <v>3.50251746177673</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>3.49310231208801</v>
+        <v>3.49310207366943</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>3.50709342956543</v>
+        <v>3.50709319114685</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G950" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>3.50709342956543</v>
+        <v>3.50709319114685</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G955" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>3.48818683624268</v>
+        <v>3.48818707466125</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G958" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G959" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G963" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G965" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G969" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G971" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G973" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G974" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G976" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G977" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928119659424</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G981" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928119659424</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G982" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G983" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G984" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>3.28967213630676</v>
+        <v>3.28967237472534</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G990" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G992" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G993" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G994" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928119659424</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G997" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G998" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>3.50709342956543</v>
+        <v>3.50709319114685</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.28967213630676</v>
+        <v>3.28967237472534</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.27076625823975</v>
+        <v>3.27076601982117</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.22350072860718</v>
+        <v>3.22350096702576</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.27076625823975</v>
+        <v>3.27076601982117</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.48818683624268</v>
+        <v>3.48818707466125</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.48818683624268</v>
+        <v>3.48818707466125</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928119659424</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928119659424</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928119659424</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.49763989448547</v>
+        <v>3.49764013290405</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.41256213188171</v>
+        <v>3.41256237030029</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.41256213188171</v>
+        <v>3.41256237030029</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.41256213188171</v>
+        <v>3.41256237030029</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.28967213630676</v>
+        <v>3.28967237472534</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.27076625823975</v>
+        <v>3.27076601982117</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41256213188171</v>
+        <v>3.41256237030029</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.41256213188171</v>
+        <v>3.41256237030029</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.41256213188171</v>
+        <v>3.41256237030029</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.28967213630676</v>
+        <v>3.28967237472534</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.22350072860718</v>
+        <v>3.22350096702576</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.18568873405457</v>
+        <v>3.18568849563599</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.19514179229736</v>
+        <v>3.19514155387878</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928119659424</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.27076625823975</v>
+        <v>3.27076601982117</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.41256213188171</v>
+        <v>3.41256237030029</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.42201566696167</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.35584402084351</v>
+        <v>3.35584378242493</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.34639120101929</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.44172930717468</v>
+        <v>3.44172954559326</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592484474182</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.29872155189514</v>
+        <v>3.29872131347656</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.251051902771</v>
+        <v>3.25105214118958</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.29872155189514</v>
+        <v>3.29872131347656</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.38452625274658</v>
+        <v>3.384526014328</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545848846436</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.44172930717468</v>
+        <v>3.44172954559326</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.44172930717468</v>
+        <v>3.44172954559326</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.44172930717468</v>
+        <v>3.44172954559326</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.44172930717468</v>
+        <v>3.44172954559326</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.53706860542297</v>
+        <v>3.53706836700439</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.6991446018219</v>
+        <v>3.69914436340332</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007636070251</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.53706860542297</v>
+        <v>3.53706836700439</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.6133394241333</v>
+        <v>3.61333918571472</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.6991446018219</v>
+        <v>3.69914436340332</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.6991446018219</v>
+        <v>3.69914436340332</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.76588129997253</v>
+        <v>3.76588153839111</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.76588129997253</v>
+        <v>3.76588153839111</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.6991446018219</v>
+        <v>3.69914436340332</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007636070251</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.6991446018219</v>
+        <v>3.69914436340332</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007636070251</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007636070251</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.6133394241333</v>
+        <v>3.61333918571472</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.6133394241333</v>
+        <v>3.61333918571472</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.6133394241333</v>
+        <v>3.61333918571472</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.6133394241333</v>
+        <v>3.61333918571472</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.6133394241333</v>
+        <v>3.61333918571472</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.6133394241333</v>
+        <v>3.61333918571472</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.56566977500916</v>
+        <v>3.56567001342773</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.63240718841553</v>
+        <v>3.63240694999695</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.6705424785614</v>
+        <v>3.67054271697998</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.65147495269775</v>
+        <v>3.65147471427917</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.67125654220581</v>
+        <v>3.67125630378723</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.5556263923645</v>
+        <v>3.55562663078308</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.57489824295044</v>
+        <v>3.57489800453186</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.67125654220581</v>
+        <v>3.67125630378723</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.57489824295044</v>
+        <v>3.57489800453186</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.57489824295044</v>
+        <v>3.57489800453186</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.57489824295044</v>
+        <v>3.57489800453186</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.67125654220581</v>
+        <v>3.67125630378723</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.67125654220581</v>
+        <v>3.67125630378723</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.67125654220581</v>
+        <v>3.67125630378723</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.69052815437317</v>
+        <v>3.69052791595459</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.39181685447693</v>
+        <v>3.39181709289551</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.41108894348145</v>
+        <v>3.41108870506287</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.41108894348145</v>
+        <v>3.41108870506287</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.40145254135132</v>
+        <v>3.4014527797699</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.41108894348145</v>
+        <v>3.41108870506287</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400201797485</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400201797485</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.39181685447693</v>
+        <v>3.39181709289551</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.39181685447693</v>
+        <v>3.39181709289551</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.42072463035583</v>
+        <v>3.42072439193726</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.42072463035583</v>
+        <v>3.42072439193726</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.40145254135132</v>
+        <v>3.4014527797699</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.42072463035583</v>
+        <v>3.42072439193726</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400201797485</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.28582262992859</v>
+        <v>3.28582286834717</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.42072463035583</v>
+        <v>3.42072439193726</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.28582262992859</v>
+        <v>3.28582286834717</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400201797485</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.76761484146118</v>
+        <v>3.76761507987976</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.76761484146118</v>
+        <v>3.76761507987976</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.76761484146118</v>
+        <v>3.76761507987976</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.70979976654053</v>
+        <v>3.70980000495911</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.77725100517273</v>
+        <v>3.77725076675415</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.77725100517273</v>
+        <v>3.77725076675415</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.81579446792603</v>
+        <v>3.81579422950745</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.81579446792603</v>
+        <v>3.81579422950745</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.8061580657959</v>
+        <v>3.80615830421448</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.81579446792603</v>
+        <v>3.81579422950745</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.8061580657959</v>
+        <v>3.80615830421448</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.8061580657959</v>
+        <v>3.80615830421448</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.71943545341492</v>
+        <v>3.7194356918335</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.70979976654053</v>
+        <v>3.70980000495911</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.71943545341492</v>
+        <v>3.7194356918335</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.73870778083801</v>
+        <v>3.73870754241943</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.73870778083801</v>
+        <v>3.73870754241943</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.71943545341492</v>
+        <v>3.7194356918335</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.69052815437317</v>
+        <v>3.69052791595459</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.77725100517273</v>
+        <v>3.77725076675415</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1653" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.5556263923645</v>
+        <v>3.55562663078308</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.5556263923645</v>
+        <v>3.55562663078308</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1669" t="n">
-        <v>3.48817563056946</v>
+        <v>3.48817539215088</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.48817563056946</v>
+        <v>3.48817539215088</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.42072463035583</v>
+        <v>3.42072439193726</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.42072463035583</v>
+        <v>3.42072439193726</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.48817563056946</v>
+        <v>3.48817539215088</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.47853946685791</v>
+        <v>3.47853970527649</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.48817563056946</v>
+        <v>3.48817539215088</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.65198493003845</v>
+        <v>3.65198469161987</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.67125654220581</v>
+        <v>3.67125630378723</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.69052815437317</v>
+        <v>3.69052791595459</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.70979976654053</v>
+        <v>3.70980000495911</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.5556263923645</v>
+        <v>3.55562663078308</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.59853577613831</v>
+        <v>3.59853601455688</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.52051854133606</v>
+        <v>3.52051877975464</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.52051854133606</v>
+        <v>3.52051877975464</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.53027105331421</v>
+        <v>3.53027081489563</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.53027105331421</v>
+        <v>3.53027081489563</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.59853577613831</v>
+        <v>3.59853601455688</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.75456976890564</v>
+        <v>3.75457000732422</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.81308269500732</v>
+        <v>3.8130829334259</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.16415977478027</v>
+        <v>4.16415929794312</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1751" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.96911668777466</v>
+        <v>3.96911692619324</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1762" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1764" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1765" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1766" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1779" t="n">
-        <v>4.11539840698242</v>
+        <v>4.11539888381958</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1781" t="n">
-        <v>4.16415977478027</v>
+        <v>4.16415929794312</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1788" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.16415977478027</v>
+        <v>4.16415929794312</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1801" t="n">
-        <v>4.30068874359131</v>
+        <v>4.30068922042847</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>4.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1831" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>4.25</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.98862147331238</v>
+        <v>3.9886212348938</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>4.25</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.93986058235168</v>
+        <v>3.93986034393311</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.93986058235168</v>
+        <v>3.93986034393311</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1895" t="n">
-        <v>4.3982105255127</v>
+        <v>4.39821100234985</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.30068874359131</v>
+        <v>4.30068922042847</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.35920190811157</v>
+        <v>4.35920143127441</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.33969783782959</v>
+        <v>4.33969736099243</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1923" t="n">
-        <v>4.33969783782959</v>
+        <v>4.33969736099243</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1924" t="n">
-        <v>4.33969783782959</v>
+        <v>4.33969736099243</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.30068874359131</v>
+        <v>4.30068922042847</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1974" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1985" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1995" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -60328,6 +60328,32 @@
         <v>7.01999998092651</v>
       </c>
       <c r="H2306" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2307" t="n">
+        <v>71499</v>
+      </c>
+      <c r="C2307" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>7.11999988555908</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G2307" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H2307" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28400492668152</v>
+        <v>2.28400468826294</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32163238525391</v>
+        <v>2.32163214683533</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28400492668152</v>
+        <v>2.28400468826294</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G22" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>2.255784034729</v>
+        <v>2.25578379631042</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>2.30093717575073</v>
+        <v>2.30093741416931</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G28" t="n">
-        <v>2.255784034729</v>
+        <v>2.25578379631042</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G29" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>2.28400492668152</v>
+        <v>2.28400468826294</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>2.33480215072632</v>
+        <v>2.3348023891449</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G36" t="n">
-        <v>2.30846309661865</v>
+        <v>2.30846261978149</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.31034445762634</v>
+        <v>2.31034421920776</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G40" t="n">
-        <v>2.32163238525391</v>
+        <v>2.32163214683533</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G41" t="n">
-        <v>2.32163238525391</v>
+        <v>2.32163214683533</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G42" t="n">
-        <v>2.2915301322937</v>
+        <v>2.29153037071228</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G46" t="n">
-        <v>2.29717445373535</v>
+        <v>2.29717421531677</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G47" t="n">
-        <v>2.35549759864807</v>
+        <v>2.35549712181091</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G50" t="n">
-        <v>2.39312481880188</v>
+        <v>2.39312505722046</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G51" t="n">
-        <v>2.38748097419739</v>
+        <v>2.38748121261597</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G57" t="n">
-        <v>2.34609007835388</v>
+        <v>2.34609031677246</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G58" t="n">
-        <v>2.34609007835388</v>
+        <v>2.34609031677246</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G59" t="n">
-        <v>2.34609007835388</v>
+        <v>2.34609031677246</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G61" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G65" t="n">
-        <v>2.24261403083801</v>
+        <v>2.24261379241943</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>2.22944450378418</v>
+        <v>2.2294442653656</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G69" t="n">
-        <v>2.29717445373535</v>
+        <v>2.29717421531677</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G70" t="n">
-        <v>2.30846309661865</v>
+        <v>2.30846261978149</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G74" t="n">
-        <v>2.30093717575073</v>
+        <v>2.30093741416931</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G78" t="n">
-        <v>2.35737872123718</v>
+        <v>2.35737895965576</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G79" t="n">
-        <v>2.35926008224487</v>
+        <v>2.35925984382629</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34985327720642</v>
+        <v>2.34985303878784</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G84" t="n">
-        <v>2.33480215072632</v>
+        <v>2.3348023891449</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G85" t="n">
-        <v>2.34797191619873</v>
+        <v>2.34797143936157</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G86" t="n">
-        <v>2.34420919418335</v>
+        <v>2.34420895576477</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G92" t="n">
-        <v>2.32539510726929</v>
+        <v>2.32539486885071</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G93" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G98" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G109" t="n">
-        <v>2.43639707565308</v>
+        <v>2.4363968372345</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.50224542617798</v>
+        <v>2.50224566459656</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>2.60572195053101</v>
+        <v>2.60572218894958</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60572195053101</v>
+        <v>2.60572218894958</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G117" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>2.54928040504456</v>
+        <v>2.54928064346313</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>2.51165294647217</v>
+        <v>2.51165246963501</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>2.54928040504456</v>
+        <v>2.54928064346313</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.54928040504456</v>
+        <v>2.54928064346313</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G127" t="n">
-        <v>2.52105951309204</v>
+        <v>2.52105927467346</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.5398736000061</v>
+        <v>2.53987336158752</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G131" t="n">
-        <v>2.52105951309204</v>
+        <v>2.52105927467346</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G132" t="n">
-        <v>2.51165294647217</v>
+        <v>2.51165246963501</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G137" t="n">
-        <v>2.46461772918701</v>
+        <v>2.46461820602417</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>2.42699027061462</v>
+        <v>2.42698979377747</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G139" t="n">
-        <v>2.42699027061462</v>
+        <v>2.42698979377747</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G140" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G141" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G142" t="n">
-        <v>2.51165294647217</v>
+        <v>2.51165246963501</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.52105951309204</v>
+        <v>2.52105927467346</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>2.42699027061462</v>
+        <v>2.42698979377747</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G148" t="n">
-        <v>2.43639707565308</v>
+        <v>2.4363968372345</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.43639707565308</v>
+        <v>2.4363968372345</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G152" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G157" t="n">
-        <v>2.46461772918701</v>
+        <v>2.46461820602417</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G159" t="n">
-        <v>2.46461772918701</v>
+        <v>2.46461820602417</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G162" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>2.46461772918701</v>
+        <v>2.46461820602417</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G169" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G189" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G197" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G201" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G209" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>2.46461772918701</v>
+        <v>2.46461820602417</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>2.49283885955811</v>
+        <v>2.49283862113953</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G219" t="n">
-        <v>2.4834315776825</v>
+        <v>2.48343181610107</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G223" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>2.47402477264404</v>
+        <v>2.47402501106262</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42699027061462</v>
+        <v>2.42698979377747</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G226" t="n">
-        <v>2.43639707565308</v>
+        <v>2.4363968372345</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.21063017845154</v>
+        <v>2.21063041687012</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>2.22003722190857</v>
+        <v>2.22003746032715</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>2.21063017845154</v>
+        <v>2.21063041687012</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.21063017845154</v>
+        <v>2.21063041687012</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G236" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22003722190857</v>
+        <v>2.22003746032715</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22944450378418</v>
+        <v>2.2294442653656</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G252" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G259" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G272" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G274" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G276" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G284" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G286" t="n">
-        <v>2.18241000175476</v>
+        <v>2.18240928649902</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>2.15418910980225</v>
+        <v>2.15418887138367</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.03189849853516</v>
+        <v>2.03189897537231</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G289" t="n">
-        <v>2.0507128238678</v>
+        <v>2.05071258544922</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G291" t="n">
-        <v>2.0036780834198</v>
+        <v>2.00367784500122</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="n">
-        <v>2.16359543800354</v>
+        <v>2.16359567642212</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>2.21063017845154</v>
+        <v>2.21063041687012</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G294" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G305" t="n">
-        <v>2.18241000175476</v>
+        <v>2.18240928649902</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>2.21063017845154</v>
+        <v>2.21063041687012</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G320" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G335" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G336" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G337" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G338" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G339" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G340" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G346" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G348" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G354" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G359" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G361" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G362" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G365" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>2.22944450378418</v>
+        <v>2.2294442653656</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G370" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G374" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G377" t="n">
-        <v>2.20122361183167</v>
+        <v>2.20122337341309</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G378" t="n">
-        <v>2.20122361183167</v>
+        <v>2.20122337341309</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G379" t="n">
-        <v>2.20122361183167</v>
+        <v>2.20122337341309</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G380" t="n">
-        <v>2.20122361183167</v>
+        <v>2.20122337341309</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G381" t="n">
-        <v>2.22003722190857</v>
+        <v>2.22003746032715</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G382" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.22003722190857</v>
+        <v>2.22003746032715</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G385" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G389" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G394" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G400" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G407" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G411" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G421" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G423" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G424" t="n">
-        <v>2.43639707565308</v>
+        <v>2.4363968372345</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.46461772918701</v>
+        <v>2.46461820602417</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.42699027061462</v>
+        <v>2.42698979377747</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G430" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G433" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24825835227966</v>
+        <v>2.24825859069824</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>2.27647924423218</v>
+        <v>2.2764790058136</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.29529285430908</v>
+        <v>2.29529309272766</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G443" t="n">
-        <v>2.26707220077515</v>
+        <v>2.26707196235657</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G449" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G451" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.37054848670959</v>
+        <v>2.37054872512817</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G455" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G461" t="n">
-        <v>2.30469965934753</v>
+        <v>2.30469989776611</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G464" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>2.42699027061462</v>
+        <v>2.42698979377747</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G476" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>2.42699027061462</v>
+        <v>2.42698979377747</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G479" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>2.37995553016663</v>
+        <v>2.37995529174805</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.36114168167114</v>
+        <v>2.36114144325256</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>2.33292102813721</v>
+        <v>2.33292078971863</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.38936233520508</v>
+        <v>2.38936257362366</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G495" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>2.40817618370056</v>
+        <v>2.40817594528198</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G500" t="n">
-        <v>2.5398736000061</v>
+        <v>2.53987336158752</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.63394260406494</v>
+        <v>2.63394284248352</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G502" t="n">
-        <v>2.5398736000061</v>
+        <v>2.53987336158752</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>2.56809401512146</v>
+        <v>2.56809425354004</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G505" t="n">
-        <v>2.56809401512146</v>
+        <v>2.56809425354004</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G506" t="n">
-        <v>2.56809401512146</v>
+        <v>2.56809425354004</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G507" t="n">
-        <v>2.57750105857849</v>
+        <v>2.57750129699707</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.68097758293152</v>
+        <v>2.68097734451294</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>2.80326771736145</v>
+        <v>2.80326747894287</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.80326771736145</v>
+        <v>2.80326747894287</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>2.80326771736145</v>
+        <v>2.80326747894287</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>2.80326771736145</v>
+        <v>2.80326747894287</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>2.81267428398132</v>
+        <v>2.8126745223999</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.81267428398132</v>
+        <v>2.8126745223999</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.90674376487732</v>
+        <v>2.9067440032959</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>3.01022028923035</v>
+        <v>3.01022052764893</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G537" t="n">
-        <v>2.99140620231628</v>
+        <v>2.99140644073486</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>3.09488272666931</v>
+        <v>3.09488248825073</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>3.0666618347168</v>
+        <v>3.06666159629822</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>3.0196270942688</v>
+        <v>3.01962733268738</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>3.0196270942688</v>
+        <v>3.01962733268738</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G544" t="n">
-        <v>3.02903437614441</v>
+        <v>3.02903413772583</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G545" t="n">
-        <v>3.01022028923035</v>
+        <v>3.01022052764893</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G546" t="n">
-        <v>2.9725923538208</v>
+        <v>2.97259259223938</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.99140620231628</v>
+        <v>2.99140644073486</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>2.93496465682983</v>
+        <v>2.93496489524841</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.94437193870544</v>
+        <v>2.94437170028687</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.9725923538208</v>
+        <v>2.97259259223938</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G552" t="n">
-        <v>3.01022028923035</v>
+        <v>3.01022052764893</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>2.94437193870544</v>
+        <v>2.94437170028687</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G554" t="n">
-        <v>2.93496465682983</v>
+        <v>2.93496489524841</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.99140620231628</v>
+        <v>2.99140644073486</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>3.0196270942688</v>
+        <v>3.01962733268738</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>3.01022028923035</v>
+        <v>3.01022052764893</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G560" t="n">
-        <v>2.93496465682983</v>
+        <v>2.93496489524841</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.99140620231628</v>
+        <v>2.99140644073486</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89733695983887</v>
+        <v>2.89733672142029</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>2.74682593345642</v>
+        <v>2.746826171875</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>2.80326771736145</v>
+        <v>2.80326747894287</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G573" t="n">
-        <v>2.99140620231628</v>
+        <v>2.99140644073486</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G575" t="n">
-        <v>3.30183529853821</v>
+        <v>3.30183506011963</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G576" t="n">
-        <v>3.34886980056763</v>
+        <v>3.34887027740479</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>3.4711606502533</v>
+        <v>3.47116017341614</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G586" t="n">
-        <v>3.4429395198822</v>
+        <v>3.44293975830078</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G588" t="n">
-        <v>3.4711606502533</v>
+        <v>3.47116017341614</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G589" t="n">
-        <v>3.40531158447266</v>
+        <v>3.40531182289124</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G591" t="n">
-        <v>3.40531158447266</v>
+        <v>3.40531182289124</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>3.40531158447266</v>
+        <v>3.40531182289124</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G593" t="n">
-        <v>3.36768412590027</v>
+        <v>3.36768388748169</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>3.3959047794342</v>
+        <v>3.39590454101562</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G595" t="n">
-        <v>3.65929913520813</v>
+        <v>3.65929889678955</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>3.69692707061768</v>
+        <v>3.6969268321991</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G599" t="n">
-        <v>3.59345006942749</v>
+        <v>3.59345054626465</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G600" t="n">
-        <v>3.63107800483704</v>
+        <v>3.63107824325562</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G605" t="n">
-        <v>3.49938106536865</v>
+        <v>3.49938082695007</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>3.48997402191162</v>
+        <v>3.48997449874878</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G611" t="n">
-        <v>3.51819515228271</v>
+        <v>3.51819491386414</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>3.40531158447266</v>
+        <v>3.40531182289124</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.5</v>
       </c>
       <c r="G615" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>3.35827732086182</v>
+        <v>3.35827708244324</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.62167143821716</v>
+        <v>3.62167119979858</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>3.68751955032349</v>
+        <v>3.68751978874207</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G619" t="n">
-        <v>3.65929913520813</v>
+        <v>3.65929889678955</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G621" t="n">
-        <v>3.59345006942749</v>
+        <v>3.59345054626465</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.51819515228271</v>
+        <v>3.51819491386414</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>3.36768412590027</v>
+        <v>3.36768388748169</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>3.40531158447266</v>
+        <v>3.40531182289124</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G627" t="n">
-        <v>3.3959047794342</v>
+        <v>3.39590454101562</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G630" t="n">
-        <v>3.34886980056763</v>
+        <v>3.34887027740479</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G631" t="n">
-        <v>3.3959047794342</v>
+        <v>3.39590454101562</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>3.37709069252014</v>
+        <v>3.37709093093872</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G633" t="n">
-        <v>3.26420760154724</v>
+        <v>3.2642080783844</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G634" t="n">
-        <v>3.20776629447937</v>
+        <v>3.20776605606079</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>3.25480079650879</v>
+        <v>3.25480055809021</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G638" t="n">
-        <v>3.20776629447937</v>
+        <v>3.20776605606079</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.14191722869873</v>
+        <v>3.14191699028015</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G643" t="n">
-        <v>2.81267428398132</v>
+        <v>2.8126745223999</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.89733695983887</v>
+        <v>2.89733672142029</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>2.54928040504456</v>
+        <v>2.54928064346313</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G649" t="n">
-        <v>2.90674376487732</v>
+        <v>2.9067440032959</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G651" t="n">
-        <v>2.90674376487732</v>
+        <v>2.9067440032959</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.5</v>
       </c>
       <c r="G654" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.5</v>
       </c>
       <c r="G655" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G657" t="n">
-        <v>3.24539351463318</v>
+        <v>3.24539375305176</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.5</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.5</v>
       </c>
       <c r="G660" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.5</v>
       </c>
       <c r="G662" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>3.49938106536865</v>
+        <v>3.49938082695007</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>3.61226439476013</v>
+        <v>3.61226391792297</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G680" t="n">
-        <v>3.65929913520813</v>
+        <v>3.65929889678955</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>3.58404326438904</v>
+        <v>3.58404350280762</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>3.6028573513031</v>
+        <v>3.60285711288452</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>3.51819515228271</v>
+        <v>3.51819491386414</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>3.48997402191162</v>
+        <v>3.48997449874878</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G685" t="n">
-        <v>3.49938106536865</v>
+        <v>3.49938082695007</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>3.62167143821716</v>
+        <v>3.62167119979858</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>3.62167143821716</v>
+        <v>3.62167119979858</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G691" t="n">
-        <v>3.3959047794342</v>
+        <v>3.39590454101562</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.34886980056763</v>
+        <v>3.34887027740479</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.5</v>
       </c>
       <c r="G693" t="n">
-        <v>3.29242873191833</v>
+        <v>3.29242849349976</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G694" t="n">
-        <v>3.16073131561279</v>
+        <v>3.16073107719421</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>3.04784846305847</v>
+        <v>3.04784822463989</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G697" t="n">
-        <v>3.00081348419189</v>
+        <v>3.00081324577332</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>3.01022028923035</v>
+        <v>3.01022052764893</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G701" t="n">
-        <v>3.20776629447937</v>
+        <v>3.20776605606079</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.17954516410828</v>
+        <v>3.17954540252686</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>3.00081348419189</v>
+        <v>3.00081324577332</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G710" t="n">
-        <v>2.9725923538208</v>
+        <v>2.97259259223938</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G711" t="n">
-        <v>3.0666618347168</v>
+        <v>3.06666159629822</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G712" t="n">
-        <v>3.01022028923035</v>
+        <v>3.01022052764893</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>3.0196270942688</v>
+        <v>3.01962733268738</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>3.2671332359314</v>
+        <v>3.26713347434998</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G718" t="n">
-        <v>3.19181060791016</v>
+        <v>3.19181084632874</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G719" t="n">
-        <v>3.21064138412476</v>
+        <v>3.2106409072876</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G721" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G725" t="n">
-        <v>3.19181060791016</v>
+        <v>3.19181084632874</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>3.18239498138428</v>
+        <v>3.18239521980286</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G728" t="n">
-        <v>3.17297959327698</v>
+        <v>3.17297983169556</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>3.20122575759888</v>
+        <v>3.2012255191803</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.20122575759888</v>
+        <v>3.2012255191803</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G732" t="n">
-        <v>3.18239498138428</v>
+        <v>3.18239521980286</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G733" t="n">
-        <v>3.20122575759888</v>
+        <v>3.2012255191803</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G734" t="n">
-        <v>3.20122575759888</v>
+        <v>3.2012255191803</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>3.20122575759888</v>
+        <v>3.2012255191803</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.35187149047852</v>
+        <v>3.35187172889709</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>3.40836381912231</v>
+        <v>3.40836358070374</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>3.51193284988403</v>
+        <v>3.51193308830261</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.75</v>
       </c>
       <c r="G758" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G759" t="n">
-        <v>3.51193284988403</v>
+        <v>3.51193308830261</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.47427177429199</v>
+        <v>3.47427153587341</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>3.45544099807739</v>
+        <v>3.45544075965881</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G763" t="n">
-        <v>3.52134847640991</v>
+        <v>3.52134823799133</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.45544099807739</v>
+        <v>3.45544075965881</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G772" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G778" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G786" t="n">
-        <v>3.45544099807739</v>
+        <v>3.45544075965881</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>3.45544099807739</v>
+        <v>3.45544075965881</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G791" t="n">
-        <v>3.3047947883606</v>
+        <v>3.30479431152344</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G793" t="n">
-        <v>3.33304071426392</v>
+        <v>3.3330409526825</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G796" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G798" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>3.40836381912231</v>
+        <v>3.40836358070374</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G805" t="n">
-        <v>3.36128735542297</v>
+        <v>3.36128711700439</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>3.35187149047852</v>
+        <v>3.35187172889709</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>3.35187149047852</v>
+        <v>3.35187172889709</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G815" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G816" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G820" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36128735542297</v>
+        <v>3.36128711700439</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G828" t="n">
-        <v>3.36128735542297</v>
+        <v>3.36128711700439</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.33304071426392</v>
+        <v>3.3330409526825</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G831" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G833" t="n">
-        <v>3.35187149047852</v>
+        <v>3.35187172889709</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G834" t="n">
-        <v>3.38011765480042</v>
+        <v>3.38011789321899</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>3.33304071426392</v>
+        <v>3.3330409526825</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G844" t="n">
-        <v>3.22947192192078</v>
+        <v>3.2294716835022</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>3.33304071426392</v>
+        <v>3.3330409526825</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>3.49310207366943</v>
+        <v>3.49310255050659</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>3.51193284988403</v>
+        <v>3.51193308830261</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G854" t="n">
-        <v>3.52134847640991</v>
+        <v>3.52134823799133</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.75</v>
       </c>
       <c r="G855" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.75</v>
       </c>
       <c r="G859" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>3.52134847640991</v>
+        <v>3.52134823799133</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G861" t="n">
-        <v>3.52134847640991</v>
+        <v>3.52134823799133</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.75</v>
       </c>
       <c r="G862" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.75</v>
       </c>
       <c r="G863" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>3.51193284988403</v>
+        <v>3.51193308830261</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>3.45544099807739</v>
+        <v>3.45544075965881</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.49310207366943</v>
+        <v>3.49310255050659</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>3.51193284988403</v>
+        <v>3.51193308830261</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>3.54017925262451</v>
+        <v>3.54017901420593</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G872" t="n">
-        <v>3.54017925262451</v>
+        <v>3.54017901420593</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>3.61550211906433</v>
+        <v>3.61550188064575</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G875" t="n">
-        <v>3.68140959739685</v>
+        <v>3.68140983581543</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="n">
-        <v>3.76614809036255</v>
+        <v>3.76614785194397</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G880" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G882" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G886" t="n">
-        <v>3.63433265686035</v>
+        <v>3.63433241844177</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G887" t="n">
-        <v>3.68140959739685</v>
+        <v>3.68140983581543</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G891" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G892" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G893" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G898" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>3.69082474708557</v>
+        <v>3.69082522392273</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>3.69082474708557</v>
+        <v>3.69082522392273</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>3.69082474708557</v>
+        <v>3.69082522392273</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G911" t="n">
-        <v>3.70965576171875</v>
+        <v>3.70965552330017</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G912" t="n">
-        <v>3.68140959739685</v>
+        <v>3.68140983581543</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G913" t="n">
-        <v>3.74731731414795</v>
+        <v>3.74731707572937</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>3.68140959739685</v>
+        <v>3.68140983581543</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G919" t="n">
-        <v>3.71907138824463</v>
+        <v>3.71907091140747</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G921" t="n">
-        <v>3.70965576171875</v>
+        <v>3.70965552330017</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>3.62491750717163</v>
+        <v>3.62491703033447</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>3.68140959739685</v>
+        <v>3.68140983581543</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>3.63433265686035</v>
+        <v>3.63433241844177</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>3.59667086601257</v>
+        <v>3.59667134284973</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.60608649253845</v>
+        <v>3.60608625411987</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.62491750717163</v>
+        <v>3.62491703033447</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G928" t="n">
-        <v>3.54017925262451</v>
+        <v>3.54017901420593</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G932" t="n">
-        <v>3.54017925262451</v>
+        <v>3.54017901420593</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>3.52134847640991</v>
+        <v>3.52134823799133</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.75</v>
       </c>
       <c r="G934" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>3.49310207366943</v>
+        <v>3.49310255050659</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="n">
-        <v>3.52134847640991</v>
+        <v>3.52134823799133</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>3.51193284988403</v>
+        <v>3.51193308830261</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>3.55900979042053</v>
+        <v>3.55900955200195</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>3.54959416389465</v>
+        <v>3.54959440231323</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.75</v>
       </c>
       <c r="G941" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>3.75</v>
       </c>
       <c r="G942" t="n">
-        <v>3.53076386451721</v>
+        <v>3.53076362609863</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>3.57784056663513</v>
+        <v>3.57784080505371</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>3.49310207366943</v>
+        <v>3.49310255050659</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>3.51193284988403</v>
+        <v>3.51193308830261</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G948" t="n">
-        <v>3.54017925262451</v>
+        <v>3.54017901420593</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51654624938965</v>
+        <v>3.51654648780823</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56381154060364</v>
+        <v>3.56381177902222</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G963" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G965" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G969" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G971" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G973" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G977" t="n">
-        <v>3.51654624938965</v>
+        <v>3.51654648780823</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>3.45982813835144</v>
+        <v>3.45982789993286</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>3.46928119659424</v>
+        <v>3.46928095817566</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G981" t="n">
-        <v>3.46928119659424</v>
+        <v>3.46928095817566</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G982" t="n">
-        <v>3.45982813835144</v>
+        <v>3.45982789993286</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G983" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G984" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G986" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G991" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G993" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G994" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>3.46928119659424</v>
+        <v>3.46928095817566</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G996" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G997" t="n">
-        <v>3.51654624938965</v>
+        <v>3.51654648780823</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G998" t="n">
-        <v>3.51654624938965</v>
+        <v>3.51654648780823</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.45982813835144</v>
+        <v>3.45982789993286</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.27076601982117</v>
+        <v>3.27076625823975</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.22350096702576</v>
+        <v>3.22350072860718</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.27076601982117</v>
+        <v>3.27076625823975</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.56381154060364</v>
+        <v>3.56381177902222</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.51654624938965</v>
+        <v>3.51654648780823</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.46928119659424</v>
+        <v>3.46928095817566</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.46928119659424</v>
+        <v>3.46928095817566</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.46928119659424</v>
+        <v>3.46928095817566</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.52599930763245</v>
+        <v>3.52599954605103</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.45037460327148</v>
+        <v>3.45037484169006</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.41256237030029</v>
+        <v>3.41256213188171</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.41256237030029</v>
+        <v>3.41256213188171</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.41256237030029</v>
+        <v>3.41256213188171</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28021931648254</v>
+        <v>3.28021955490112</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.28021931648254</v>
+        <v>3.28021955490112</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.28021931648254</v>
+        <v>3.28021955490112</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.27076601982117</v>
+        <v>3.27076625823975</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.45982813835144</v>
+        <v>3.45982789993286</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41256237030029</v>
+        <v>3.41256213188171</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.41256237030029</v>
+        <v>3.41256213188171</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.41256237030029</v>
+        <v>3.41256213188171</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.28021931648254</v>
+        <v>3.28021955490112</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.26131296157837</v>
+        <v>3.26131319999695</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.22350096702576</v>
+        <v>3.22350072860718</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.10061049461365</v>
+        <v>3.10061073303223</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.19514155387878</v>
+        <v>3.19514179229736</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.46928119659424</v>
+        <v>3.46928095817566</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.29912543296814</v>
+        <v>3.29912567138672</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.26131296157837</v>
+        <v>3.26131319999695</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.27076601982117</v>
+        <v>3.27076625823975</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.41256237030029</v>
+        <v>3.41256213188171</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.31803154945374</v>
+        <v>3.31803131103516</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.39365601539612</v>
+        <v>3.3936562538147</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43146848678589</v>
+        <v>3.43146872520447</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.42201542854309</v>
+        <v>3.42201519012451</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.4031093120575</v>
+        <v>3.40310883522034</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.3747501373291</v>
+        <v>3.37474989891052</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.36529684066772</v>
+        <v>3.3652970790863</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.28021931648254</v>
+        <v>3.28021955490112</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.32748460769653</v>
+        <v>3.32748436927795</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.26131296157837</v>
+        <v>3.26131319999695</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.33693766593933</v>
+        <v>3.33693742752075</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.34639096260071</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.34639096260071</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.44172954559326</v>
+        <v>3.44172930717468</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.54660224914551</v>
+        <v>3.54660248756409</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.31778907775879</v>
+        <v>3.31778931617737</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.31778907775879</v>
+        <v>3.31778931617737</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.34639096260071</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.34639096260071</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.34639096260071</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.37499237060547</v>
+        <v>3.37499260902405</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1273" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.35592484474182</v>
+        <v>3.35592460632324</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.34639096260071</v>
+        <v>3.34639072418213</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.31778907775879</v>
+        <v>3.31778931617737</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.25105214118958</v>
+        <v>3.251051902771</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.31778907775879</v>
+        <v>3.31778931617737</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.31778907775879</v>
+        <v>3.31778931617737</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.28918766975403</v>
+        <v>3.28918790817261</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.46079778671265</v>
+        <v>3.46079754829407</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.46079778671265</v>
+        <v>3.46079754829407</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.384526014328</v>
+        <v>3.38452649116516</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.36545848846436</v>
+        <v>3.36545825004578</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.46079778671265</v>
+        <v>3.46079754829407</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.44172954559326</v>
+        <v>3.44172930717468</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.43219542503357</v>
+        <v>3.43219566345215</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.44172954559326</v>
+        <v>3.44172930717468</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.44172954559326</v>
+        <v>3.44172930717468</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.39406037330627</v>
+        <v>3.3940601348877</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.44172954559326</v>
+        <v>3.44172930717468</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.81355094909668</v>
+        <v>3.8135507106781</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.80401682853699</v>
+        <v>3.80401706695557</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.68007636070251</v>
+        <v>3.68007612228394</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380530357361</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.61333918571472</v>
+        <v>3.6133394241333</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.58473777770996</v>
+        <v>3.58473753929138</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.76588153839111</v>
+        <v>3.76588129997253</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.76588153839111</v>
+        <v>3.76588129997253</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.68007636070251</v>
+        <v>3.68007612228394</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.68007636070251</v>
+        <v>3.68007612228394</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.68007636070251</v>
+        <v>3.68007612228394</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.61333918571472</v>
+        <v>3.6133394241333</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380530357361</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.61333918571472</v>
+        <v>3.6133394241333</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.61333918571472</v>
+        <v>3.6133394241333</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.61333918571472</v>
+        <v>3.6133394241333</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380530357361</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380530357361</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380530357361</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.61333918571472</v>
+        <v>3.6133394241333</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.68961048126221</v>
+        <v>3.68961024284363</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.66100859642029</v>
+        <v>3.66100883483887</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.58473777770996</v>
+        <v>3.58473753929138</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.61333918571472</v>
+        <v>3.6133394241333</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.58473777770996</v>
+        <v>3.58473753929138</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.54660224914551</v>
+        <v>3.54660248756409</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.67054271697998</v>
+        <v>3.6705424785614</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380530357361</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.64234900474548</v>
+        <v>3.6423487663269</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.67125630378723</v>
+        <v>3.67125654220581</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.70016407966614</v>
+        <v>3.70016384124756</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.70016407966614</v>
+        <v>3.70016384124756</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.5941698551178</v>
+        <v>3.59416961669922</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.5941698551178</v>
+        <v>3.59416961669922</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.60380578041077</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.60380578041077</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.55562663078308</v>
+        <v>3.5556263923645</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.60380578041077</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.67125630378723</v>
+        <v>3.67125654220581</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.5941698551178</v>
+        <v>3.59416961669922</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.60380578041077</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.67125630378723</v>
+        <v>3.67125654220581</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.67125630378723</v>
+        <v>3.67125654220581</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.67125630378723</v>
+        <v>3.67125654220581</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.69052791595459</v>
+        <v>3.69052815437317</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.50744724273682</v>
+        <v>3.5074474811554</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.52671885490417</v>
+        <v>3.52671909332275</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.39181709289551</v>
+        <v>3.39181685447693</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.5</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.38218116760254</v>
+        <v>3.38218092918396</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.35327363014221</v>
+        <v>3.35327386856079</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.33400201797485</v>
+        <v>3.33400225639343</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.35327363014221</v>
+        <v>3.35327386856079</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.33400201797485</v>
+        <v>3.33400225639343</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.39181709289551</v>
+        <v>3.39181685447693</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.39181709289551</v>
+        <v>3.39181685447693</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.42072439193726</v>
+        <v>3.42072463035583</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.42072439193726</v>
+        <v>3.42072463035583</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.42072439193726</v>
+        <v>3.42072463035583</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.35327363014221</v>
+        <v>3.35327386856079</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.33400201797485</v>
+        <v>3.33400225639343</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.42072439193726</v>
+        <v>3.42072463035583</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.29545879364014</v>
+        <v>3.29545855522156</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.35327363014221</v>
+        <v>3.35327386856079</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.35327363014221</v>
+        <v>3.35327386856079</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.35327363014221</v>
+        <v>3.35327386856079</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.5</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.32436609268188</v>
+        <v>3.32436633110046</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.32436609268188</v>
+        <v>3.32436633110046</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.29545879364014</v>
+        <v>3.29545855522156</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.33400201797485</v>
+        <v>3.33400225639343</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.35327363014221</v>
+        <v>3.35327386856079</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.31473016738892</v>
+        <v>3.3147304058075</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1578" t="n">
-        <v>3.38218116760254</v>
+        <v>3.38218092918396</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1582" t="n">
-        <v>3.50744724273682</v>
+        <v>3.5074474811554</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.5</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.37254548072815</v>
+        <v>3.37254524230957</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.70016407966614</v>
+        <v>3.70016384124756</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.70980000495911</v>
+        <v>3.70979976654053</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.78688669204712</v>
+        <v>3.78688645362854</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>4</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.85433769226074</v>
+        <v>3.85433745384216</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>4</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.85433769226074</v>
+        <v>3.85433745384216</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>4</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.85433769226074</v>
+        <v>3.85433745384216</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.84470152854919</v>
+        <v>3.84470176696777</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>4</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.85433769226074</v>
+        <v>3.85433745384216</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.84470152854919</v>
+        <v>3.84470176696777</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.84470152854919</v>
+        <v>3.84470176696777</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.78688669204712</v>
+        <v>3.78688645362854</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.84470152854919</v>
+        <v>3.84470176696777</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.70016407966614</v>
+        <v>3.70016384124756</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.70980000495911</v>
+        <v>3.70979976654053</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.73870754241943</v>
+        <v>3.73870778083801</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.73870754241943</v>
+        <v>3.73870778083801</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.69052791595459</v>
+        <v>3.69052815437317</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.75797915458679</v>
+        <v>3.75797939300537</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.78688669204712</v>
+        <v>3.78688645362854</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.78688669204712</v>
+        <v>3.78688645362854</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.64234900474548</v>
+        <v>3.6423487663269</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.70016407966614</v>
+        <v>3.70016384124756</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.64234900474548</v>
+        <v>3.6423487663269</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.64234900474548</v>
+        <v>3.6423487663269</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1653" t="n">
-        <v>3.64234900474548</v>
+        <v>3.6423487663269</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.5941698551178</v>
+        <v>3.59416961669922</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.5941698551178</v>
+        <v>3.59416961669922</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.55562663078308</v>
+        <v>3.5556263923645</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.54599046707153</v>
+        <v>3.54599070549011</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.50744724273682</v>
+        <v>3.5074474811554</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.55562663078308</v>
+        <v>3.5556263923645</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.5941698551178</v>
+        <v>3.59416961669922</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.50744724273682</v>
+        <v>3.5074474811554</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.52671885490417</v>
+        <v>3.52671909332275</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.42072439193726</v>
+        <v>3.42072463035583</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.42072439193726</v>
+        <v>3.42072463035583</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.44963216781616</v>
+        <v>3.44963192939758</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.47853970527649</v>
+        <v>3.47853946685791</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.65198469161987</v>
+        <v>3.65198493003845</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.67125630378723</v>
+        <v>3.67125654220581</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.64234900474548</v>
+        <v>3.6423487663269</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.69052791595459</v>
+        <v>3.69052815437317</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.70980000495911</v>
+        <v>3.70979976654053</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.66162085533142</v>
+        <v>3.66162061691284</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.52671885490417</v>
+        <v>3.52671909332275</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.55562663078308</v>
+        <v>3.5556263923645</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.59853601455688</v>
+        <v>3.59853577613831</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.52051877975464</v>
+        <v>3.52051854133606</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.52051877975464</v>
+        <v>3.52051854133606</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.53027081489563</v>
+        <v>3.53027105331421</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.53027081489563</v>
+        <v>3.53027105331421</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.59853601455688</v>
+        <v>3.59853577613831</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.75457000732422</v>
+        <v>3.75456976890564</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.8130829334259</v>
+        <v>3.81308269500732</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.16415929794312</v>
+        <v>4.16415977478027</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1751" t="n">
-        <v>4.19341611862183</v>
+        <v>4.19341564178467</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.99837327003479</v>
+        <v>3.99837303161621</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.96911692619324</v>
+        <v>3.96911668777466</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1762" t="n">
-        <v>4.03738164901733</v>
+        <v>4.03738117218018</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1764" t="n">
-        <v>4.03738164901733</v>
+        <v>4.03738117218018</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1765" t="n">
-        <v>4.03738164901733</v>
+        <v>4.03738117218018</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1766" t="n">
-        <v>4.03738164901733</v>
+        <v>4.03738117218018</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.19341611862183</v>
+        <v>4.19341564178467</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="n">
-        <v>4.19341611862183</v>
+        <v>4.19341564178467</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1779" t="n">
-        <v>4.11539888381958</v>
+        <v>4.11539840698242</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1781" t="n">
-        <v>4.16415929794312</v>
+        <v>4.16415977478027</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1788" t="n">
-        <v>4.02762937545776</v>
+        <v>4.02762985229492</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.16415929794312</v>
+        <v>4.16415977478027</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1801" t="n">
-        <v>4.30068922042847</v>
+        <v>4.30068874359131</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>4.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.14465522766113</v>
+        <v>4.14465475082397</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.14465522766113</v>
+        <v>4.14465475082397</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.02762937545776</v>
+        <v>4.02762985229492</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1831" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>4.25</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.14465522766113</v>
+        <v>4.14465475082397</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.03738164901733</v>
+        <v>4.03738117218018</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.9886212348938</v>
+        <v>3.98862147331238</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>4.25</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.14465522766113</v>
+        <v>4.14465475082397</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.1349024772644</v>
+        <v>4.13490295410156</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.99837327003479</v>
+        <v>3.99837303161621</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.02762937545776</v>
+        <v>4.02762985229492</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.99837327003479</v>
+        <v>3.99837303161621</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.99837327003479</v>
+        <v>3.99837303161621</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.93986034393311</v>
+        <v>3.93986058235168</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.99837327003479</v>
+        <v>3.99837303161621</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.93986034393311</v>
+        <v>3.93986058235168</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.02762937545776</v>
+        <v>4.02762985229492</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1895" t="n">
-        <v>4.39821100234985</v>
+        <v>4.3982105255127</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.30068922042847</v>
+        <v>4.30068874359131</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.35920143127441</v>
+        <v>4.35920190811157</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.33969736099243</v>
+        <v>4.33969783782959</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1923" t="n">
-        <v>4.33969736099243</v>
+        <v>4.33969783782959</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1924" t="n">
-        <v>4.33969736099243</v>
+        <v>4.33969783782959</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.25192832946777</v>
+        <v>4.25192880630493</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.30068922042847</v>
+        <v>4.30068874359131</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1974" t="n">
-        <v>4.25192832946777</v>
+        <v>4.25192880630493</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1985" t="n">
-        <v>4.19341611862183</v>
+        <v>4.19341564178467</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.25192832946777</v>
+        <v>4.25192880630493</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1995" t="n">
-        <v>4.25192832946777</v>
+        <v>4.25192880630493</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -60354,6 +60354,32 @@
         <v>7.5</v>
       </c>
       <c r="H2307" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2308" t="n">
+        <v>107973</v>
+      </c>
+      <c r="C2308" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F2308" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="G2308" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="H2308" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28964877128601</v>
+        <v>2.28964900970459</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28964877128601</v>
+        <v>2.28964900970459</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G14" t="n">
-        <v>2.33103919029236</v>
+        <v>2.33103942871094</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G18" t="n">
-        <v>2.25954651832581</v>
+        <v>2.25954675674438</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G19" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G22" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>2.25578379631042</v>
+        <v>2.255784034729</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G25" t="n">
-        <v>2.25390243530273</v>
+        <v>2.25390219688416</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G28" t="n">
-        <v>2.25578379631042</v>
+        <v>2.255784034729</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G29" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G32" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3348023891449</v>
+        <v>2.33480215072632</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G39" t="n">
-        <v>2.31975102424622</v>
+        <v>2.31975126266479</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G43" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G44" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G47" t="n">
-        <v>2.35549712181091</v>
+        <v>2.35549736022949</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G49" t="n">
-        <v>2.36866688728333</v>
+        <v>2.36866664886475</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G52" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G53" t="n">
-        <v>2.39124369621277</v>
+        <v>2.39124417304993</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G54" t="n">
-        <v>2.39124369621277</v>
+        <v>2.39124417304993</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G61" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G65" t="n">
-        <v>2.24261379241943</v>
+        <v>2.24261450767517</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G71" t="n">
-        <v>2.29905581474304</v>
+        <v>2.29905557632446</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G72" t="n">
-        <v>2.31598782539368</v>
+        <v>2.31598830223083</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G76" t="n">
-        <v>2.32915806770325</v>
+        <v>2.32915830612183</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G77" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G78" t="n">
-        <v>2.35737895965576</v>
+        <v>2.3573784828186</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G79" t="n">
-        <v>2.35925984382629</v>
+        <v>2.35926008224487</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34985303878784</v>
+        <v>2.34985327720642</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G83" t="n">
-        <v>2.33668351173401</v>
+        <v>2.33668327331543</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G84" t="n">
-        <v>2.3348023891449</v>
+        <v>2.33480215072632</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G85" t="n">
-        <v>2.34797143936157</v>
+        <v>2.34797167778015</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G88" t="n">
-        <v>2.31975102424622</v>
+        <v>2.31975126266479</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G89" t="n">
-        <v>2.31598782539368</v>
+        <v>2.31598830223083</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>2.3385648727417</v>
+        <v>2.33856463432312</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G92" t="n">
-        <v>2.32539486885071</v>
+        <v>2.32539510726929</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G93" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G98" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G99" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G109" t="n">
-        <v>2.4363968372345</v>
+        <v>2.43639731407166</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.50224566459656</v>
+        <v>2.50224590301514</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G112" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>2.60572218894958</v>
+        <v>2.60572195053101</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60572218894958</v>
+        <v>2.60572195053101</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.75</v>
       </c>
       <c r="G116" t="n">
-        <v>2.58690786361694</v>
+        <v>2.58690810203552</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>2.54928064346313</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G119" t="n">
-        <v>2.55868744850159</v>
+        <v>2.55868697166443</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>2.51165246963501</v>
+        <v>2.51165270805359</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>2.54928064346313</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.54928064346313</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.75</v>
       </c>
       <c r="G124" t="n">
-        <v>2.58690786361694</v>
+        <v>2.58690810203552</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>2.62453556060791</v>
+        <v>2.62453579902649</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="n">
-        <v>2.58690786361694</v>
+        <v>2.58690810203552</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G127" t="n">
-        <v>2.52105927467346</v>
+        <v>2.52105951309204</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.53987336158752</v>
+        <v>2.5398736000061</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G131" t="n">
-        <v>2.52105927467346</v>
+        <v>2.52105951309204</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G132" t="n">
-        <v>2.51165246963501</v>
+        <v>2.51165270805359</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.41758298873901</v>
+        <v>2.41758322715759</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G137" t="n">
-        <v>2.46461820602417</v>
+        <v>2.46461796760559</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G142" t="n">
-        <v>2.51165246963501</v>
+        <v>2.51165270805359</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.52105927467346</v>
+        <v>2.52105951309204</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G148" t="n">
-        <v>2.4363968372345</v>
+        <v>2.43639731407166</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.4363968372345</v>
+        <v>2.43639731407166</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G153" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G157" t="n">
-        <v>2.46461820602417</v>
+        <v>2.46461796760559</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G159" t="n">
-        <v>2.46461820602417</v>
+        <v>2.46461796760559</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>2.46461820602417</v>
+        <v>2.46461796760559</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G166" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G173" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G183" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G189" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G193" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G196" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G209" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>2.46461820602417</v>
+        <v>2.46461796760559</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>2.49283862113953</v>
+        <v>2.49283838272095</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G222" t="n">
-        <v>2.45521092414856</v>
+        <v>2.45521068572998</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>2.47402501106262</v>
+        <v>2.47402453422546</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G226" t="n">
-        <v>2.4363968372345</v>
+        <v>2.43639731407166</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>2.19181656837463</v>
+        <v>2.19181680679321</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>2.19181656837463</v>
+        <v>2.19181680679321</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003698348999</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G236" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003698348999</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G242" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G243" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G244" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G245" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G262" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G272" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G274" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G276" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G278" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G284" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G285" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G286" t="n">
-        <v>2.18240928649902</v>
+        <v>2.18240976333618</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.03189897537231</v>
+        <v>2.03189921379089</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G289" t="n">
-        <v>2.05071258544922</v>
+        <v>2.05071234703064</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G291" t="n">
-        <v>2.00367784500122</v>
+        <v>2.0036780834198</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="n">
-        <v>2.16359567642212</v>
+        <v>2.1635959148407</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G294" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G305" t="n">
-        <v>2.18240928649902</v>
+        <v>2.18240976333618</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G307" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G320" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G323" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G332" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G335" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G336" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G338" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G339" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G340" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G346" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G348" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G354" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G355" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G359" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G361" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G362" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G365" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G366" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G370" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G374" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G381" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003698348999</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G382" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.22003746032715</v>
+        <v>2.22003698348999</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G385" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G389" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G399" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G400" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>2.23885130882263</v>
+        <v>2.23885154724121</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G407" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G411" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G415" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25766515731812</v>
+        <v>2.25766539573669</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G417" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G418" t="n">
-        <v>2.28588628768921</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G424" t="n">
-        <v>2.4363968372345</v>
+        <v>2.43639731407166</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.46461820602417</v>
+        <v>2.46461796760559</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G429" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G430" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G433" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.24825859069824</v>
+        <v>2.24825835227966</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>2.2764790058136</v>
+        <v>2.27647924423218</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.29529309272766</v>
+        <v>2.2952926158905</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G443" t="n">
-        <v>2.26707196235657</v>
+        <v>2.26707220077515</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.41758298873901</v>
+        <v>2.41758322715759</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G450" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.37054872512817</v>
+        <v>2.37054848670959</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G458" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G461" t="n">
-        <v>2.30469989776611</v>
+        <v>2.30470013618469</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G462" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G467" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G468" t="n">
-        <v>2.41758298873901</v>
+        <v>2.41758322715759</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G470" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G474" t="n">
-        <v>2.41758298873901</v>
+        <v>2.41758322715759</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G478" t="n">
-        <v>2.41758298873901</v>
+        <v>2.41758322715759</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G487" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>2.33292078971863</v>
+        <v>2.33292102813721</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G490" t="n">
-        <v>2.34232759475708</v>
+        <v>2.34232783317566</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.38936257362366</v>
+        <v>2.38936233520508</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G494" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G496" t="n">
-        <v>2.41758298873901</v>
+        <v>2.41758322715759</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G497" t="n">
-        <v>2.41758298873901</v>
+        <v>2.41758322715759</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.39876914024353</v>
+        <v>2.39876937866211</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53987336158752</v>
+        <v>2.5398736000061</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.63394284248352</v>
+        <v>2.6339430809021</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G502" t="n">
-        <v>2.53987336158752</v>
+        <v>2.5398736000061</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G504" t="n">
-        <v>2.55868744850159</v>
+        <v>2.55868697166443</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G507" t="n">
-        <v>2.57750129699707</v>
+        <v>2.57750105857849</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>2.61512875556946</v>
+        <v>2.61512899398804</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G509" t="n">
-        <v>2.64334988594055</v>
+        <v>2.64334940910339</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.76564002037048</v>
+        <v>2.76563954353333</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>2.80326747894287</v>
+        <v>2.80326771736145</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.80326747894287</v>
+        <v>2.80326771736145</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>2.80326747894287</v>
+        <v>2.80326771736145</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G516" t="n">
-        <v>2.79386067390442</v>
+        <v>2.793860912323</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.79386067390442</v>
+        <v>2.793860912323</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.79386067390442</v>
+        <v>2.793860912323</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.79386067390442</v>
+        <v>2.793860912323</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>2.80326747894287</v>
+        <v>2.80326771736145</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>2.8126745223999</v>
+        <v>2.81267476081848</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>2.76564002037048</v>
+        <v>2.76563954353333</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.8126745223999</v>
+        <v>2.81267476081848</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G533" t="n">
-        <v>2.84089517593384</v>
+        <v>2.84089541435242</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.9067440032959</v>
+        <v>2.90674376487732</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G537" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>3.09488248825073</v>
+        <v>3.09488272666931</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>3.06666159629822</v>
+        <v>3.06666207313538</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>3.03844094276428</v>
+        <v>3.03844118118286</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97259259223938</v>
+        <v>2.97259283065796</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.94437170028687</v>
+        <v>2.94437193870544</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.97259259223938</v>
+        <v>2.97259283065796</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>2.94437170028687</v>
+        <v>2.94437193870544</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89733672142029</v>
+        <v>2.89733695983887</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>2.85030245780945</v>
+        <v>2.85030221939087</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>2.85030245780945</v>
+        <v>2.85030221939087</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>2.85030245780945</v>
+        <v>2.85030221939087</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>2.80326747894287</v>
+        <v>2.80326771736145</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G571" t="n">
-        <v>2.91615080833435</v>
+        <v>2.91615056991577</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.88792991638184</v>
+        <v>2.88793015480042</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G573" t="n">
-        <v>2.99140644073486</v>
+        <v>2.99140620231628</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G575" t="n">
-        <v>3.30183506011963</v>
+        <v>3.30183529853821</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G576" t="n">
-        <v>3.34887027740479</v>
+        <v>3.34886980056763</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>3.42412543296814</v>
+        <v>3.42412567138672</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="n">
-        <v>3.42412543296814</v>
+        <v>3.42412567138672</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G580" t="n">
-        <v>3.42412543296814</v>
+        <v>3.42412567138672</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>3.42412543296814</v>
+        <v>3.42412567138672</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G582" t="n">
-        <v>3.43353247642517</v>
+        <v>3.43353223800659</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G586" t="n">
-        <v>3.44293975830078</v>
+        <v>3.44293999671936</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>3.43353247642517</v>
+        <v>3.43353223800659</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G599" t="n">
-        <v>3.59345054626465</v>
+        <v>3.59345006942749</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G600" t="n">
-        <v>3.63107824325562</v>
+        <v>3.63107800483704</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>3.64989233016968</v>
+        <v>3.64989256858826</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>3.56522965431213</v>
+        <v>3.56522989273071</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G605" t="n">
-        <v>3.49938082695007</v>
+        <v>3.49938106536865</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.75</v>
       </c>
       <c r="G606" t="n">
-        <v>3.52760195732117</v>
+        <v>3.52760171890259</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.75</v>
       </c>
       <c r="G607" t="n">
-        <v>3.52760195732117</v>
+        <v>3.52760171890259</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>3.42412543296814</v>
+        <v>3.42412567138672</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G614" t="n">
-        <v>3.42412543296814</v>
+        <v>3.42412567138672</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>3.35827708244324</v>
+        <v>3.35827684402466</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G620" t="n">
-        <v>3.56522965431213</v>
+        <v>3.56522989273071</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G621" t="n">
-        <v>3.59345054626465</v>
+        <v>3.59345006942749</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>3.42412543296814</v>
+        <v>3.42412567138672</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>3.43353247642517</v>
+        <v>3.43353223800659</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G630" t="n">
-        <v>3.34887027740479</v>
+        <v>3.34886980056763</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>3.37709093093872</v>
+        <v>3.3770911693573</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G633" t="n">
-        <v>3.2642080783844</v>
+        <v>3.26420760154724</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>3.33946299552917</v>
+        <v>3.33946323394775</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G639" t="n">
-        <v>3.15132427215576</v>
+        <v>3.15132451057434</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.14191699028015</v>
+        <v>3.14191746711731</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.91615080833435</v>
+        <v>2.91615056991577</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G643" t="n">
-        <v>2.8126745223999</v>
+        <v>2.81267476081848</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>2.79386067390442</v>
+        <v>2.793860912323</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.89733672142029</v>
+        <v>2.89733695983887</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>2.54928064346313</v>
+        <v>2.54928040504456</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G647" t="n">
-        <v>2.79386067390442</v>
+        <v>2.793860912323</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>2.91615080833435</v>
+        <v>2.91615056991577</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G649" t="n">
-        <v>2.9067440032959</v>
+        <v>2.90674376487732</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G650" t="n">
-        <v>2.88792991638184</v>
+        <v>2.88793015480042</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G651" t="n">
-        <v>2.9067440032959</v>
+        <v>2.90674376487732</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G652" t="n">
-        <v>3.10428977012634</v>
+        <v>3.10428953170776</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>3.21717286109924</v>
+        <v>3.2171733379364</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>3.33946299552917</v>
+        <v>3.33946323394775</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G664" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G665" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G669" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G672" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G675" t="n">
-        <v>3.38649773597717</v>
+        <v>3.38649749755859</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>3.49938082695007</v>
+        <v>3.49938106536865</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>3.61226391792297</v>
+        <v>3.61226415634155</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.64989233016968</v>
+        <v>3.64989256858826</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G685" t="n">
-        <v>3.49938082695007</v>
+        <v>3.49938106536865</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>3.56522965431213</v>
+        <v>3.56522989273071</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.34887027740479</v>
+        <v>3.34886980056763</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G694" t="n">
-        <v>3.16073107719421</v>
+        <v>3.16073083877563</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>3.15132427215576</v>
+        <v>3.15132451057434</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>3.18895244598389</v>
+        <v>3.18895220756531</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.17954540252686</v>
+        <v>3.17954516410828</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>2.96318578720093</v>
+        <v>2.96318554878235</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G710" t="n">
-        <v>2.97259259223938</v>
+        <v>2.97259283065796</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G711" t="n">
-        <v>3.06666159629822</v>
+        <v>3.06666207313538</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>3.15132427215576</v>
+        <v>3.15132451057434</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G715" t="n">
-        <v>3.15414881706238</v>
+        <v>3.15414905548096</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>3.26713347434998</v>
+        <v>3.2671332359314</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>3.15414881706238</v>
+        <v>3.15414905548096</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G718" t="n">
-        <v>3.19181084632874</v>
+        <v>3.19181036949158</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G719" t="n">
-        <v>3.2106409072876</v>
+        <v>3.21064114570618</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.5</v>
       </c>
       <c r="G720" t="n">
-        <v>3.29537963867188</v>
+        <v>3.2953794002533</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G722" t="n">
-        <v>3.22005653381348</v>
+        <v>3.22005677223206</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>3.22005653381348</v>
+        <v>3.22005677223206</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G725" t="n">
-        <v>3.19181084632874</v>
+        <v>3.19181036949158</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>3.18239521980286</v>
+        <v>3.18239498138428</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>3.13531804084778</v>
+        <v>3.13531827926636</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G728" t="n">
-        <v>3.17297983169556</v>
+        <v>3.17297959327698</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>3.2012255191803</v>
+        <v>3.20122575759888</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.2012255191803</v>
+        <v>3.20122575759888</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G732" t="n">
-        <v>3.18239521980286</v>
+        <v>3.18239498138428</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G733" t="n">
-        <v>3.2012255191803</v>
+        <v>3.20122575759888</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G734" t="n">
-        <v>3.2012255191803</v>
+        <v>3.20122575759888</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>3.22005653381348</v>
+        <v>3.22005677223206</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>3.2012255191803</v>
+        <v>3.20122575759888</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G737" t="n">
-        <v>3.22005653381348</v>
+        <v>3.22005677223206</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.5</v>
       </c>
       <c r="G740" t="n">
-        <v>3.29537963867188</v>
+        <v>3.2953794002533</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.5</v>
       </c>
       <c r="G743" t="n">
-        <v>3.29537963867188</v>
+        <v>3.2953794002533</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G747" t="n">
-        <v>3.42719459533691</v>
+        <v>3.42719483375549</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187125205994</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>3.40836358070374</v>
+        <v>3.40836405754089</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G752" t="n">
-        <v>3.44602537155151</v>
+        <v>3.44602584838867</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G768" t="n">
-        <v>3.44602537155151</v>
+        <v>3.44602584838867</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G773" t="n">
-        <v>3.44602537155151</v>
+        <v>3.44602584838867</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>3.42719459533691</v>
+        <v>3.42719483375549</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>3.37070250511169</v>
+        <v>3.37070226669312</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>3.37070250511169</v>
+        <v>3.37070226669312</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G791" t="n">
-        <v>3.30479431152344</v>
+        <v>3.3047947883606</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>3.5</v>
       </c>
       <c r="G792" t="n">
-        <v>3.29537963867188</v>
+        <v>3.2953794002533</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.29537963867188</v>
+        <v>3.2953794002533</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>3.40836358070374</v>
+        <v>3.40836405754089</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G805" t="n">
-        <v>3.36128711700439</v>
+        <v>3.36128687858582</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187125205994</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>3.37070250511169</v>
+        <v>3.37070226669312</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187125205994</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.37070250511169</v>
+        <v>3.37070226669312</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36128711700439</v>
+        <v>3.36128687858582</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G828" t="n">
-        <v>3.36128711700439</v>
+        <v>3.36128687858582</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G833" t="n">
-        <v>3.35187172889709</v>
+        <v>3.35187125205994</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>3.37070250511169</v>
+        <v>3.37070226669312</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>3.37070250511169</v>
+        <v>3.37070226669312</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.5</v>
       </c>
       <c r="G840" t="n">
-        <v>3.29537963867188</v>
+        <v>3.2953794002533</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G844" t="n">
-        <v>3.2294716835022</v>
+        <v>3.22947192192078</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>3.37070250511169</v>
+        <v>3.37070226669312</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.5</v>
       </c>
       <c r="G847" t="n">
-        <v>3.29537963867188</v>
+        <v>3.2953794002533</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G865" t="n">
-        <v>3.50251746177673</v>
+        <v>3.50251770019531</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G866" t="n">
-        <v>3.50251746177673</v>
+        <v>3.50251770019531</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>3.65316367149353</v>
+        <v>3.65316390991211</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G875" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G880" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G881" t="n">
-        <v>3.70024061203003</v>
+        <v>3.70024037361145</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G882" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G884" t="n">
-        <v>3.70024061203003</v>
+        <v>3.70024037361145</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G886" t="n">
-        <v>3.63433241844177</v>
+        <v>3.63433265686035</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G887" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G893" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>3.69082522392273</v>
+        <v>3.69082498550415</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>3.69082522392273</v>
+        <v>3.69082498550415</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>3.69082522392273</v>
+        <v>3.69082498550415</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G908" t="n">
-        <v>3.70024061203003</v>
+        <v>3.70024037361145</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G912" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G915" t="n">
-        <v>3.70024061203003</v>
+        <v>3.70024037361145</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>3.70024061203003</v>
+        <v>3.70024037361145</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G918" t="n">
-        <v>3.70024061203003</v>
+        <v>3.70024037361145</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G919" t="n">
-        <v>3.71907091140747</v>
+        <v>3.71907138824463</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>3.64374780654907</v>
+        <v>3.64374804496765</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>3.62491703033447</v>
+        <v>3.62491726875305</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>3.68140983581543</v>
+        <v>3.68140959739685</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>3.63433241844177</v>
+        <v>3.63433265686035</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>3.59667134284973</v>
+        <v>3.59667086601257</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.60608625411987</v>
+        <v>3.60608649253845</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.62491703033447</v>
+        <v>3.62491726875305</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G929" t="n">
-        <v>3.50251746177673</v>
+        <v>3.50251770019531</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G931" t="n">
-        <v>3.50251746177673</v>
+        <v>3.50251770019531</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>3.55900955200195</v>
+        <v>3.55900979042053</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50251746177673</v>
+        <v>3.50251770019531</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>3.57784080505371</v>
+        <v>3.57784056663513</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G945" t="n">
-        <v>3.50251746177673</v>
+        <v>3.50251770019531</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>3.53545236587524</v>
+        <v>3.53545260429382</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G957" t="n">
-        <v>3.53545236587524</v>
+        <v>3.53545260429382</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56381177902222</v>
+        <v>3.56381154060364</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G963" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G965" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G969" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G971" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G973" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G977" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928071975708</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G981" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928071975708</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G982" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G983" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G984" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G986" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>3.28967237472534</v>
+        <v>3.28967261314392</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G991" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G993" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G994" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928071975708</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G997" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G998" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.28967237472534</v>
+        <v>3.28967261314392</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.56381177902222</v>
+        <v>3.56381154060364</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.51654648780823</v>
+        <v>3.51654624938965</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928071975708</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928071975708</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928071975708</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.52599954605103</v>
+        <v>3.52599930763245</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.45037484169006</v>
+        <v>3.45037460327148</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.28967237472534</v>
+        <v>3.28967261314392</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.28021955490112</v>
+        <v>3.28021907806396</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.28021955490112</v>
+        <v>3.28021907806396</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.28021955490112</v>
+        <v>3.28021907806396</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.45982789993286</v>
+        <v>3.45982813835144</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.28967237472534</v>
+        <v>3.28967261314392</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.28021955490112</v>
+        <v>3.28021907806396</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.26131319999695</v>
+        <v>3.26131272315979</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.02498602867126</v>
+        <v>3.02498626708984</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.10061073303223</v>
+        <v>3.10061097145081</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.19514179229736</v>
+        <v>3.19514155387878</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.46928095817566</v>
+        <v>3.46928071975708</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.29912567138672</v>
+        <v>3.29912543296814</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.26131319999695</v>
+        <v>3.26131272315979</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.31803131103516</v>
+        <v>3.31803154945374</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43146872520447</v>
+        <v>3.43146848678589</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.42201519012451</v>
+        <v>3.42201542854309</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.40310883522034</v>
+        <v>3.40310907363892</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.37474989891052</v>
+        <v>3.3747501373291</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.28021955490112</v>
+        <v>3.28021907806396</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.26131319999695</v>
+        <v>3.26131272315979</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.33693742752075</v>
+        <v>3.33693766593933</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.34639072418213</v>
+        <v>3.34639096260071</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.34639072418213</v>
+        <v>3.34639096260071</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.54660248756409</v>
+        <v>3.54660224914551</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.42266178131104</v>
+        <v>3.42266201972961</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.42266178131104</v>
+        <v>3.42266201972961</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.34639072418213</v>
+        <v>3.34639096260071</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.34639072418213</v>
+        <v>3.34639096260071</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.34639072418213</v>
+        <v>3.34639096260071</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.37499260902405</v>
+        <v>3.37499237060547</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>3.42266178131104</v>
+        <v>3.42266201972961</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.35592460632324</v>
+        <v>3.35592436790466</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.34639072418213</v>
+        <v>3.34639096260071</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.251051902771</v>
+        <v>3.25105214118958</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.32732319831848</v>
+        <v>3.3273229598999</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.28918790817261</v>
+        <v>3.28918743133545</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.32732319831848</v>
+        <v>3.3273229598999</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.42266178131104</v>
+        <v>3.42266201972961</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.46079754829407</v>
+        <v>3.46079730987549</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.42266178131104</v>
+        <v>3.42266201972961</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.46079754829407</v>
+        <v>3.46079730987549</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.38452649116516</v>
+        <v>3.38452625274658</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.36545825004578</v>
+        <v>3.36545872688293</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.42266178131104</v>
+        <v>3.42266201972961</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.46079754829407</v>
+        <v>3.46079730987549</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.48939895629883</v>
+        <v>3.48939919471741</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.42266178131104</v>
+        <v>3.42266201972961</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.40359401702881</v>
+        <v>3.40359425544739</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.53706836700439</v>
+        <v>3.53706860542297</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.71821212768555</v>
+        <v>3.71821188926697</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.71821212768555</v>
+        <v>3.71821188926697</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.71821212768555</v>
+        <v>3.71821188926697</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.70867848396301</v>
+        <v>3.70867824554443</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.70867848396301</v>
+        <v>3.70867824554443</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.70867848396301</v>
+        <v>3.70867824554443</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.70867848396301</v>
+        <v>3.70867824554443</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.70867848396301</v>
+        <v>3.70867824554443</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.69914436340332</v>
+        <v>3.6991446018219</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007659912109</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.53706836700439</v>
+        <v>3.53706860542297</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.69914436340332</v>
+        <v>3.6991446018219</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.69914436340332</v>
+        <v>3.6991446018219</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.76588129997253</v>
+        <v>3.76588177680969</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.76588129997253</v>
+        <v>3.76588177680969</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.69914436340332</v>
+        <v>3.6991446018219</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007659912109</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.69914436340332</v>
+        <v>3.6991446018219</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007659912109</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.68007612228394</v>
+        <v>3.68007659912109</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.70867848396301</v>
+        <v>3.70867824554443</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.75</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.57520413398743</v>
+        <v>3.57520389556885</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.75</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.57520413398743</v>
+        <v>3.57520389556885</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.75</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.57520413398743</v>
+        <v>3.57520389556885</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.59427165985107</v>
+        <v>3.59427189826965</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.56567001342773</v>
+        <v>3.56567025184631</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.54660248756409</v>
+        <v>3.54660224914551</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.63240694999695</v>
+        <v>3.63240718841553</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.64194107055664</v>
+        <v>3.64194083213806</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.60380530357361</v>
+        <v>3.60380554199219</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.75</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.59416961669922</v>
+        <v>3.5941698551178</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.59416961669922</v>
+        <v>3.5941698551178</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.75</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.59416961669922</v>
+        <v>3.5941698551178</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.75</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.60380554199219</v>
+        <v>3.60380578041077</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.69052815437317</v>
+        <v>3.69052791595459</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.51708316802979</v>
+        <v>3.51708292961121</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.5074474811554</v>
+        <v>3.50744724273682</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.45926785469055</v>
+        <v>3.45926809310913</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.46890354156494</v>
+        <v>3.46890377998352</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.46890354156494</v>
+        <v>3.46890377998352</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.5</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.38218092918396</v>
+        <v>3.38218116760254</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.35327386856079</v>
+        <v>3.35327363014221</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400177955627</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.35327386856079</v>
+        <v>3.35327363014221</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400177955627</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.45926785469055</v>
+        <v>3.45926809310913</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.35327386856079</v>
+        <v>3.35327363014221</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400177955627</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.29545855522156</v>
+        <v>3.29545879364014</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.35327386856079</v>
+        <v>3.35327363014221</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.35327386856079</v>
+        <v>3.35327363014221</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.35327386856079</v>
+        <v>3.35327363014221</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.5</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.32436633110046</v>
+        <v>3.32436609268188</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.32436633110046</v>
+        <v>3.32436609268188</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.29545855522156</v>
+        <v>3.29545879364014</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.26655125617981</v>
+        <v>3.26655101776123</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.33400225639343</v>
+        <v>3.33400177955627</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.35327386856079</v>
+        <v>3.35327363014221</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.3629093170166</v>
+        <v>3.36290955543518</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1578" t="n">
-        <v>3.38218092918396</v>
+        <v>3.38218116760254</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.58453392982483</v>
+        <v>3.58453416824341</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1582" t="n">
-        <v>3.5074474811554</v>
+        <v>3.50744724273682</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.5</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.37254524230957</v>
+        <v>3.37254548072815</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.72907137870789</v>
+        <v>3.72907161712646</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.78688645362854</v>
+        <v>3.78688669204712</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.77725076675415</v>
+        <v>3.77725100517273</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.77725076675415</v>
+        <v>3.77725100517273</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.79652237892151</v>
+        <v>3.79652261734009</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.79652237892151</v>
+        <v>3.79652261734009</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.79652237892151</v>
+        <v>3.79652261734009</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.79652237892151</v>
+        <v>3.79652261734009</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.78688645362854</v>
+        <v>3.78688669204712</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.72907137870789</v>
+        <v>3.72907161712646</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.7483434677124</v>
+        <v>3.74834322929382</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.73870778083801</v>
+        <v>3.73870754241943</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.7483434677124</v>
+        <v>3.74834322929382</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.7483434677124</v>
+        <v>3.74834322929382</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.73870778083801</v>
+        <v>3.73870754241943</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.72907137870789</v>
+        <v>3.72907161712646</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.7483434677124</v>
+        <v>3.74834322929382</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.69052815437317</v>
+        <v>3.69052791595459</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.75797939300537</v>
+        <v>3.75797891616821</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.78688645362854</v>
+        <v>3.78688669204712</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.78688645362854</v>
+        <v>3.78688669204712</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.77725076675415</v>
+        <v>3.77725100517273</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3.75</v>
       </c>
       <c r="G1651" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1653" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>3.75</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.59416961669922</v>
+        <v>3.5941698551178</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.59416961669922</v>
+        <v>3.5941698551178</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>3.75</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.51708316802979</v>
+        <v>3.51708292961121</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1662" t="n">
-        <v>3.49781155586243</v>
+        <v>3.49781131744385</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.54599070549011</v>
+        <v>3.54599046707153</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.5074474811554</v>
+        <v>3.50744724273682</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.49781155586243</v>
+        <v>3.49781131744385</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.59416961669922</v>
+        <v>3.5941698551178</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1668" t="n">
-        <v>3.51708316802979</v>
+        <v>3.51708292961121</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1671" t="n">
-        <v>3.46890354156494</v>
+        <v>3.46890377998352</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.49781155586243</v>
+        <v>3.49781131744385</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.46890354156494</v>
+        <v>3.46890377998352</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.5074474811554</v>
+        <v>3.50744724273682</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.46890354156494</v>
+        <v>3.46890377998352</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.51708316802979</v>
+        <v>3.51708292961121</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.45926785469055</v>
+        <v>3.45926809310913</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.49781155586243</v>
+        <v>3.49781131744385</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.51708316802979</v>
+        <v>3.51708292961121</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>3.75</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>3.75</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.61344146728516</v>
+        <v>3.61344122886658</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.6423487663269</v>
+        <v>3.64234900474548</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.69052815437317</v>
+        <v>3.69052791595459</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.59853577613831</v>
+        <v>3.59853601455688</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.52051854133606</v>
+        <v>3.52051877975464</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.52051854133606</v>
+        <v>3.52051877975464</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.53027105331421</v>
+        <v>3.53027081489563</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.53027105331421</v>
+        <v>3.53027081489563</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.59853577613831</v>
+        <v>3.59853601455688</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.75456976890564</v>
+        <v>3.75457000732422</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.81308269500732</v>
+        <v>3.8130829334259</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.16415977478027</v>
+        <v>4.16415929794312</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1751" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.96911668777466</v>
+        <v>3.96911692619324</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1762" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1764" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1765" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1766" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1779" t="n">
-        <v>4.11539840698242</v>
+        <v>4.11539888381958</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1781" t="n">
-        <v>4.16415977478027</v>
+        <v>4.16415929794312</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1788" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.16415977478027</v>
+        <v>4.16415929794312</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1801" t="n">
-        <v>4.30068874359131</v>
+        <v>4.30068922042847</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>4.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1831" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>4.25</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.03738117218018</v>
+        <v>4.03738164901733</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.98862147331238</v>
+        <v>3.9886212348938</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>4.25</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.14465475082397</v>
+        <v>4.14465522766113</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.13490295410156</v>
+        <v>4.1349024772644</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.93986058235168</v>
+        <v>3.93986034393311</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.99837303161621</v>
+        <v>3.99837327003479</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.93986058235168</v>
+        <v>3.93986034393311</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.02762985229492</v>
+        <v>4.02762937545776</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1895" t="n">
-        <v>4.3982105255127</v>
+        <v>4.39821100234985</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.30068874359131</v>
+        <v>4.30068922042847</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.35920190811157</v>
+        <v>4.35920143127441</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.33969783782959</v>
+        <v>4.33969736099243</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1923" t="n">
-        <v>4.33969783782959</v>
+        <v>4.33969736099243</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1924" t="n">
-        <v>4.33969783782959</v>
+        <v>4.33969736099243</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.30068874359131</v>
+        <v>4.30068922042847</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1974" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1985" t="n">
-        <v>4.19341564178467</v>
+        <v>4.19341611862183</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1995" t="n">
-        <v>4.25192880630493</v>
+        <v>4.25192832946777</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -60380,6 +60380,32 @@
         <v>7.42000007629395</v>
       </c>
       <c r="H2308" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2309" t="n">
+        <v>29512</v>
+      </c>
+      <c r="C2309" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="D2309" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E2309" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="F2309" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="G2309" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="H2309" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53610,8 +53610,31 @@
       <c r="E2315" t="n">
         <v>8.02000045776367</v>
       </c>
-      <c r="F2315"/>
+      <c r="F2315" t="n">
+        <v>8</v>
+      </c>
       <c r="G2315" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2316" t="n">
+        <v>47892</v>
+      </c>
+      <c r="C2316" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D2316" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="E2316" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="F2316"/>
+      <c r="G2316" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53628,13 +53628,36 @@
         <v>8.10000038146973</v>
       </c>
       <c r="D2316" t="n">
-        <v>7.65999984741211</v>
+        <v>7.6399998664856</v>
       </c>
       <c r="E2316" t="n">
         <v>7.96000003814697</v>
       </c>
-      <c r="F2316"/>
+      <c r="F2316" t="n">
+        <v>7.6399998664856</v>
+      </c>
       <c r="G2316" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2317" t="n">
+        <v>27520</v>
+      </c>
+      <c r="C2317" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="F2317"/>
+      <c r="G2317" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53656,8 +53656,31 @@
       <c r="E2317" t="n">
         <v>7.78000020980835</v>
       </c>
-      <c r="F2317"/>
+      <c r="F2317" t="n">
+        <v>7.48000001907349</v>
+      </c>
       <c r="G2317" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2318" t="n">
+        <v>21372</v>
+      </c>
+      <c r="C2318" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E2318" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F2318"/>
+      <c r="G2318" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53679,8 +53679,31 @@
       <c r="E2318" t="n">
         <v>7.80000019073486</v>
       </c>
-      <c r="F2318"/>
+      <c r="F2318" t="n">
+        <v>7.40000009536743</v>
+      </c>
       <c r="G2318" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2319" t="n">
+        <v>18764</v>
+      </c>
+      <c r="C2319" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D2319" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E2319" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="F2319"/>
+      <c r="G2319" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -53709,6 +53709,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2320">
+      <c r="A2320" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2320" t="n">
+        <v>31210</v>
+      </c>
+      <c r="C2320" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="D2320" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="E2320" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F2320" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="G2320" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G3" t="n">
-        <v>2.27264428138733</v>
+        <v>2.27264451980591</v>
       </c>
       <c r="H3" t="n">
         <v>300</v>
@@ -514,7 +514,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H5" t="n">
         <v>15210</v>
@@ -804,7 +804,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G15" t="n">
-        <v>2.31008505821228</v>
+        <v>2.3100848197937</v>
       </c>
       <c r="H15" t="n">
         <v>150</v>
@@ -833,7 +833,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H16" t="n">
         <v>1501</v>
@@ -862,7 +862,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H17" t="n">
         <v>19552</v>
@@ -920,7 +920,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G19" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H19" t="n">
         <v>19780</v>
@@ -949,7 +949,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G20" t="n">
-        <v>2.27264428138733</v>
+        <v>2.27264451980591</v>
       </c>
       <c r="H20" t="n">
         <v>18228</v>
@@ -1065,7 +1065,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>2.24456405639648</v>
+        <v>2.24456357955933</v>
       </c>
       <c r="H24" t="n">
         <v>9501</v>
@@ -1181,7 +1181,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G28" t="n">
-        <v>2.24456405639648</v>
+        <v>2.24456357955933</v>
       </c>
       <c r="H28" t="n">
         <v>17543</v>
@@ -1268,7 +1268,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>2.27264428138733</v>
+        <v>2.27264451980591</v>
       </c>
       <c r="H31" t="n">
         <v>47973</v>
@@ -1326,7 +1326,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32318925857544</v>
+        <v>2.32318949699402</v>
       </c>
       <c r="H33" t="n">
         <v>14771</v>
@@ -1355,7 +1355,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H34" t="n">
         <v>10362</v>
@@ -1384,7 +1384,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H35" t="n">
         <v>1012</v>
@@ -1413,7 +1413,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G36" t="n">
-        <v>2.29698038101196</v>
+        <v>2.29698061943054</v>
       </c>
       <c r="H36" t="n">
         <v>3211</v>
@@ -1442,7 +1442,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H37" t="n">
         <v>14451</v>
@@ -1471,7 +1471,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.29885268211365</v>
+        <v>2.29885292053223</v>
       </c>
       <c r="H38" t="n">
         <v>7960</v>
@@ -1529,7 +1529,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G40" t="n">
-        <v>2.31008505821228</v>
+        <v>2.3100848197937</v>
       </c>
       <c r="H40" t="n">
         <v>3266</v>
@@ -1558,7 +1558,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G41" t="n">
-        <v>2.31008505821228</v>
+        <v>2.3100848197937</v>
       </c>
       <c r="H41" t="n">
         <v>11643</v>
@@ -1587,7 +1587,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G42" t="n">
-        <v>2.28013253211975</v>
+        <v>2.28013277053833</v>
       </c>
       <c r="H42" t="n">
         <v>16445</v>
@@ -1616,7 +1616,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G43" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H43" t="n">
         <v>2650</v>
@@ -1645,7 +1645,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G44" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H44" t="n">
         <v>10190</v>
@@ -1703,7 +1703,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28574848175049</v>
+        <v>2.28574872016907</v>
       </c>
       <c r="H46" t="n">
         <v>8211</v>
@@ -1790,7 +1790,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G49" t="n">
-        <v>2.35688519477844</v>
+        <v>2.35688543319702</v>
       </c>
       <c r="H49" t="n">
         <v>17001</v>
@@ -1819,7 +1819,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G50" t="n">
-        <v>2.38122153282166</v>
+        <v>2.38122248649597</v>
       </c>
       <c r="H50" t="n">
         <v>9851</v>
@@ -1848,7 +1848,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G51" t="n">
-        <v>2.37560653686523</v>
+        <v>2.37560629844666</v>
       </c>
       <c r="H51" t="n">
         <v>3100</v>
@@ -1964,7 +1964,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H55" t="n">
         <v>1111</v>
@@ -2022,7 +2022,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G57" t="n">
-        <v>2.33442115783691</v>
+        <v>2.33442139625549</v>
       </c>
       <c r="H57" t="n">
         <v>1778</v>
@@ -2051,7 +2051,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G58" t="n">
-        <v>2.33442115783691</v>
+        <v>2.33442139625549</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G59" t="n">
-        <v>2.33442115783691</v>
+        <v>2.33442139625549</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H60" t="n">
         <v>12630</v>
@@ -2254,7 +2254,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G65" t="n">
-        <v>2.23145985603333</v>
+        <v>2.23145961761475</v>
       </c>
       <c r="H65" t="n">
         <v>4450</v>
@@ -2283,7 +2283,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>2.21835565567017</v>
+        <v>2.21835541725159</v>
       </c>
       <c r="H66" t="n">
         <v>8331</v>
@@ -2370,7 +2370,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G69" t="n">
-        <v>2.28574848175049</v>
+        <v>2.28574872016907</v>
       </c>
       <c r="H69" t="n">
         <v>262</v>
@@ -2399,7 +2399,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G70" t="n">
-        <v>2.29698038101196</v>
+        <v>2.29698061943054</v>
       </c>
       <c r="H70" t="n">
         <v>1875</v>
@@ -2428,7 +2428,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G71" t="n">
-        <v>2.28762078285217</v>
+        <v>2.28762054443359</v>
       </c>
       <c r="H71" t="n">
         <v>252</v>
@@ -2457,7 +2457,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G72" t="n">
-        <v>2.30446910858154</v>
+        <v>2.30446839332581</v>
       </c>
       <c r="H72" t="n">
         <v>5916</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H75" t="n">
         <v>57801</v>
@@ -2573,7 +2573,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G76" t="n">
-        <v>2.3175733089447</v>
+        <v>2.31757307052612</v>
       </c>
       <c r="H76" t="n">
         <v>4672</v>
@@ -2602,7 +2602,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G77" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H77" t="n">
         <v>26401</v>
@@ -2631,7 +2631,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G78" t="n">
-        <v>2.34565377235413</v>
+        <v>2.34565353393555</v>
       </c>
       <c r="H78" t="n">
         <v>1261</v>
@@ -2660,7 +2660,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G79" t="n">
-        <v>2.34752559661865</v>
+        <v>2.34752535820007</v>
       </c>
       <c r="H79" t="n">
         <v>3112</v>
@@ -2689,7 +2689,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G80" t="n">
-        <v>2.3381655216217</v>
+        <v>2.33816528320312</v>
       </c>
       <c r="H80" t="n">
         <v>19198</v>
@@ -2747,7 +2747,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H82" t="n">
         <v>2012</v>
@@ -2805,7 +2805,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G84" t="n">
-        <v>2.32318925857544</v>
+        <v>2.32318949699402</v>
       </c>
       <c r="H84" t="n">
         <v>12792</v>
@@ -2863,7 +2863,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G86" t="n">
-        <v>2.33254957199097</v>
+        <v>2.33254933357239</v>
       </c>
       <c r="H86" t="n">
         <v>5927</v>
@@ -2892,7 +2892,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H87" t="n">
         <v>13036</v>
@@ -2950,7 +2950,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G89" t="n">
-        <v>2.30446910858154</v>
+        <v>2.30446839332581</v>
       </c>
       <c r="H89" t="n">
         <v>5068</v>
@@ -3008,7 +3008,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>2.32693290710449</v>
+        <v>2.32693314552307</v>
       </c>
       <c r="H91" t="n">
         <v>5575</v>
@@ -3037,7 +3037,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G92" t="n">
-        <v>2.31382870674133</v>
+        <v>2.31382894515991</v>
       </c>
       <c r="H92" t="n">
         <v>9404</v>
@@ -3066,7 +3066,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G93" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H93" t="n">
         <v>3104</v>
@@ -3153,7 +3153,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H96" t="n">
         <v>8878</v>
@@ -3182,7 +3182,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H97" t="n">
         <v>30057</v>
@@ -3240,7 +3240,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G99" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H99" t="n">
         <v>40000</v>
@@ -3298,7 +3298,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G101" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H101" t="n">
         <v>4650</v>
@@ -3327,7 +3327,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H102" t="n">
         <v>8000</v>
@@ -3356,7 +3356,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G103" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G106" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H106" t="n">
         <v>3950</v>
@@ -3472,7 +3472,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H107" t="n">
         <v>65506</v>
@@ -3501,7 +3501,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>2.43363904953003</v>
+        <v>2.43363833427429</v>
       </c>
       <c r="H108" t="n">
         <v>68109</v>
@@ -3559,7 +3559,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.48980021476746</v>
+        <v>2.48979997634888</v>
       </c>
       <c r="H110" t="n">
         <v>36853</v>
@@ -3588,7 +3588,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G111" t="n">
-        <v>2.5178804397583</v>
+        <v>2.51788020133972</v>
       </c>
       <c r="H111" t="n">
         <v>50415</v>
@@ -3646,7 +3646,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>2.5178804397583</v>
+        <v>2.51788020133972</v>
       </c>
       <c r="H113" t="n">
         <v>61120</v>
@@ -3675,7 +3675,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>2.59276127815247</v>
+        <v>2.59276151657104</v>
       </c>
       <c r="H114" t="n">
         <v>106846</v>
@@ -3704,7 +3704,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G115" t="n">
-        <v>2.59276127815247</v>
+        <v>2.59276151657104</v>
       </c>
       <c r="H115" t="n">
         <v>42848</v>
@@ -3733,7 +3733,7 @@
         <v>2.75</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57404112815857</v>
+        <v>2.57404136657715</v>
       </c>
       <c r="H116" t="n">
         <v>27141</v>
@@ -3762,7 +3762,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G117" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H117" t="n">
         <v>85374</v>
@@ -3791,7 +3791,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>2.5366005897522</v>
+        <v>2.53660106658936</v>
       </c>
       <c r="H118" t="n">
         <v>26180</v>
@@ -3878,7 +3878,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>2.5366005897522</v>
+        <v>2.53660106658936</v>
       </c>
       <c r="H121" t="n">
         <v>26346</v>
@@ -3907,7 +3907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H122" t="n">
         <v>27237</v>
@@ -3936,7 +3936,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.5366005897522</v>
+        <v>2.53660106658936</v>
       </c>
       <c r="H123" t="n">
         <v>26213</v>
@@ -3965,7 +3965,7 @@
         <v>2.75</v>
       </c>
       <c r="G124" t="n">
-        <v>2.57404112815857</v>
+        <v>2.57404136657715</v>
       </c>
       <c r="H124" t="n">
         <v>52662</v>
@@ -3994,7 +3994,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>2.61148190498352</v>
+        <v>2.61148166656494</v>
       </c>
       <c r="H125" t="n">
         <v>27448</v>
@@ -4023,7 +4023,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="n">
-        <v>2.57404112815857</v>
+        <v>2.57404136657715</v>
       </c>
       <c r="H126" t="n">
         <v>5270</v>
@@ -4052,7 +4052,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G127" t="n">
-        <v>2.50851988792419</v>
+        <v>2.50852036476135</v>
       </c>
       <c r="H127" t="n">
         <v>34728</v>
@@ -4081,7 +4081,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.52724075317383</v>
+        <v>2.52724051475525</v>
       </c>
       <c r="H128" t="n">
         <v>9990</v>
@@ -4110,7 +4110,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H129" t="n">
         <v>42756</v>
@@ -4139,7 +4139,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G131" t="n">
-        <v>2.50851988792419</v>
+        <v>2.50852036476135</v>
       </c>
       <c r="H131" t="n">
         <v>28801</v>
@@ -4226,7 +4226,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H133" t="n">
         <v>10690</v>
@@ -4313,7 +4313,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H136" t="n">
         <v>1076</v>
@@ -4342,7 +4342,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G137" t="n">
-        <v>2.45235872268677</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H137" t="n">
         <v>6677</v>
@@ -4429,7 +4429,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G140" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H140" t="n">
         <v>7419</v>
@@ -4458,7 +4458,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G141" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H141" t="n">
         <v>2000</v>
@@ -4516,7 +4516,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>2.5178804397583</v>
+        <v>2.51788020133972</v>
       </c>
       <c r="H143" t="n">
         <v>5968</v>
@@ -4545,7 +4545,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.50851988792419</v>
+        <v>2.50852036476135</v>
       </c>
       <c r="H144" t="n">
         <v>13613</v>
@@ -4574,7 +4574,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H145" t="n">
         <v>5650</v>
@@ -4603,7 +4603,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H146" t="n">
         <v>28110</v>
@@ -4748,7 +4748,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H151" t="n">
         <v>2337</v>
@@ -4777,7 +4777,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G152" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H152" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>2.43363904953003</v>
+        <v>2.43363833427429</v>
       </c>
       <c r="H154" t="n">
         <v>5575</v>
@@ -4864,7 +4864,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H155" t="n">
         <v>6961</v>
@@ -4922,7 +4922,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45235872268677</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H157" t="n">
         <v>5630</v>
@@ -4951,7 +4951,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H158" t="n">
         <v>4890</v>
@@ -4980,7 +4980,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G159" t="n">
-        <v>2.45235872268677</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H159" t="n">
         <v>960</v>
@@ -5009,7 +5009,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H160" t="n">
         <v>4282</v>
@@ -5067,7 +5067,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G162" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H162" t="n">
         <v>9630</v>
@@ -5096,7 +5096,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>2.45235872268677</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H163" t="n">
         <v>4386</v>
@@ -5125,7 +5125,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H164" t="n">
         <v>9227</v>
@@ -5154,7 +5154,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H165" t="n">
         <v>3840</v>
@@ -5270,7 +5270,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G169" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H169" t="n">
         <v>22</v>
@@ -5328,7 +5328,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H171" t="n">
         <v>27524</v>
@@ -5357,7 +5357,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H172" t="n">
         <v>7001</v>
@@ -5386,7 +5386,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G173" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H173" t="n">
         <v>77053</v>
@@ -5415,7 +5415,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H174" t="n">
         <v>13277</v>
@@ -5473,7 +5473,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G176" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H176" t="n">
         <v>27550</v>
@@ -5560,7 +5560,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G179" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H179" t="n">
         <v>11740</v>
@@ -5647,7 +5647,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G182" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H182" t="n">
         <v>3080</v>
@@ -5676,7 +5676,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G183" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H183" t="n">
         <v>8900</v>
@@ -5763,7 +5763,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H186" t="n">
         <v>14434</v>
@@ -5792,7 +5792,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G187" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H187" t="n">
         <v>2702</v>
@@ -5821,7 +5821,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G188" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H188" t="n">
         <v>3100</v>
@@ -5879,7 +5879,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H190" t="n">
         <v>4060</v>
@@ -5908,7 +5908,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G193" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H193" t="n">
         <v>3661</v>
@@ -6024,7 +6024,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H195" t="n">
         <v>4023</v>
@@ -6082,7 +6082,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G197" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H197" t="n">
         <v>16440</v>
@@ -6140,7 +6140,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H199" t="n">
         <v>7762</v>
@@ -6169,7 +6169,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H200" t="n">
         <v>16425</v>
@@ -6198,7 +6198,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G201" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H201" t="n">
         <v>4361</v>
@@ -6285,7 +6285,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H204" t="n">
         <v>18189</v>
@@ -6401,7 +6401,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H208" t="n">
         <v>60253</v>
@@ -6459,7 +6459,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>2.43363904953003</v>
+        <v>2.43363833427429</v>
       </c>
       <c r="H210" t="n">
         <v>9053</v>
@@ -6488,7 +6488,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>2.43363904953003</v>
+        <v>2.43363833427429</v>
       </c>
       <c r="H211" t="n">
         <v>10871</v>
@@ -6517,7 +6517,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>2.45235872268677</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H212" t="n">
         <v>9809</v>
@@ -6575,7 +6575,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H214" t="n">
         <v>20579</v>
@@ -6662,7 +6662,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H217" t="n">
         <v>40160</v>
@@ -6720,7 +6720,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G219" t="n">
-        <v>2.47107982635498</v>
+        <v>2.4710795879364</v>
       </c>
       <c r="H219" t="n">
         <v>9098</v>
@@ -6836,7 +6836,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G223" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H223" t="n">
         <v>22256</v>
@@ -7010,7 +7010,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>2.18091511726379</v>
+        <v>2.18091487884521</v>
       </c>
       <c r="H229" t="n">
         <v>20208</v>
@@ -7068,7 +7068,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>2.18091511726379</v>
+        <v>2.18091487884521</v>
       </c>
       <c r="H231" t="n">
         <v>3460</v>
@@ -7213,7 +7213,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G236" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H236" t="n">
         <v>12937</v>
@@ -7271,7 +7271,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>2.21835565567017</v>
+        <v>2.21835541725159</v>
       </c>
       <c r="H238" t="n">
         <v>4362</v>
@@ -7358,7 +7358,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H241" t="n">
         <v>6461</v>
@@ -7387,7 +7387,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G242" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H242" t="n">
         <v>2205</v>
@@ -7445,7 +7445,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G244" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H244" t="n">
         <v>13001</v>
@@ -7474,7 +7474,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G245" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H245" t="n">
         <v>11500</v>
@@ -7561,7 +7561,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H248" t="n">
         <v>8700</v>
@@ -7590,7 +7590,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H249" t="n">
         <v>9734</v>
@@ -7619,7 +7619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H250" t="n">
         <v>2000</v>
@@ -7648,7 +7648,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H251" t="n">
         <v>8381</v>
@@ -7677,7 +7677,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G252" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H252" t="n">
         <v>11500</v>
@@ -7706,7 +7706,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H253" t="n">
         <v>13809</v>
@@ -7880,7 +7880,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G259" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H259" t="n">
         <v>14470</v>
@@ -7996,7 +7996,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H263" t="n">
         <v>28276</v>
@@ -8025,7 +8025,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H264" t="n">
         <v>2500</v>
@@ -8112,7 +8112,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H267" t="n">
         <v>506</v>
@@ -8141,7 +8141,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H268" t="n">
         <v>293</v>
@@ -8199,7 +8199,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H270" t="n">
         <v>22</v>
@@ -8257,7 +8257,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G272" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H272" t="n">
         <v>14153</v>
@@ -8286,7 +8286,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H273" t="n">
         <v>9312</v>
@@ -8344,7 +8344,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H275" t="n">
         <v>50736</v>
@@ -8373,7 +8373,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G276" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H276" t="n">
         <v>100</v>
@@ -8402,7 +8402,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H277" t="n">
         <v>51182</v>
@@ -8431,7 +8431,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G278" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H278" t="n">
         <v>47465</v>
@@ -8460,7 +8460,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H279" t="n">
         <v>6401</v>
@@ -8489,7 +8489,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H280" t="n">
         <v>29015</v>
@@ -8518,7 +8518,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H281" t="n">
         <v>16267</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H282" t="n">
         <v>2810</v>
@@ -8576,7 +8576,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H283" t="n">
         <v>800</v>
@@ -8663,7 +8663,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G286" t="n">
-        <v>2.17155480384827</v>
+        <v>2.17155456542969</v>
       </c>
       <c r="H286" t="n">
         <v>19722</v>
@@ -8692,7 +8692,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>2.14347410202026</v>
+        <v>2.14347434043884</v>
       </c>
       <c r="H287" t="n">
         <v>17670</v>
@@ -8750,7 +8750,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G289" t="n">
-        <v>2.04051280021667</v>
+        <v>2.04051303863525</v>
       </c>
       <c r="H289" t="n">
         <v>300073</v>
@@ -8779,7 +8779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>1.94691097736359</v>
+        <v>1.94691121578217</v>
       </c>
       <c r="H290" t="n">
         <v>57032</v>
@@ -8924,7 +8924,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H295" t="n">
         <v>19268</v>
@@ -8953,7 +8953,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H296" t="n">
         <v>86437</v>
@@ -9011,7 +9011,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H298" t="n">
         <v>43668</v>
@@ -9069,7 +9069,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H300" t="n">
         <v>22505</v>
@@ -9098,7 +9098,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.16219425201416</v>
+        <v>2.16219449043274</v>
       </c>
       <c r="H304" t="n">
         <v>41725</v>
@@ -9214,7 +9214,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G305" t="n">
-        <v>2.17155480384827</v>
+        <v>2.17155456542969</v>
       </c>
       <c r="H305" t="n">
         <v>9053</v>
@@ -9243,7 +9243,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H306" t="n">
         <v>199531</v>
@@ -9272,7 +9272,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H307" t="n">
         <v>81352</v>
@@ -9301,7 +9301,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H308" t="n">
         <v>64204</v>
@@ -9330,7 +9330,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H309" t="n">
         <v>33763</v>
@@ -9388,7 +9388,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H311" t="n">
         <v>10160</v>
@@ -9417,7 +9417,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H312" t="n">
         <v>26681</v>
@@ -9446,7 +9446,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H313" t="n">
         <v>7193</v>
@@ -9475,7 +9475,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H314" t="n">
         <v>8050</v>
@@ -9533,7 +9533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H316" t="n">
         <v>750</v>
@@ -9620,7 +9620,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G319" t="n">
-        <v>2.16219425201416</v>
+        <v>2.16219449043274</v>
       </c>
       <c r="H319" t="n">
         <v>18946</v>
@@ -9649,7 +9649,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G320" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H320" t="n">
         <v>47122</v>
@@ -9678,7 +9678,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H321" t="n">
         <v>18454</v>
@@ -9765,7 +9765,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H324" t="n">
         <v>30211</v>
@@ -9794,7 +9794,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H325" t="n">
         <v>98214</v>
@@ -9939,7 +9939,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H330" t="n">
         <v>29880</v>
@@ -9968,7 +9968,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H331" t="n">
         <v>106731</v>
@@ -9997,7 +9997,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G332" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H332" t="n">
         <v>24459</v>
@@ -10026,7 +10026,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H333" t="n">
         <v>27881</v>
@@ -10113,7 +10113,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G336" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H336" t="n">
         <v>7485</v>
@@ -10142,7 +10142,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G337" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H337" t="n">
         <v>11056</v>
@@ -10287,7 +10287,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H342" t="n">
         <v>74958</v>
@@ -10316,7 +10316,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>2.43363904953003</v>
+        <v>2.43363833427429</v>
       </c>
       <c r="H343" t="n">
         <v>108400</v>
@@ -10345,7 +10345,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H350" t="n">
         <v>7329</v>
@@ -10577,7 +10577,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H352" t="n">
         <v>8959</v>
@@ -10664,7 +10664,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G355" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H355" t="n">
         <v>513</v>
@@ -10693,7 +10693,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G356" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H356" t="n">
         <v>8330</v>
@@ -10722,7 +10722,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G357" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H357" t="n">
         <v>38546</v>
@@ -10751,7 +10751,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H358" t="n">
         <v>3050</v>
@@ -10809,7 +10809,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H360" t="n">
         <v>55919</v>
@@ -10896,7 +10896,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H363" t="n">
         <v>11900</v>
@@ -10983,7 +10983,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G366" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H366" t="n">
         <v>4177</v>
@@ -11012,7 +11012,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H367" t="n">
         <v>11034</v>
@@ -11070,7 +11070,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>2.21835565567017</v>
+        <v>2.21835541725159</v>
       </c>
       <c r="H369" t="n">
         <v>36923</v>
@@ -11099,7 +11099,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G370" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H371" t="n">
         <v>2249</v>
@@ -11157,7 +11157,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H372" t="n">
         <v>1750</v>
@@ -11186,7 +11186,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H376" t="n">
         <v>4839</v>
@@ -11447,7 +11447,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G382" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H382" t="n">
         <v>4930</v>
@@ -11476,7 +11476,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H386" t="n">
         <v>6018</v>
@@ -11592,7 +11592,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H387" t="n">
         <v>7512</v>
@@ -11621,7 +11621,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H388" t="n">
         <v>574</v>
@@ -11650,7 +11650,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G389" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H389" t="n">
         <v>5471</v>
@@ -11679,7 +11679,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H392" t="n">
         <v>14885</v>
@@ -11795,7 +11795,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G394" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -11824,7 +11824,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G395" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H395" t="n">
         <v>37806</v>
@@ -11853,7 +11853,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G396" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H396" t="n">
         <v>11394</v>
@@ -11882,7 +11882,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G397" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H397" t="n">
         <v>27047</v>
@@ -11911,7 +11911,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H398" t="n">
         <v>46985</v>
@@ -11940,7 +11940,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G399" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H399" t="n">
         <v>30870</v>
@@ -11969,7 +11969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G400" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H400" t="n">
         <v>38756</v>
@@ -12201,7 +12201,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H408" t="n">
         <v>3100</v>
@@ -12230,7 +12230,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H409" t="n">
         <v>2100</v>
@@ -12259,7 +12259,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H410" t="n">
         <v>24738</v>
@@ -12404,7 +12404,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G415" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H415" t="n">
         <v>25926</v>
@@ -12433,7 +12433,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G416" t="n">
-        <v>2.24643611907959</v>
+        <v>2.24643588066101</v>
       </c>
       <c r="H416" t="n">
         <v>6504</v>
@@ -12462,7 +12462,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G417" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H417" t="n">
         <v>2000</v>
@@ -12491,7 +12491,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G418" t="n">
-        <v>2.27451658248901</v>
+        <v>2.27451634407043</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H419" t="n">
         <v>56944</v>
@@ -12549,7 +12549,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G420" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H420" t="n">
         <v>111514</v>
@@ -12578,7 +12578,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G421" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H421" t="n">
         <v>45993</v>
@@ -12607,7 +12607,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H422" t="n">
         <v>108321</v>
@@ -12636,7 +12636,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G423" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H423" t="n">
         <v>11481</v>
@@ -12694,7 +12694,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.45235872268677</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H425" t="n">
         <v>151198</v>
@@ -12723,7 +12723,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G426" t="n">
-        <v>2.43363904953003</v>
+        <v>2.43363833427429</v>
       </c>
       <c r="H426" t="n">
         <v>228749</v>
@@ -12781,7 +12781,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H428" t="n">
         <v>27357</v>
@@ -12810,7 +12810,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G429" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H429" t="n">
         <v>86914</v>
@@ -12839,7 +12839,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G430" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H430" t="n">
         <v>11999</v>
@@ -12868,7 +12868,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G431" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H431" t="n">
         <v>5751</v>
@@ -12897,7 +12897,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G432" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H432" t="n">
         <v>13150</v>
@@ -12955,7 +12955,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H434" t="n">
         <v>1252</v>
@@ -12984,7 +12984,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H436" t="n">
         <v>3254</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G438" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.23707604408264</v>
+        <v>2.23707556724548</v>
       </c>
       <c r="H439" t="n">
         <v>4275</v>
@@ -13245,7 +13245,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G444" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H444" t="n">
         <v>12469</v>
@@ -13274,7 +13274,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.31195688247681</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H445" t="n">
         <v>531</v>
@@ -13361,7 +13361,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H448" t="n">
         <v>1564637</v>
@@ -13390,7 +13390,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G449" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H449" t="n">
         <v>142747</v>
@@ -13419,7 +13419,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G450" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H450" t="n">
         <v>23918</v>
@@ -13448,7 +13448,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G451" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H451" t="n">
         <v>25684</v>
@@ -13564,7 +13564,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G455" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H455" t="n">
         <v>148756</v>
@@ -13622,7 +13622,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H457" t="n">
         <v>2289</v>
@@ -13651,7 +13651,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H458" t="n">
         <v>1000</v>
@@ -13709,7 +13709,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>2.30259728431702</v>
+        <v>2.30259704589844</v>
       </c>
       <c r="H460" t="n">
         <v>914</v>
@@ -13738,7 +13738,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G461" t="n">
-        <v>2.29323697090149</v>
+        <v>2.29323649406433</v>
       </c>
       <c r="H461" t="n">
         <v>1250</v>
@@ -13767,7 +13767,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G462" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H462" t="n">
         <v>16580</v>
@@ -13796,7 +13796,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H463" t="n">
         <v>33833</v>
@@ -13825,7 +13825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G464" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H464" t="n">
         <v>15150</v>
@@ -13941,7 +13941,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G468" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H468" t="n">
         <v>44500</v>
@@ -13970,7 +13970,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H469" t="n">
         <v>30332</v>
@@ -14057,7 +14057,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H472" t="n">
         <v>16025</v>
@@ -14086,7 +14086,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H473" t="n">
         <v>6086</v>
@@ -14115,7 +14115,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G474" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H474" t="n">
         <v>15848</v>
@@ -14144,7 +14144,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H475" t="n">
         <v>10000</v>
@@ -14173,7 +14173,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G476" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H476" t="n">
         <v>10200</v>
@@ -14231,7 +14231,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G478" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H478" t="n">
         <v>22406</v>
@@ -14260,7 +14260,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G479" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H479" t="n">
         <v>5137</v>
@@ -14318,7 +14318,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H481" t="n">
         <v>6871</v>
@@ -14347,7 +14347,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>2.36811780929565</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H483" t="n">
         <v>2700</v>
@@ -14434,7 +14434,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.34939765930176</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H485" t="n">
         <v>5500</v>
@@ -14492,7 +14492,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G487" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H487" t="n">
         <v>7565</v>
@@ -14521,7 +14521,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H488" t="n">
         <v>67898</v>
@@ -14579,7 +14579,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G490" t="n">
-        <v>2.33067727088928</v>
+        <v>2.33067750930786</v>
       </c>
       <c r="H490" t="n">
         <v>7202</v>
@@ -14608,7 +14608,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H491" t="n">
         <v>8000</v>
@@ -14637,7 +14637,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.37747812271118</v>
+        <v>2.37747836112976</v>
       </c>
       <c r="H493" t="n">
         <v>8491</v>
@@ -14724,7 +14724,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G495" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H495" t="n">
         <v>38256</v>
@@ -14753,7 +14753,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G496" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H496" t="n">
         <v>5000</v>
@@ -14782,7 +14782,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G497" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H497" t="n">
         <v>26080</v>
@@ -14811,7 +14811,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>2.3961980342865</v>
+        <v>2.39619851112366</v>
       </c>
       <c r="H498" t="n">
         <v>11600</v>
@@ -14869,7 +14869,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G500" t="n">
-        <v>2.52724075317383</v>
+        <v>2.52724051475525</v>
       </c>
       <c r="H500" t="n">
         <v>107378</v>
@@ -14927,7 +14927,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G502" t="n">
-        <v>2.52724075317383</v>
+        <v>2.52724051475525</v>
       </c>
       <c r="H502" t="n">
         <v>90321</v>
@@ -14956,7 +14956,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>2.55532097816467</v>
+        <v>2.55532073974609</v>
       </c>
       <c r="H503" t="n">
         <v>11558</v>
@@ -15014,7 +15014,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G505" t="n">
-        <v>2.55532097816467</v>
+        <v>2.55532073974609</v>
       </c>
       <c r="H505" t="n">
         <v>81185</v>
@@ -15043,7 +15043,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G506" t="n">
-        <v>2.55532097816467</v>
+        <v>2.55532073974609</v>
       </c>
       <c r="H506" t="n">
         <v>35190</v>
@@ -15072,7 +15072,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G507" t="n">
-        <v>2.56468105316162</v>
+        <v>2.5646812915802</v>
       </c>
       <c r="H507" t="n">
         <v>60564</v>
@@ -15101,7 +15101,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>2.60212182998657</v>
+        <v>2.60212135314941</v>
       </c>
       <c r="H508" t="n">
         <v>22510</v>
@@ -15130,7 +15130,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G509" t="n">
-        <v>2.63020205497742</v>
+        <v>2.630202293396</v>
       </c>
       <c r="H509" t="n">
         <v>64049</v>
@@ -15246,7 +15246,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>2.78932452201843</v>
+        <v>2.78932476043701</v>
       </c>
       <c r="H513" t="n">
         <v>169395</v>
@@ -15275,7 +15275,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.78932452201843</v>
+        <v>2.78932476043701</v>
       </c>
       <c r="H514" t="n">
         <v>62277</v>
@@ -15304,7 +15304,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>2.78932452201843</v>
+        <v>2.78932476043701</v>
       </c>
       <c r="H515" t="n">
         <v>19300</v>
@@ -15333,7 +15333,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G516" t="n">
-        <v>2.77996420860291</v>
+        <v>2.77996444702148</v>
       </c>
       <c r="H516" t="n">
         <v>5400</v>
@@ -15362,7 +15362,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.77996420860291</v>
+        <v>2.77996444702148</v>
       </c>
       <c r="H517" t="n">
         <v>54995</v>
@@ -15391,7 +15391,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.77996420860291</v>
+        <v>2.77996444702148</v>
       </c>
       <c r="H518" t="n">
         <v>46424</v>
@@ -15420,7 +15420,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.77996420860291</v>
+        <v>2.77996444702148</v>
       </c>
       <c r="H519" t="n">
         <v>15753</v>
@@ -15449,7 +15449,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>2.78932452201843</v>
+        <v>2.78932476043701</v>
       </c>
       <c r="H520" t="n">
         <v>190831</v>
@@ -15478,7 +15478,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>2.79868483543396</v>
+        <v>2.79868507385254</v>
       </c>
       <c r="H521" t="n">
         <v>45690</v>
@@ -15623,7 +15623,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.79868483543396</v>
+        <v>2.79868507385254</v>
       </c>
       <c r="H526" t="n">
         <v>84209</v>
@@ -15826,7 +15826,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G533" t="n">
-        <v>2.82676553726196</v>
+        <v>2.82676529884338</v>
       </c>
       <c r="H533" t="n">
         <v>54489</v>
@@ -15855,7 +15855,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G534" t="n">
-        <v>2.91100645065308</v>
+        <v>2.91100692749023</v>
       </c>
       <c r="H534" t="n">
         <v>92567</v>
@@ -16000,7 +16000,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>3.0794894695282</v>
+        <v>3.07948923110962</v>
       </c>
       <c r="H539" t="n">
         <v>1328039</v>
@@ -16116,7 +16116,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>3.02332878112793</v>
+        <v>3.02332830429077</v>
       </c>
       <c r="H543" t="n">
         <v>44507</v>
@@ -16261,7 +16261,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>2.92036652565002</v>
+        <v>2.9203667640686</v>
       </c>
       <c r="H548" t="n">
         <v>203116</v>
@@ -16435,7 +16435,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G554" t="n">
-        <v>2.92036652565002</v>
+        <v>2.9203667640686</v>
       </c>
       <c r="H554" t="n">
         <v>80665</v>
@@ -16580,7 +16580,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.86420559883118</v>
+        <v>2.86420583724976</v>
       </c>
       <c r="H559" t="n">
         <v>120717</v>
@@ -16609,7 +16609,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G560" t="n">
-        <v>2.92036652565002</v>
+        <v>2.9203667640686</v>
       </c>
       <c r="H560" t="n">
         <v>113199</v>
@@ -16696,7 +16696,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>2.88292622566223</v>
+        <v>2.88292598724365</v>
       </c>
       <c r="H563" t="n">
         <v>112305</v>
@@ -16899,7 +16899,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>2.78932452201843</v>
+        <v>2.78932476043701</v>
       </c>
       <c r="H570" t="n">
         <v>78096</v>
@@ -16928,7 +16928,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G571" t="n">
-        <v>2.90164613723755</v>
+        <v>2.90164637565613</v>
       </c>
       <c r="H571" t="n">
         <v>199785</v>
@@ -17015,7 +17015,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G574" t="n">
-        <v>3.11692953109741</v>
+        <v>3.11693000793457</v>
       </c>
       <c r="H574" t="n">
         <v>360144</v>
@@ -17044,7 +17044,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G575" t="n">
-        <v>3.28541254997253</v>
+        <v>3.28541278839111</v>
       </c>
       <c r="H575" t="n">
         <v>655278</v>
@@ -17073,7 +17073,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G576" t="n">
-        <v>3.33221340179443</v>
+        <v>3.33221364021301</v>
       </c>
       <c r="H576" t="n">
         <v>274523</v>
@@ -17160,7 +17160,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G579" t="n">
-        <v>3.39773416519165</v>
+        <v>3.39773440361023</v>
       </c>
       <c r="H579" t="n">
         <v>74160</v>
@@ -17363,7 +17363,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G586" t="n">
-        <v>3.42581462860107</v>
+        <v>3.42581534385681</v>
       </c>
       <c r="H586" t="n">
         <v>29415</v>
@@ -17450,7 +17450,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G589" t="n">
-        <v>3.38837432861328</v>
+        <v>3.38837385177612</v>
       </c>
       <c r="H589" t="n">
         <v>37431</v>
@@ -17508,7 +17508,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G591" t="n">
-        <v>3.38837432861328</v>
+        <v>3.38837385177612</v>
       </c>
       <c r="H591" t="n">
         <v>140103</v>
@@ -17537,7 +17537,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>3.38837432861328</v>
+        <v>3.38837385177612</v>
       </c>
       <c r="H592" t="n">
         <v>48927</v>
@@ -17595,7 +17595,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>3.37901377677917</v>
+        <v>3.37901401519775</v>
       </c>
       <c r="H594" t="n">
         <v>41694</v>
@@ -17653,7 +17653,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67853927612305</v>
+        <v>3.67853879928589</v>
       </c>
       <c r="H596" t="n">
         <v>60272</v>
@@ -17682,7 +17682,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>3.70661926269531</v>
+        <v>3.70661950111389</v>
       </c>
       <c r="H597" t="n">
         <v>36651</v>
@@ -17711,7 +17711,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G598" t="n">
-        <v>3.55685710906982</v>
+        <v>3.55685663223267</v>
       </c>
       <c r="H598" t="n">
         <v>19889</v>
@@ -17740,7 +17740,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G599" t="n">
-        <v>3.57557678222656</v>
+        <v>3.57557702064514</v>
       </c>
       <c r="H599" t="n">
         <v>37016</v>
@@ -17798,7 +17798,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>3.63173818588257</v>
+        <v>3.63173842430115</v>
       </c>
       <c r="H601" t="n">
         <v>91801</v>
@@ -17827,7 +17827,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G602" t="n">
-        <v>3.53813672065735</v>
+        <v>3.53813648223877</v>
       </c>
       <c r="H602" t="n">
         <v>26633</v>
@@ -17885,7 +17885,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.53813672065735</v>
+        <v>3.53813648223877</v>
       </c>
       <c r="H604" t="n">
         <v>8079</v>
@@ -18088,7 +18088,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G611" t="n">
-        <v>3.5006959438324</v>
+        <v>3.50069570541382</v>
       </c>
       <c r="H611" t="n">
         <v>8068</v>
@@ -18117,7 +18117,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>3.38837432861328</v>
+        <v>3.38837385177612</v>
       </c>
       <c r="H612" t="n">
         <v>29302</v>
@@ -18233,7 +18233,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>3.3415732383728</v>
+        <v>3.34157347679138</v>
       </c>
       <c r="H616" t="n">
         <v>39898</v>
@@ -18262,7 +18262,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.60365772247314</v>
+        <v>3.60365796089172</v>
       </c>
       <c r="H617" t="n">
         <v>129761</v>
@@ -18291,7 +18291,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>3.6691792011261</v>
+        <v>3.66917872428894</v>
       </c>
       <c r="H618" t="n">
         <v>33184</v>
@@ -18378,7 +18378,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G621" t="n">
-        <v>3.57557678222656</v>
+        <v>3.57557702064514</v>
       </c>
       <c r="H621" t="n">
         <v>1414</v>
@@ -18407,7 +18407,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.5006959438324</v>
+        <v>3.50069570541382</v>
       </c>
       <c r="H622" t="n">
         <v>38669</v>
@@ -18465,7 +18465,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>3.38837432861328</v>
+        <v>3.38837385177612</v>
       </c>
       <c r="H624" t="n">
         <v>8687</v>
@@ -18494,7 +18494,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>3.39773416519165</v>
+        <v>3.39773440361023</v>
       </c>
       <c r="H625" t="n">
         <v>16296</v>
@@ -18552,7 +18552,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G627" t="n">
-        <v>3.37901377677917</v>
+        <v>3.37901401519775</v>
       </c>
       <c r="H627" t="n">
         <v>48267</v>
@@ -18610,7 +18610,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.39773416519165</v>
+        <v>3.39773440361023</v>
       </c>
       <c r="H629" t="n">
         <v>2495</v>
@@ -18639,7 +18639,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G630" t="n">
-        <v>3.33221340179443</v>
+        <v>3.33221364021301</v>
       </c>
       <c r="H630" t="n">
         <v>10750</v>
@@ -18668,7 +18668,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G631" t="n">
-        <v>3.37901377677917</v>
+        <v>3.37901401519775</v>
       </c>
       <c r="H631" t="n">
         <v>27218</v>
@@ -18697,7 +18697,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>3.36029386520386</v>
+        <v>3.36029362678528</v>
       </c>
       <c r="H632" t="n">
         <v>12645</v>
@@ -18755,7 +18755,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G634" t="n">
-        <v>3.19181132316589</v>
+        <v>3.19181084632874</v>
       </c>
       <c r="H634" t="n">
         <v>67053</v>
@@ -18813,7 +18813,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G636" t="n">
-        <v>3.39773416519165</v>
+        <v>3.39773440361023</v>
       </c>
       <c r="H636" t="n">
         <v>36700</v>
@@ -18842,7 +18842,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>3.32285308837891</v>
+        <v>3.32285284996033</v>
       </c>
       <c r="H637" t="n">
         <v>23665</v>
@@ -18871,7 +18871,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G638" t="n">
-        <v>3.19181132316589</v>
+        <v>3.19181084632874</v>
       </c>
       <c r="H638" t="n">
         <v>19469</v>
@@ -18900,7 +18900,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G639" t="n">
-        <v>3.13565039634705</v>
+        <v>3.13564991950989</v>
       </c>
       <c r="H639" t="n">
         <v>7237</v>
@@ -18929,7 +18929,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.12628984451294</v>
+        <v>3.12628960609436</v>
       </c>
       <c r="H640" t="n">
         <v>8567</v>
@@ -18958,7 +18958,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>3.11692953109741</v>
+        <v>3.11693000793457</v>
       </c>
       <c r="H641" t="n">
         <v>42079</v>
@@ -18987,7 +18987,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.90164613723755</v>
+        <v>2.90164637565613</v>
       </c>
       <c r="H642" t="n">
         <v>47794</v>
@@ -19016,7 +19016,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G643" t="n">
-        <v>2.79868483543396</v>
+        <v>2.79868507385254</v>
       </c>
       <c r="H643" t="n">
         <v>69535</v>
@@ -19045,7 +19045,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>2.77996420860291</v>
+        <v>2.77996444702148</v>
       </c>
       <c r="H644" t="n">
         <v>61775</v>
@@ -19074,7 +19074,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.88292622566223</v>
+        <v>2.88292598724365</v>
       </c>
       <c r="H645" t="n">
         <v>11231</v>
@@ -19103,7 +19103,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>2.5366005897522</v>
+        <v>2.53660106658936</v>
       </c>
       <c r="H646" t="n">
         <v>3417</v>
@@ -19132,7 +19132,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G647" t="n">
-        <v>2.77996420860291</v>
+        <v>2.77996444702148</v>
       </c>
       <c r="H647" t="n">
         <v>55943</v>
@@ -19161,7 +19161,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>2.90164613723755</v>
+        <v>2.90164637565613</v>
       </c>
       <c r="H648" t="n">
         <v>34907</v>
@@ -19422,7 +19422,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G657" t="n">
-        <v>3.22925138473511</v>
+        <v>3.22925186157227</v>
       </c>
       <c r="H657" t="n">
         <v>36711</v>
@@ -19480,7 +19480,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>3.32285308837891</v>
+        <v>3.32285284996033</v>
       </c>
       <c r="H659" t="n">
         <v>65715</v>
@@ -19828,7 +19828,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G671" t="n">
-        <v>3.39773416519165</v>
+        <v>3.39773440361023</v>
       </c>
       <c r="H671" t="n">
         <v>48966</v>
@@ -20002,7 +20002,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G677" t="n">
-        <v>3.55685710906982</v>
+        <v>3.55685663223267</v>
       </c>
       <c r="H677" t="n">
         <v>74533</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.63173818588257</v>
+        <v>3.63173842430115</v>
       </c>
       <c r="H679" t="n">
         <v>81544</v>
@@ -20147,7 +20147,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>3.58493733406067</v>
+        <v>3.58493709564209</v>
       </c>
       <c r="H682" t="n">
         <v>5278</v>
@@ -20176,7 +20176,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>3.5006959438324</v>
+        <v>3.50069570541382</v>
       </c>
       <c r="H683" t="n">
         <v>8721</v>
@@ -20292,7 +20292,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>3.60365772247314</v>
+        <v>3.60365796089172</v>
       </c>
       <c r="H687" t="n">
         <v>87568</v>
@@ -20321,7 +20321,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G688" t="n">
-        <v>3.55685710906982</v>
+        <v>3.55685663223267</v>
       </c>
       <c r="H688" t="n">
         <v>193567</v>
@@ -20350,7 +20350,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>3.53813672065735</v>
+        <v>3.53813648223877</v>
       </c>
       <c r="H689" t="n">
         <v>157462</v>
@@ -20379,7 +20379,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>3.60365772247314</v>
+        <v>3.60365796089172</v>
       </c>
       <c r="H690" t="n">
         <v>390324</v>
@@ -20408,7 +20408,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G691" t="n">
-        <v>3.37901377677917</v>
+        <v>3.37901401519775</v>
       </c>
       <c r="H691" t="n">
         <v>736934</v>
@@ -20437,7 +20437,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.33221340179443</v>
+        <v>3.33221364021301</v>
       </c>
       <c r="H692" t="n">
         <v>140706</v>
@@ -20495,7 +20495,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G694" t="n">
-        <v>3.14501047134399</v>
+        <v>3.14501023292542</v>
       </c>
       <c r="H694" t="n">
         <v>536273</v>
@@ -20524,7 +20524,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>3.13565039634705</v>
+        <v>3.13564991950989</v>
       </c>
       <c r="H695" t="n">
         <v>55970</v>
@@ -20553,7 +20553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>3.03268837928772</v>
+        <v>3.0326886177063</v>
       </c>
       <c r="H696" t="n">
         <v>83216</v>
@@ -20582,7 +20582,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G697" t="n">
-        <v>2.98588752746582</v>
+        <v>2.9858877658844</v>
       </c>
       <c r="H697" t="n">
         <v>74009</v>
@@ -20640,7 +20640,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>3.17309069633484</v>
+        <v>3.17309093475342</v>
       </c>
       <c r="H699" t="n">
         <v>657362</v>
@@ -20698,7 +20698,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G701" t="n">
-        <v>3.19181132316589</v>
+        <v>3.19181084632874</v>
       </c>
       <c r="H701" t="n">
         <v>3413</v>
@@ -20756,7 +20756,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.16373085975647</v>
+        <v>3.16373109817505</v>
       </c>
       <c r="H703" t="n">
         <v>78089</v>
@@ -20785,7 +20785,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G704" t="n">
-        <v>3.21053123474121</v>
+        <v>3.21053147315979</v>
       </c>
       <c r="H704" t="n">
         <v>122552</v>
@@ -20814,7 +20814,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G705" t="n">
-        <v>3.21053123474121</v>
+        <v>3.21053147315979</v>
       </c>
       <c r="H705" t="n">
         <v>82607</v>
@@ -20843,7 +20843,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G706" t="n">
-        <v>3.21053123474121</v>
+        <v>3.21053147315979</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>3.11692953109741</v>
+        <v>3.11693000793457</v>
       </c>
       <c r="H707" t="n">
         <v>52725</v>
@@ -20901,7 +20901,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.98588752746582</v>
+        <v>2.9858877658844</v>
       </c>
       <c r="H708" t="n">
         <v>81677</v>
@@ -20930,7 +20930,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>2.94844746589661</v>
+        <v>2.94844722747803</v>
       </c>
       <c r="H709" t="n">
         <v>51596</v>
@@ -21075,7 +21075,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>3.13565039634705</v>
+        <v>3.13564991950989</v>
       </c>
       <c r="H714" t="n">
         <v>382455</v>
@@ -21133,7 +21133,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>3.25088334083557</v>
+        <v>3.25088310241699</v>
       </c>
       <c r="H716" t="n">
         <v>82513</v>
@@ -21191,7 +21191,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G718" t="n">
-        <v>3.17593455314636</v>
+        <v>3.1759352684021</v>
       </c>
       <c r="H718" t="n">
         <v>25259</v>
@@ -21220,7 +21220,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G719" t="n">
-        <v>3.19467210769653</v>
+        <v>3.19467163085938</v>
       </c>
       <c r="H719" t="n">
         <v>158462</v>
@@ -21249,7 +21249,7 @@
         <v>3.5</v>
       </c>
       <c r="G720" t="n">
-        <v>3.27898907661438</v>
+        <v>3.2789888381958</v>
       </c>
       <c r="H720" t="n">
         <v>36071</v>
@@ -21278,7 +21278,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G721" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H721" t="n">
         <v>91605</v>
@@ -21394,7 +21394,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G725" t="n">
-        <v>3.17593455314636</v>
+        <v>3.1759352684021</v>
       </c>
       <c r="H725" t="n">
         <v>13863</v>
@@ -21423,7 +21423,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>3.1665666103363</v>
+        <v>3.16656637191772</v>
       </c>
       <c r="H726" t="n">
         <v>2048</v>
@@ -21452,7 +21452,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>3.1197235584259</v>
+        <v>3.11972379684448</v>
       </c>
       <c r="H727" t="n">
         <v>6974</v>
@@ -21597,7 +21597,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G732" t="n">
-        <v>3.1665666103363</v>
+        <v>3.16656637191772</v>
       </c>
       <c r="H732" t="n">
         <v>19364</v>
@@ -21829,7 +21829,7 @@
         <v>3.5</v>
       </c>
       <c r="G740" t="n">
-        <v>3.27898907661438</v>
+        <v>3.2789888381958</v>
       </c>
       <c r="H740" t="n">
         <v>31325</v>
@@ -21916,7 +21916,7 @@
         <v>3.5</v>
       </c>
       <c r="G743" t="n">
-        <v>3.27898907661438</v>
+        <v>3.2789888381958</v>
       </c>
       <c r="H743" t="n">
         <v>62675</v>
@@ -21945,7 +21945,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H744" t="n">
         <v>454803</v>
@@ -21974,7 +21974,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G745" t="n">
-        <v>3.41951704025269</v>
+        <v>3.41951680183411</v>
       </c>
       <c r="H745" t="n">
         <v>33489</v>
@@ -22003,7 +22003,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G746" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H746" t="n">
         <v>45840</v>
@@ -22032,7 +22032,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G747" t="n">
-        <v>3.41014862060547</v>
+        <v>3.41014838218689</v>
       </c>
       <c r="H747" t="n">
         <v>493111</v>
@@ -22061,7 +22061,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H748" t="n">
         <v>75973</v>
@@ -22119,7 +22119,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H750" t="n">
         <v>5946</v>
@@ -22177,7 +22177,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G752" t="n">
-        <v>3.42888522148132</v>
+        <v>3.4288854598999</v>
       </c>
       <c r="H752" t="n">
         <v>24007</v>
@@ -22206,7 +22206,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>3.44762253761292</v>
+        <v>3.44762229919434</v>
       </c>
       <c r="H753" t="n">
         <v>52774</v>
@@ -22235,7 +22235,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H754" t="n">
         <v>58210</v>
@@ -22264,7 +22264,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H755" t="n">
         <v>13024</v>
@@ -22496,7 +22496,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G763" t="n">
-        <v>3.50383377075195</v>
+        <v>3.50383353233337</v>
       </c>
       <c r="H763" t="n">
         <v>29164</v>
@@ -22525,7 +22525,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G764" t="n">
-        <v>3.44762253761292</v>
+        <v>3.44762229919434</v>
       </c>
       <c r="H764" t="n">
         <v>66986</v>
@@ -22554,7 +22554,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G765" t="n">
-        <v>3.41951704025269</v>
+        <v>3.41951680183411</v>
       </c>
       <c r="H765" t="n">
         <v>34441</v>
@@ -22612,7 +22612,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G767" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H767" t="n">
         <v>56135</v>
@@ -22641,7 +22641,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G768" t="n">
-        <v>3.42888522148132</v>
+        <v>3.4288854598999</v>
       </c>
       <c r="H768" t="n">
         <v>13075</v>
@@ -22699,7 +22699,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G770" t="n">
-        <v>3.44762253761292</v>
+        <v>3.44762229919434</v>
       </c>
       <c r="H770" t="n">
         <v>6198</v>
@@ -22728,7 +22728,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>3.44762253761292</v>
+        <v>3.44762229919434</v>
       </c>
       <c r="H771" t="n">
         <v>27405</v>
@@ -22757,7 +22757,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G772" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H772" t="n">
         <v>4806</v>
@@ -22786,7 +22786,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G773" t="n">
-        <v>3.42888522148132</v>
+        <v>3.4288854598999</v>
       </c>
       <c r="H773" t="n">
         <v>98798</v>
@@ -22815,7 +22815,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H774" t="n">
         <v>27945</v>
@@ -22873,7 +22873,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H776" t="n">
         <v>55090</v>
@@ -22902,7 +22902,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H777" t="n">
         <v>8145</v>
@@ -22931,7 +22931,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G778" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H778" t="n">
         <v>9116</v>
@@ -22960,7 +22960,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H779" t="n">
         <v>22658</v>
@@ -22989,7 +22989,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>3.41014862060547</v>
+        <v>3.41014838218689</v>
       </c>
       <c r="H780" t="n">
         <v>22131</v>
@@ -23018,7 +23018,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>3.35393691062927</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H781" t="n">
         <v>10208</v>
@@ -23047,7 +23047,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H782" t="n">
         <v>16574</v>
@@ -23076,7 +23076,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H783" t="n">
         <v>2367</v>
@@ -23105,7 +23105,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G784" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H784" t="n">
         <v>11723</v>
@@ -23134,7 +23134,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G785" t="n">
-        <v>3.41951704025269</v>
+        <v>3.41951680183411</v>
       </c>
       <c r="H785" t="n">
         <v>34035</v>
@@ -23221,7 +23221,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G788" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H788" t="n">
         <v>5065</v>
@@ -23250,7 +23250,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>3.35393691062927</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H789" t="n">
         <v>109072</v>
@@ -23279,7 +23279,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G790" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H790" t="n">
         <v>22544</v>
@@ -23337,7 +23337,7 @@
         <v>3.5</v>
       </c>
       <c r="G792" t="n">
-        <v>3.27898907661438</v>
+        <v>3.2789888381958</v>
       </c>
       <c r="H792" t="n">
         <v>3706</v>
@@ -23366,7 +23366,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G793" t="n">
-        <v>3.31646275520325</v>
+        <v>3.31646299362183</v>
       </c>
       <c r="H793" t="n">
         <v>35556</v>
@@ -23395,7 +23395,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G794" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H794" t="n">
         <v>8999</v>
@@ -23424,7 +23424,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G795" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H795" t="n">
         <v>14337</v>
@@ -23453,7 +23453,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G796" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H796" t="n">
         <v>38609</v>
@@ -23511,7 +23511,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G798" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H798" t="n">
         <v>8752</v>
@@ -23540,7 +23540,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.27898907661438</v>
+        <v>3.2789888381958</v>
       </c>
       <c r="H799" t="n">
         <v>16945</v>
@@ -23569,7 +23569,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H800" t="n">
         <v>10366</v>
@@ -23598,7 +23598,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G801" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H801" t="n">
         <v>1507</v>
@@ -23685,7 +23685,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H804" t="n">
         <v>134798</v>
@@ -23743,7 +23743,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.41951704025269</v>
+        <v>3.41951680183411</v>
       </c>
       <c r="H806" t="n">
         <v>89100</v>
@@ -23830,7 +23830,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G809" t="n">
-        <v>3.41951704025269</v>
+        <v>3.41951680183411</v>
       </c>
       <c r="H809" t="n">
         <v>61251</v>
@@ -23859,7 +23859,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.41951704025269</v>
+        <v>3.41951680183411</v>
       </c>
       <c r="H810" t="n">
         <v>114614</v>
@@ -23917,7 +23917,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H812" t="n">
         <v>89318</v>
@@ -23946,7 +23946,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>3.35393691062927</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H813" t="n">
         <v>77134</v>
@@ -24004,7 +24004,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G815" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H815" t="n">
         <v>28620</v>
@@ -24033,7 +24033,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G816" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H816" t="n">
         <v>2317</v>
@@ -24062,7 +24062,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H817" t="n">
         <v>16389</v>
@@ -24091,7 +24091,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.35393691062927</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H818" t="n">
         <v>12874</v>
@@ -24120,7 +24120,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H819" t="n">
         <v>39306</v>
@@ -24149,7 +24149,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G820" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H820" t="n">
         <v>48384</v>
@@ -24207,7 +24207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G822" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H822" t="n">
         <v>17770</v>
@@ -24236,7 +24236,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H823" t="n">
         <v>70262</v>
@@ -24265,7 +24265,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H824" t="n">
         <v>15100</v>
@@ -24294,7 +24294,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H825" t="n">
         <v>32231</v>
@@ -24323,7 +24323,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H826" t="n">
         <v>37605</v>
@@ -24410,7 +24410,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.31646275520325</v>
+        <v>3.31646299362183</v>
       </c>
       <c r="H829" t="n">
         <v>6640</v>
@@ -24439,7 +24439,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G830" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H830" t="n">
         <v>48136</v>
@@ -24468,7 +24468,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G831" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H831" t="n">
         <v>7251</v>
@@ -24497,7 +24497,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G832" t="n">
-        <v>3.37267374992371</v>
+        <v>3.37267398834229</v>
       </c>
       <c r="H832" t="n">
         <v>17409</v>
@@ -24555,7 +24555,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G834" t="n">
-        <v>3.36330580711365</v>
+        <v>3.36330533027649</v>
       </c>
       <c r="H834" t="n">
         <v>12149</v>
@@ -24584,7 +24584,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H835" t="n">
         <v>4670</v>
@@ -24613,7 +24613,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>3.35393691062927</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H836" t="n">
         <v>41</v>
@@ -24642,7 +24642,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G837" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H837" t="n">
         <v>6979</v>
@@ -24671,7 +24671,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H838" t="n">
         <v>6632</v>
@@ -24700,7 +24700,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>3.35393691062927</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H839" t="n">
         <v>1914</v>
@@ -24729,7 +24729,7 @@
         <v>3.5</v>
       </c>
       <c r="G840" t="n">
-        <v>3.27898907661438</v>
+        <v>3.2789888381958</v>
       </c>
       <c r="H840" t="n">
         <v>43854</v>
@@ -24758,7 +24758,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>3.31646275520325</v>
+        <v>3.31646299362183</v>
       </c>
       <c r="H841" t="n">
         <v>15368</v>
@@ -24787,7 +24787,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G842" t="n">
-        <v>3.32583165168762</v>
+        <v>3.32583141326904</v>
       </c>
       <c r="H842" t="n">
         <v>45487</v>
@@ -24845,7 +24845,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G844" t="n">
-        <v>3.21340894699097</v>
+        <v>3.21340918540955</v>
       </c>
       <c r="H844" t="n">
         <v>116420</v>
@@ -24874,7 +24874,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G845" t="n">
-        <v>3.41951704025269</v>
+        <v>3.41951680183411</v>
       </c>
       <c r="H845" t="n">
         <v>60753</v>
@@ -24903,7 +24903,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>3.35393691062927</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H846" t="n">
         <v>37415</v>
@@ -24932,7 +24932,7 @@
         <v>3.5</v>
       </c>
       <c r="G847" t="n">
-        <v>3.27898907661438</v>
+        <v>3.2789888381958</v>
       </c>
       <c r="H847" t="n">
         <v>30952</v>
@@ -24961,7 +24961,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>3.31646275520325</v>
+        <v>3.31646299362183</v>
       </c>
       <c r="H848" t="n">
         <v>634236</v>
@@ -25048,7 +25048,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572827339172</v>
       </c>
       <c r="H851" t="n">
         <v>7970</v>
@@ -25135,7 +25135,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G854" t="n">
-        <v>3.50383377075195</v>
+        <v>3.50383353233337</v>
       </c>
       <c r="H854" t="n">
         <v>25599</v>
@@ -25309,7 +25309,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>3.50383377075195</v>
+        <v>3.50383353233337</v>
       </c>
       <c r="H860" t="n">
         <v>12796</v>
@@ -25338,7 +25338,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G861" t="n">
-        <v>3.50383377075195</v>
+        <v>3.50383353233337</v>
       </c>
       <c r="H861" t="n">
         <v>6018</v>
@@ -25454,7 +25454,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G865" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509669303894</v>
       </c>
       <c r="H865" t="n">
         <v>47730</v>
@@ -25483,7 +25483,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G866" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509669303894</v>
       </c>
       <c r="H866" t="n">
         <v>29971</v>
@@ -25570,7 +25570,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572827339172</v>
       </c>
       <c r="H869" t="n">
         <v>31615</v>
@@ -25715,7 +25715,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>3.63499331474304</v>
+        <v>3.63499355316162</v>
       </c>
       <c r="H874" t="n">
         <v>25969</v>
@@ -25744,7 +25744,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G875" t="n">
-        <v>3.66309905052185</v>
+        <v>3.66309857368469</v>
       </c>
       <c r="H875" t="n">
         <v>31745</v>
@@ -25773,7 +25773,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994162559509</v>
       </c>
       <c r="H876" t="n">
         <v>33432</v>
@@ -25802,7 +25802,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994162559509</v>
       </c>
       <c r="H877" t="n">
         <v>44786</v>
@@ -25831,7 +25831,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G878" t="n">
-        <v>3.7380473613739</v>
+        <v>3.73804712295532</v>
       </c>
       <c r="H878" t="n">
         <v>23690</v>
@@ -25918,7 +25918,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G881" t="n">
-        <v>3.68183636665344</v>
+        <v>3.68183612823486</v>
       </c>
       <c r="H881" t="n">
         <v>32331</v>
@@ -26005,7 +26005,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G884" t="n">
-        <v>3.68183636665344</v>
+        <v>3.68183612823486</v>
       </c>
       <c r="H884" t="n">
         <v>63486</v>
@@ -26034,7 +26034,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H885" t="n">
         <v>25749</v>
@@ -26092,7 +26092,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G887" t="n">
-        <v>3.66309905052185</v>
+        <v>3.66309857368469</v>
       </c>
       <c r="H887" t="n">
         <v>21941</v>
@@ -26121,7 +26121,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994162559509</v>
       </c>
       <c r="H888" t="n">
         <v>4653</v>
@@ -26150,7 +26150,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994162559509</v>
       </c>
       <c r="H889" t="n">
         <v>12975</v>
@@ -26179,7 +26179,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994162559509</v>
       </c>
       <c r="H890" t="n">
         <v>11433</v>
@@ -26208,7 +26208,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G891" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H891" t="n">
         <v>5098</v>
@@ -26237,7 +26237,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G892" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H892" t="n">
         <v>9543</v>
@@ -26295,7 +26295,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>3.71931028366089</v>
+        <v>3.71931004524231</v>
       </c>
       <c r="H894" t="n">
         <v>9115</v>
@@ -26353,7 +26353,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G896" t="n">
-        <v>3.71931028366089</v>
+        <v>3.71931004524231</v>
       </c>
       <c r="H896" t="n">
         <v>10204</v>
@@ -26382,7 +26382,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G897" t="n">
-        <v>3.71931028366089</v>
+        <v>3.71931004524231</v>
       </c>
       <c r="H897" t="n">
         <v>17345</v>
@@ -26411,7 +26411,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G898" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H898" t="n">
         <v>5349</v>
@@ -26440,7 +26440,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H899" t="n">
         <v>16909</v>
@@ -26469,7 +26469,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H900" t="n">
         <v>19442</v>
@@ -26527,7 +26527,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H902" t="n">
         <v>8425</v>
@@ -26556,7 +26556,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994162559509</v>
       </c>
       <c r="H903" t="n">
         <v>7500</v>
@@ -26701,7 +26701,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G908" t="n">
-        <v>3.68183636665344</v>
+        <v>3.68183612823486</v>
       </c>
       <c r="H908" t="n">
         <v>5045</v>
@@ -26730,7 +26730,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H909" t="n">
         <v>16470</v>
@@ -26788,7 +26788,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G911" t="n">
-        <v>3.6912043094635</v>
+        <v>3.69120478630066</v>
       </c>
       <c r="H911" t="n">
         <v>1036</v>
@@ -26817,7 +26817,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G912" t="n">
-        <v>3.66309905052185</v>
+        <v>3.66309857368469</v>
       </c>
       <c r="H912" t="n">
         <v>15979</v>
@@ -26846,7 +26846,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G913" t="n">
-        <v>3.72867894172668</v>
+        <v>3.72867846488953</v>
       </c>
       <c r="H913" t="n">
         <v>38206</v>
@@ -26875,7 +26875,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994162559509</v>
       </c>
       <c r="H914" t="n">
         <v>7713</v>
@@ -26904,7 +26904,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G915" t="n">
-        <v>3.68183636665344</v>
+        <v>3.68183612823486</v>
       </c>
       <c r="H915" t="n">
         <v>20933</v>
@@ -26933,7 +26933,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>3.68183636665344</v>
+        <v>3.68183612823486</v>
       </c>
       <c r="H916" t="n">
         <v>1586</v>
@@ -26962,7 +26962,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>3.66309905052185</v>
+        <v>3.66309857368469</v>
       </c>
       <c r="H917" t="n">
         <v>8568</v>
@@ -26991,7 +26991,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G918" t="n">
-        <v>3.68183636665344</v>
+        <v>3.68183612823486</v>
       </c>
       <c r="H918" t="n">
         <v>5481</v>
@@ -27078,7 +27078,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G921" t="n">
-        <v>3.6912043094635</v>
+        <v>3.69120478630066</v>
       </c>
       <c r="H921" t="n">
         <v>16172</v>
@@ -27107,7 +27107,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>3.60688781738281</v>
+        <v>3.60688757896423</v>
       </c>
       <c r="H922" t="n">
         <v>21416</v>
@@ -27136,7 +27136,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>3.66309905052185</v>
+        <v>3.66309857368469</v>
       </c>
       <c r="H923" t="n">
         <v>18984</v>
@@ -27223,7 +27223,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.58815050125122</v>
+        <v>3.58815026283264</v>
       </c>
       <c r="H926" t="n">
         <v>4549</v>
@@ -27252,7 +27252,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.60688781738281</v>
+        <v>3.60688757896423</v>
       </c>
       <c r="H927" t="n">
         <v>22410</v>
@@ -27310,7 +27310,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G929" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509669303894</v>
       </c>
       <c r="H929" t="n">
         <v>10522</v>
@@ -27368,7 +27368,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G931" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509669303894</v>
       </c>
       <c r="H931" t="n">
         <v>26777</v>
@@ -27426,7 +27426,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>3.50383377075195</v>
+        <v>3.50383353233337</v>
       </c>
       <c r="H933" t="n">
         <v>1509</v>
@@ -27484,7 +27484,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572827339172</v>
       </c>
       <c r="H935" t="n">
         <v>4902</v>
@@ -27542,7 +27542,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50383377075195</v>
+        <v>3.50383353233337</v>
       </c>
       <c r="H937" t="n">
         <v>16816</v>
@@ -27600,7 +27600,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>3.54130816459656</v>
+        <v>3.54130792617798</v>
       </c>
       <c r="H939" t="n">
         <v>10462</v>
@@ -27716,7 +27716,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509669303894</v>
       </c>
       <c r="H943" t="n">
         <v>23604</v>
@@ -27745,7 +27745,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>3.56004500389099</v>
+        <v>3.56004524230957</v>
       </c>
       <c r="H944" t="n">
         <v>16909</v>
@@ -27774,7 +27774,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G945" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509669303894</v>
       </c>
       <c r="H945" t="n">
         <v>13661</v>
@@ -27803,7 +27803,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572827339172</v>
       </c>
       <c r="H946" t="n">
         <v>9434</v>
@@ -27890,7 +27890,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>3.48964953422546</v>
+        <v>3.48964929580688</v>
       </c>
       <c r="H949" t="n">
         <v>16149</v>
@@ -27919,7 +27919,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G950" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H950" t="n">
         <v>9898</v>
@@ -27977,7 +27977,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>3.48964953422546</v>
+        <v>3.48964929580688</v>
       </c>
       <c r="H952" t="n">
         <v>33876</v>
@@ -28035,7 +28035,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H954" t="n">
         <v>36717</v>
@@ -28064,7 +28064,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G955" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H955" t="n">
         <v>7960</v>
@@ -28093,7 +28093,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>3.47083735466003</v>
+        <v>3.47083711624146</v>
       </c>
       <c r="H956" t="n">
         <v>9783</v>
@@ -28151,7 +28151,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G958" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H958" t="n">
         <v>6601</v>
@@ -28180,7 +28180,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G959" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H959" t="n">
         <v>22295</v>
@@ -28209,7 +28209,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G960" t="n">
-        <v>3.54608607292175</v>
+        <v>3.54608559608459</v>
       </c>
       <c r="H960" t="n">
         <v>19657</v>
@@ -28238,7 +28238,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G961" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H961" t="n">
         <v>83077</v>
@@ -28267,7 +28267,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G962" t="n">
-        <v>3.46143174171448</v>
+        <v>3.4614315032959</v>
       </c>
       <c r="H962" t="n">
         <v>9986</v>
@@ -28296,7 +28296,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G963" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H963" t="n">
         <v>14536</v>
@@ -28354,7 +28354,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G965" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H965" t="n">
         <v>15852</v>
@@ -28383,7 +28383,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G966" t="n">
-        <v>3.46143174171448</v>
+        <v>3.4614315032959</v>
       </c>
       <c r="H966" t="n">
         <v>6216</v>
@@ -28412,7 +28412,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G967" t="n">
-        <v>3.46143174171448</v>
+        <v>3.4614315032959</v>
       </c>
       <c r="H967" t="n">
         <v>7483</v>
@@ -28441,7 +28441,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H968" t="n">
         <v>28318</v>
@@ -28470,7 +28470,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G969" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H969" t="n">
         <v>1955</v>
@@ -28528,7 +28528,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G971" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H971" t="n">
         <v>7052</v>
@@ -28557,7 +28557,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H972" t="n">
         <v>10374</v>
@@ -28586,7 +28586,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H973" t="n">
         <v>4480</v>
@@ -28615,7 +28615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G974" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H974" t="n">
         <v>2355</v>
@@ -28644,7 +28644,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H975" t="n">
         <v>291</v>
@@ -28673,7 +28673,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G976" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H976" t="n">
         <v>875969</v>
@@ -28731,7 +28731,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H978" t="n">
         <v>27471</v>
@@ -28760,7 +28760,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>3.44261932373047</v>
+        <v>3.44261956214905</v>
       </c>
       <c r="H979" t="n">
         <v>2001</v>
@@ -28847,7 +28847,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G982" t="n">
-        <v>3.44261932373047</v>
+        <v>3.44261956214905</v>
       </c>
       <c r="H982" t="n">
         <v>19297</v>
@@ -28876,7 +28876,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G983" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H983" t="n">
         <v>7025</v>
@@ -28905,7 +28905,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G984" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H984" t="n">
         <v>33582</v>
@@ -28934,7 +28934,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H985" t="n">
         <v>16634</v>
@@ -28992,7 +28992,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>3.27330994606018</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H987" t="n">
         <v>4720</v>
@@ -29050,7 +29050,7 @@
         <v>3.5</v>
       </c>
       <c r="G989" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H989" t="n">
         <v>15262</v>
@@ -29108,7 +29108,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G991" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H991" t="n">
         <v>5729</v>
@@ -29166,7 +29166,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G993" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H993" t="n">
         <v>17975</v>
@@ -29195,7 +29195,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G994" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H994" t="n">
         <v>23673</v>
@@ -29253,7 +29253,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G996" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H996" t="n">
         <v>19809</v>
@@ -29340,7 +29340,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>3.48964953422546</v>
+        <v>3.48964929580688</v>
       </c>
       <c r="H999" t="n">
         <v>7580</v>
@@ -29369,7 +29369,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H1000" t="n">
         <v>24970</v>
@@ -29398,7 +29398,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H1001" t="n">
         <v>14225</v>
@@ -29427,7 +29427,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1002" t="n">
         <v>13743</v>
@@ -29456,7 +29456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H1003" t="n">
         <v>23097</v>
@@ -29485,7 +29485,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1004" t="n">
         <v>24939</v>
@@ -29514,7 +29514,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.44261932373047</v>
+        <v>3.44261956214905</v>
       </c>
       <c r="H1005" t="n">
         <v>15939</v>
@@ -29543,7 +29543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H1006" t="n">
         <v>8363</v>
@@ -29572,7 +29572,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H1007" t="n">
         <v>22863</v>
@@ -29601,7 +29601,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1008" t="n">
         <v>28103</v>
@@ -29688,7 +29688,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H1011" t="n">
         <v>19917</v>
@@ -29717,7 +29717,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1012" t="n">
         <v>15052</v>
@@ -29746,7 +29746,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H1013" t="n">
         <v>14413</v>
@@ -29775,7 +29775,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H1014" t="n">
         <v>25232</v>
@@ -29833,7 +29833,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1016" t="n">
         <v>17274</v>
@@ -29862,7 +29862,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1017" t="n">
         <v>31009</v>
@@ -29891,7 +29891,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1018" t="n">
         <v>21367</v>
@@ -29920,7 +29920,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1019" t="n">
         <v>6494</v>
@@ -29949,7 +29949,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.27330994606018</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H1020" t="n">
         <v>11369</v>
@@ -30007,7 +30007,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.20746755599976</v>
+        <v>3.20746779441833</v>
       </c>
       <c r="H1022" t="n">
         <v>21166</v>
@@ -30065,7 +30065,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1024" t="n">
         <v>20799</v>
@@ -30094,7 +30094,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H1025" t="n">
         <v>19436</v>
@@ -30152,7 +30152,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.47083735466003</v>
+        <v>3.47083711624146</v>
       </c>
       <c r="H1027" t="n">
         <v>11337</v>
@@ -30181,7 +30181,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.47083735466003</v>
+        <v>3.47083711624146</v>
       </c>
       <c r="H1028" t="n">
         <v>16516</v>
@@ -30210,7 +30210,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H1029" t="n">
         <v>13498</v>
@@ -30239,7 +30239,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.54608607292175</v>
+        <v>3.54608559608459</v>
       </c>
       <c r="H1030" t="n">
         <v>12652</v>
@@ -30268,7 +30268,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H1031" t="n">
         <v>17049</v>
@@ -30326,7 +30326,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H1033" t="n">
         <v>14872</v>
@@ -30355,7 +30355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H1034" t="n">
         <v>8021</v>
@@ -30471,7 +30471,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H1038" t="n">
         <v>7642</v>
@@ -30529,7 +30529,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1040" t="n">
         <v>6370</v>
@@ -30558,7 +30558,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H1041" t="n">
         <v>4136</v>
@@ -30587,7 +30587,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.48024368286133</v>
+        <v>3.48024344444275</v>
       </c>
       <c r="H1042" t="n">
         <v>9206</v>
@@ -30645,7 +30645,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H1044" t="n">
         <v>14048</v>
@@ -30674,7 +30674,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.43321299552917</v>
+        <v>3.4332127571106</v>
       </c>
       <c r="H1045" t="n">
         <v>9253</v>
@@ -30732,7 +30732,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1047" t="n">
         <v>28501</v>
@@ -30761,7 +30761,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1048" t="n">
         <v>3095</v>
@@ -30790,7 +30790,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1049" t="n">
         <v>6837</v>
@@ -30819,7 +30819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1050" t="n">
         <v>2753</v>
@@ -30848,7 +30848,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1051" t="n">
         <v>50625</v>
@@ -30877,7 +30877,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1052" t="n">
         <v>3526</v>
@@ -30906,7 +30906,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1053" t="n">
         <v>9192</v>
@@ -30935,7 +30935,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1054" t="n">
         <v>9622</v>
@@ -31109,7 +31109,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1060" t="n">
         <v>1040</v>
@@ -31225,7 +31225,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1064" t="n">
         <v>6163</v>
@@ -31254,7 +31254,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1065" t="n">
         <v>5109</v>
@@ -31283,7 +31283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1066" t="n">
         <v>9447</v>
@@ -31312,7 +31312,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1067" t="n">
         <v>17821</v>
@@ -31370,7 +31370,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1069" t="n">
         <v>8548</v>
@@ -31399,7 +31399,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1070" t="n">
         <v>8700</v>
@@ -31457,7 +31457,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1072" t="n">
         <v>11679</v>
@@ -31486,7 +31486,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1073" t="n">
         <v>9850</v>
@@ -31544,7 +31544,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1075" t="n">
         <v>9204</v>
@@ -31573,7 +31573,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1076" t="n">
         <v>8834</v>
@@ -31631,7 +31631,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H1078" t="n">
         <v>122293</v>
@@ -31660,7 +31660,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1079" t="n">
         <v>114960</v>
@@ -31805,7 +31805,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1084" t="n">
         <v>31241</v>
@@ -31892,7 +31892,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1087" t="n">
         <v>37589</v>
@@ -31950,7 +31950,7 @@
         <v>3.5</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1089" t="n">
         <v>6814</v>
@@ -32066,7 +32066,7 @@
         <v>3.5</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1093" t="n">
         <v>42910</v>
@@ -32124,7 +32124,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1095" t="n">
         <v>6031</v>
@@ -32153,7 +32153,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.27330994606018</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H1096" t="n">
         <v>36379</v>
@@ -32211,7 +32211,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.26390409469604</v>
+        <v>3.26390433311462</v>
       </c>
       <c r="H1098" t="n">
         <v>10085</v>
@@ -32240,7 +32240,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.26390409469604</v>
+        <v>3.26390433311462</v>
       </c>
       <c r="H1099" t="n">
         <v>21707</v>
@@ -32269,7 +32269,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.26390409469604</v>
+        <v>3.26390433311462</v>
       </c>
       <c r="H1100" t="n">
         <v>4249</v>
@@ -32356,7 +32356,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H1103" t="n">
         <v>134663</v>
@@ -32385,7 +32385,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H1104" t="n">
         <v>248108</v>
@@ -32414,7 +32414,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1105" t="n">
         <v>31138</v>
@@ -32443,7 +32443,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.46143174171448</v>
+        <v>3.4614315032959</v>
       </c>
       <c r="H1106" t="n">
         <v>101164</v>
@@ -32472,7 +32472,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H1107" t="n">
         <v>56458</v>
@@ -32530,7 +32530,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.44261932373047</v>
+        <v>3.44261956214905</v>
       </c>
       <c r="H1109" t="n">
         <v>18068</v>
@@ -32588,7 +32588,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1111" t="n">
         <v>15319</v>
@@ -32617,7 +32617,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1112" t="n">
         <v>69565</v>
@@ -32675,7 +32675,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H1114" t="n">
         <v>5899</v>
@@ -32704,7 +32704,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1115" t="n">
         <v>808</v>
@@ -32820,7 +32820,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1119" t="n">
         <v>10067</v>
@@ -32849,7 +32849,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1120" t="n">
         <v>5895</v>
@@ -32878,7 +32878,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1121" t="n">
         <v>9350</v>
@@ -32936,7 +32936,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1123" t="n">
         <v>8305</v>
@@ -32965,7 +32965,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1124" t="n">
         <v>594</v>
@@ -33023,7 +33023,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1126" t="n">
         <v>6326</v>
@@ -33081,7 +33081,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H1128" t="n">
         <v>7133</v>
@@ -33168,7 +33168,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1131" t="n">
         <v>3010</v>
@@ -33197,7 +33197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1132" t="n">
         <v>2552</v>
@@ -33226,7 +33226,7 @@
         <v>3.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1133" t="n">
         <v>13100</v>
@@ -33255,7 +33255,7 @@
         <v>3.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1134" t="n">
         <v>10219</v>
@@ -33313,7 +33313,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.27330994606018</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H1136" t="n">
         <v>34900</v>
@@ -33342,7 +33342,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1137" t="n">
         <v>12331</v>
@@ -33371,7 +33371,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.26390409469604</v>
+        <v>3.26390433311462</v>
       </c>
       <c r="H1138" t="n">
         <v>28037</v>
@@ -33458,7 +33458,7 @@
         <v>3.5</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1141" t="n">
         <v>16864</v>
@@ -33487,7 +33487,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.24509167671204</v>
+        <v>3.24509143829346</v>
       </c>
       <c r="H1142" t="n">
         <v>10849</v>
@@ -33516,7 +33516,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.20746755599976</v>
+        <v>3.20746779441833</v>
       </c>
       <c r="H1143" t="n">
         <v>11163</v>
@@ -33603,7 +33603,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.0851891040802</v>
+        <v>3.08518886566162</v>
       </c>
       <c r="H1146" t="n">
         <v>19787</v>
@@ -33632,7 +33632,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.16984343528748</v>
+        <v>3.1698431968689</v>
       </c>
       <c r="H1147" t="n">
         <v>14261</v>
@@ -33719,7 +33719,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1150" t="n">
         <v>45850</v>
@@ -33777,7 +33777,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.24509167671204</v>
+        <v>3.24509143829346</v>
       </c>
       <c r="H1152" t="n">
         <v>57910</v>
@@ -33864,7 +33864,7 @@
         <v>3.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1155" t="n">
         <v>27404</v>
@@ -33893,7 +33893,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1156" t="n">
         <v>14999</v>
@@ -33922,7 +33922,7 @@
         <v>3.5</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1157" t="n">
         <v>28053</v>
@@ -33951,7 +33951,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1158" t="n">
         <v>11615</v>
@@ -33980,7 +33980,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1159" t="n">
         <v>22763</v>
@@ -34009,7 +34009,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1160" t="n">
         <v>6945</v>
@@ -34038,7 +34038,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1161" t="n">
         <v>12453</v>
@@ -34067,7 +34067,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H1162" t="n">
         <v>17267</v>
@@ -34096,7 +34096,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1163" t="n">
         <v>7503</v>
@@ -34125,7 +34125,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1164" t="n">
         <v>12318</v>
@@ -34154,7 +34154,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1165" t="n">
         <v>31537</v>
@@ -34183,7 +34183,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1166" t="n">
         <v>12895</v>
@@ -34212,7 +34212,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1167" t="n">
         <v>4153</v>
@@ -34241,7 +34241,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1168" t="n">
         <v>4352</v>
@@ -34299,7 +34299,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1170" t="n">
         <v>42476</v>
@@ -34328,7 +34328,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1171" t="n">
         <v>14778</v>
@@ -34357,7 +34357,7 @@
         <v>3.5</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1172" t="n">
         <v>7570</v>
@@ -34386,7 +34386,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1173" t="n">
         <v>26219</v>
@@ -34415,7 +34415,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1174" t="n">
         <v>11204</v>
@@ -34444,7 +34444,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.3015284538269</v>
+        <v>3.30152797698975</v>
       </c>
       <c r="H1175" t="n">
         <v>9316</v>
@@ -34473,7 +34473,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1176" t="n">
         <v>3870</v>
@@ -34502,7 +34502,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.37677669525146</v>
+        <v>3.37677693367004</v>
       </c>
       <c r="H1177" t="n">
         <v>6851</v>
@@ -34531,7 +34531,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1178" t="n">
         <v>2015</v>
@@ -34560,7 +34560,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H1179" t="n">
         <v>6440</v>
@@ -34589,7 +34589,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1180" t="n">
         <v>17356</v>
@@ -34618,7 +34618,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.4144012928009</v>
+        <v>3.41440105438232</v>
       </c>
       <c r="H1181" t="n">
         <v>43268</v>
@@ -34647,7 +34647,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1182" t="n">
         <v>2033</v>
@@ -34676,7 +34676,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H1183" t="n">
         <v>6020</v>
@@ -34705,7 +34705,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.40499496459961</v>
+        <v>3.40499472618103</v>
       </c>
       <c r="H1184" t="n">
         <v>8021</v>
@@ -34734,7 +34734,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1185" t="n">
         <v>10211</v>
@@ -34821,7 +34821,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1188" t="n">
         <v>977</v>
@@ -34879,7 +34879,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35796451568604</v>
+        <v>3.35796427726746</v>
       </c>
       <c r="H1190" t="n">
         <v>3902</v>
@@ -34937,7 +34937,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.36737036705017</v>
+        <v>3.36737060546875</v>
       </c>
       <c r="H1192" t="n">
         <v>736</v>
@@ -35082,7 +35082,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1197" t="n">
         <v>5453</v>
@@ -35111,7 +35111,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.26390409469604</v>
+        <v>3.26390433311462</v>
       </c>
       <c r="H1198" t="n">
         <v>22076</v>
@@ -35140,7 +35140,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.31093430519104</v>
+        <v>3.31093406677246</v>
       </c>
       <c r="H1199" t="n">
         <v>9573</v>
@@ -35169,7 +35169,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.24509167671204</v>
+        <v>3.24509143829346</v>
       </c>
       <c r="H1200" t="n">
         <v>123001</v>
@@ -35198,7 +35198,7 @@
         <v>3.5</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.29212188720703</v>
+        <v>3.29212212562561</v>
       </c>
       <c r="H1201" t="n">
         <v>17101</v>
@@ -35227,7 +35227,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1202" t="n">
         <v>33897</v>
@@ -35256,7 +35256,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.32034039497375</v>
+        <v>3.32034063339233</v>
       </c>
       <c r="H1203" t="n">
         <v>8482</v>
@@ -35314,7 +35314,7 @@
         <v>3.5</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1205" t="n">
         <v>13924</v>
@@ -35343,7 +35343,7 @@
         <v>3.5</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1206" t="n">
         <v>1243</v>
@@ -35372,7 +35372,7 @@
         <v>3.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1207" t="n">
         <v>1219</v>
@@ -35430,7 +35430,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.32974648475647</v>
+        <v>3.32974624633789</v>
       </c>
       <c r="H1209" t="n">
         <v>18950</v>
@@ -35459,7 +35459,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.32974648475647</v>
+        <v>3.32974624633789</v>
       </c>
       <c r="H1210" t="n">
         <v>3861</v>
@@ -35488,7 +35488,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1211" t="n">
         <v>3508</v>
@@ -35517,7 +35517,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1212" t="n">
         <v>3165</v>
@@ -35546,7 +35546,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1213" t="n">
         <v>2384</v>
@@ -35807,7 +35807,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1222" t="n">
         <v>4743</v>
@@ -36010,7 +36010,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1229" t="n">
         <v>6507</v>
@@ -36155,7 +36155,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1234" t="n">
         <v>7222</v>
@@ -36184,7 +36184,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1235" t="n">
         <v>12401</v>
@@ -36213,7 +36213,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.30128693580627</v>
+        <v>3.30128717422485</v>
       </c>
       <c r="H1236" t="n">
         <v>20244</v>
@@ -36358,7 +36358,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.30128693580627</v>
+        <v>3.30128717422485</v>
       </c>
       <c r="H1241" t="n">
         <v>54707</v>
@@ -36387,7 +36387,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1242" t="n">
         <v>3091</v>
@@ -36416,7 +36416,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.32974648475647</v>
+        <v>3.32974624633789</v>
       </c>
       <c r="H1243" t="n">
         <v>5824</v>
@@ -36503,7 +36503,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1246" t="n">
         <v>6241</v>
@@ -36561,7 +36561,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1248" t="n">
         <v>2526</v>
@@ -36590,7 +36590,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1249" t="n">
         <v>9760</v>
@@ -36619,7 +36619,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.32974648475647</v>
+        <v>3.32974624633789</v>
       </c>
       <c r="H1250" t="n">
         <v>9482</v>
@@ -36706,7 +36706,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1253" t="n">
         <v>4000</v>
@@ -36735,7 +36735,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1254" t="n">
         <v>2921</v>
@@ -36822,7 +36822,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.32974648475647</v>
+        <v>3.32974624633789</v>
       </c>
       <c r="H1257" t="n">
         <v>91040</v>
@@ -37025,7 +37025,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1264" t="n">
         <v>1725</v>
@@ -37054,7 +37054,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1265" t="n">
         <v>3014</v>
@@ -37083,7 +37083,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1266" t="n">
         <v>6584</v>
@@ -37170,7 +37170,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1269" t="n">
         <v>7300</v>
@@ -37199,7 +37199,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1270" t="n">
         <v>3113</v>
@@ -37344,7 +37344,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1275" t="n">
         <v>522</v>
@@ -37431,7 +37431,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1278" t="n">
         <v>19303</v>
@@ -37489,7 +37489,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1280" t="n">
         <v>3868</v>
@@ -37518,7 +37518,7 @@
         <v>3.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1281" t="n">
         <v>18576</v>
@@ -37547,7 +37547,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.32974648475647</v>
+        <v>3.32974624633789</v>
       </c>
       <c r="H1282" t="n">
         <v>4916</v>
@@ -37576,7 +37576,7 @@
         <v>3.5</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1283" t="n">
         <v>23288</v>
@@ -37605,7 +37605,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.30128693580627</v>
+        <v>3.30128717422485</v>
       </c>
       <c r="H1284" t="n">
         <v>154495</v>
@@ -37634,7 +37634,7 @@
         <v>3.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1285" t="n">
         <v>17175</v>
@@ -37663,7 +37663,7 @@
         <v>3.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1286" t="n">
         <v>14605</v>
@@ -37692,7 +37692,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.28231406211853</v>
+        <v>3.28231382369995</v>
       </c>
       <c r="H1287" t="n">
         <v>17850</v>
@@ -37779,7 +37779,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.30128693580627</v>
+        <v>3.30128717422485</v>
       </c>
       <c r="H1290" t="n">
         <v>2972</v>
@@ -37808,7 +37808,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.30128693580627</v>
+        <v>3.30128717422485</v>
       </c>
       <c r="H1291" t="n">
         <v>3986</v>
@@ -37837,7 +37837,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1292" t="n">
         <v>6737</v>
@@ -37866,7 +37866,7 @@
         <v>3.5</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.32025980949402</v>
+        <v>3.3202600479126</v>
       </c>
       <c r="H1293" t="n">
         <v>10857</v>
@@ -37924,7 +37924,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.28231406211853</v>
+        <v>3.28231382369995</v>
       </c>
       <c r="H1295" t="n">
         <v>900</v>
@@ -37982,7 +37982,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1297" t="n">
         <v>23272</v>
@@ -38011,7 +38011,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.45307064056396</v>
+        <v>3.45307040214539</v>
       </c>
       <c r="H1298" t="n">
         <v>31730</v>
@@ -38069,7 +38069,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1300" t="n">
         <v>6137</v>
@@ -38098,7 +38098,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.45307064056396</v>
+        <v>3.45307040214539</v>
       </c>
       <c r="H1301" t="n">
         <v>5347</v>
@@ -38127,7 +38127,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.44358420372009</v>
+        <v>3.44358396530151</v>
       </c>
       <c r="H1302" t="n">
         <v>5259</v>
@@ -38185,7 +38185,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1304" t="n">
         <v>9749</v>
@@ -38214,7 +38214,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.44358420372009</v>
+        <v>3.44358396530151</v>
       </c>
       <c r="H1305" t="n">
         <v>5513</v>
@@ -38243,7 +38243,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1306" t="n">
         <v>2109</v>
@@ -38272,7 +38272,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.36769223213196</v>
+        <v>3.36769247055054</v>
       </c>
       <c r="H1307" t="n">
         <v>6377</v>
@@ -38475,7 +38475,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.34871935844421</v>
+        <v>3.34871959686279</v>
       </c>
       <c r="H1314" t="n">
         <v>13661</v>
@@ -38533,7 +38533,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.44358420372009</v>
+        <v>3.44358396530151</v>
       </c>
       <c r="H1316" t="n">
         <v>3324</v>
@@ -38620,7 +38620,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.41512441635132</v>
+        <v>3.4151246547699</v>
       </c>
       <c r="H1319" t="n">
         <v>1500</v>
@@ -38852,7 +38852,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.51947569847107</v>
+        <v>3.51947546005249</v>
       </c>
       <c r="H1327" t="n">
         <v>35165</v>
@@ -38881,7 +38881,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.6997184753418</v>
+        <v>3.69971823692322</v>
       </c>
       <c r="H1328" t="n">
         <v>148742</v>
@@ -38968,7 +38968,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.6997184753418</v>
+        <v>3.69971823692322</v>
       </c>
       <c r="H1331" t="n">
         <v>27325</v>
@@ -39026,7 +39026,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.6997184753418</v>
+        <v>3.69971823692322</v>
       </c>
       <c r="H1333" t="n">
         <v>30168</v>
@@ -39142,7 +39142,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1337" t="n">
         <v>25748</v>
@@ -39345,7 +39345,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1344" t="n">
         <v>4146</v>
@@ -39374,7 +39374,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1345" t="n">
         <v>11667</v>
@@ -39403,7 +39403,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.66177225112915</v>
+        <v>3.66177248954773</v>
       </c>
       <c r="H1346" t="n">
         <v>4769</v>
@@ -39461,7 +39461,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1348" t="n">
         <v>4269</v>
@@ -39490,7 +39490,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1349" t="n">
         <v>9385</v>
@@ -39577,7 +39577,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.51947569847107</v>
+        <v>3.51947546005249</v>
       </c>
       <c r="H1352" t="n">
         <v>5476</v>
@@ -39606,7 +39606,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.59536695480347</v>
+        <v>3.59536719322205</v>
       </c>
       <c r="H1353" t="n">
         <v>7842</v>
@@ -39664,7 +39664,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1355" t="n">
         <v>4918</v>
@@ -39722,7 +39722,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1357" t="n">
         <v>3436</v>
@@ -39751,7 +39751,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1358" t="n">
         <v>6625</v>
@@ -39780,7 +39780,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1359" t="n">
         <v>2648</v>
@@ -39838,7 +39838,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1361" t="n">
         <v>9755</v>
@@ -39954,7 +39954,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1365" t="n">
         <v>18108</v>
@@ -40012,7 +40012,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1367" t="n">
         <v>11540</v>
@@ -40041,7 +40041,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1368" t="n">
         <v>15221</v>
@@ -40070,7 +40070,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.74715065956116</v>
+        <v>3.74715042114258</v>
       </c>
       <c r="H1369" t="n">
         <v>229363</v>
@@ -40099,7 +40099,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.74715065956116</v>
+        <v>3.74715042114258</v>
       </c>
       <c r="H1370" t="n">
         <v>72359</v>
@@ -40157,7 +40157,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1372" t="n">
         <v>11860</v>
@@ -40186,7 +40186,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1373" t="n">
         <v>51194</v>
@@ -40215,7 +40215,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.66177225112915</v>
+        <v>3.66177248954773</v>
       </c>
       <c r="H1374" t="n">
         <v>7000</v>
@@ -40244,7 +40244,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1375" t="n">
         <v>9170</v>
@@ -40273,7 +40273,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1376" t="n">
         <v>14833</v>
@@ -40331,7 +40331,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1378" t="n">
         <v>11890</v>
@@ -40505,7 +40505,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1384" t="n">
         <v>15858</v>
@@ -40592,7 +40592,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.66177225112915</v>
+        <v>3.66177248954773</v>
       </c>
       <c r="H1387" t="n">
         <v>8003</v>
@@ -40621,7 +40621,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.66177225112915</v>
+        <v>3.66177248954773</v>
       </c>
       <c r="H1388" t="n">
         <v>11195</v>
@@ -40650,7 +40650,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1389" t="n">
         <v>8881</v>
@@ -40679,7 +40679,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1390" t="n">
         <v>5051</v>
@@ -40708,7 +40708,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1391" t="n">
         <v>2025</v>
@@ -40795,7 +40795,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1394" t="n">
         <v>3830</v>
@@ -40824,7 +40824,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1395" t="n">
         <v>8093</v>
@@ -40853,7 +40853,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1396" t="n">
         <v>2013</v>
@@ -40911,7 +40911,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.59536695480347</v>
+        <v>3.59536719322205</v>
       </c>
       <c r="H1398" t="n">
         <v>17208</v>
@@ -40940,7 +40940,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1399" t="n">
         <v>4513</v>
@@ -41027,7 +41027,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1402" t="n">
         <v>5050</v>
@@ -41056,7 +41056,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1403" t="n">
         <v>3766</v>
@@ -41085,7 +41085,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.59536695480347</v>
+        <v>3.59536719322205</v>
       </c>
       <c r="H1404" t="n">
         <v>4488</v>
@@ -41114,7 +41114,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.59536695480347</v>
+        <v>3.59536719322205</v>
       </c>
       <c r="H1405" t="n">
         <v>2769</v>
@@ -41230,7 +41230,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1409" t="n">
         <v>5292</v>
@@ -41259,7 +41259,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.59536695480347</v>
+        <v>3.59536719322205</v>
       </c>
       <c r="H1410" t="n">
         <v>5</v>
@@ -41346,7 +41346,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1413" t="n">
         <v>4447</v>
@@ -41462,7 +41462,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1417" t="n">
         <v>11002</v>
@@ -41491,7 +41491,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1418" t="n">
         <v>21864</v>
@@ -41520,7 +41520,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1419" t="n">
         <v>18053</v>
@@ -41549,7 +41549,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1420" t="n">
         <v>29627</v>
@@ -41636,7 +41636,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1423" t="n">
         <v>4350</v>
@@ -41665,7 +41665,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1424" t="n">
         <v>6719</v>
@@ -41723,7 +41723,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.59536695480347</v>
+        <v>3.59536719322205</v>
       </c>
       <c r="H1426" t="n">
         <v>936</v>
@@ -41752,7 +41752,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1427" t="n">
         <v>28806</v>
@@ -41839,7 +41839,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1430" t="n">
         <v>9372</v>
@@ -41897,7 +41897,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1432" t="n">
         <v>1886</v>
@@ -42013,7 +42013,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1436" t="n">
         <v>59</v>
@@ -42042,7 +42042,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1437" t="n">
         <v>9602</v>
@@ -42071,7 +42071,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1438" t="n">
         <v>13866</v>
@@ -42100,7 +42100,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1439" t="n">
         <v>3365</v>
@@ -42129,7 +42129,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1440" t="n">
         <v>10976</v>
@@ -42158,7 +42158,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1441" t="n">
         <v>0</v>
@@ -42187,7 +42187,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.64279913902283</v>
+        <v>3.64279937744141</v>
       </c>
       <c r="H1442" t="n">
         <v>0</v>
@@ -42303,7 +42303,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.59536695480347</v>
+        <v>3.59536719322205</v>
       </c>
       <c r="H1446" t="n">
         <v>4109</v>
@@ -42390,7 +42390,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.5763943195343</v>
+        <v>3.57639408111572</v>
       </c>
       <c r="H1449" t="n">
         <v>12494</v>
@@ -42477,7 +42477,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.61434006690979</v>
+        <v>3.61434030532837</v>
       </c>
       <c r="H1452" t="n">
         <v>6393</v>
@@ -42593,7 +42593,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.62382650375366</v>
+        <v>3.62382674217224</v>
       </c>
       <c r="H1456" t="n">
         <v>2017</v>
@@ -42709,7 +42709,7 @@
         <v>3.75</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1460" t="n">
         <v>30425</v>
@@ -42738,7 +42738,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1461" t="n">
         <v>10285</v>
@@ -42767,7 +42767,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.62423229217529</v>
+        <v>3.62423253059387</v>
       </c>
       <c r="H1462" t="n">
         <v>10451</v>
@@ -42796,7 +42796,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1463" t="n">
         <v>6816</v>
@@ -42825,7 +42825,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1464" t="n">
         <v>7463</v>
@@ -42883,7 +42883,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1466" t="n">
         <v>1305</v>
@@ -42941,7 +42941,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1468" t="n">
         <v>535</v>
@@ -42970,7 +42970,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1469" t="n">
         <v>0</v>
@@ -42999,7 +42999,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1470" t="n">
         <v>20214</v>
@@ -43144,7 +43144,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1475" t="n">
         <v>900</v>
@@ -43173,7 +43173,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1476" t="n">
         <v>2526</v>
@@ -43434,7 +43434,7 @@
         <v>3.75</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1485" t="n">
         <v>915</v>
@@ -43492,7 +43492,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.55711722373962</v>
+        <v>3.55711698532104</v>
       </c>
       <c r="H1487" t="n">
         <v>1120</v>
@@ -43521,7 +43521,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1488" t="n">
         <v>27452</v>
@@ -43666,7 +43666,7 @@
         <v>3.75</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1493" t="n">
         <v>2701</v>
@@ -43695,7 +43695,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.55711722373962</v>
+        <v>3.55711698532104</v>
       </c>
       <c r="H1494" t="n">
         <v>4273</v>
@@ -43753,7 +43753,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.55711722373962</v>
+        <v>3.55711698532104</v>
       </c>
       <c r="H1496" t="n">
         <v>3773</v>
@@ -43782,7 +43782,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.55711722373962</v>
+        <v>3.55711698532104</v>
       </c>
       <c r="H1497" t="n">
         <v>650</v>
@@ -43927,7 +43927,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1502" t="n">
         <v>34693</v>
@@ -44275,7 +44275,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.50917744636536</v>
+        <v>3.50917768478394</v>
       </c>
       <c r="H1514" t="n">
         <v>591712</v>
@@ -44478,7 +44478,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.394122838974</v>
+        <v>3.39412236213684</v>
       </c>
       <c r="H1521" t="n">
         <v>185</v>
@@ -44536,7 +44536,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.394122838974</v>
+        <v>3.39412236213684</v>
       </c>
       <c r="H1523" t="n">
         <v>34901</v>
@@ -44565,7 +44565,7 @@
         <v>3.5</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1524" t="n">
         <v>25993</v>
@@ -44623,7 +44623,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.38453435897827</v>
+        <v>3.38453459739685</v>
       </c>
       <c r="H1526" t="n">
         <v>9125</v>
@@ -44652,7 +44652,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.394122838974</v>
+        <v>3.39412236213684</v>
       </c>
       <c r="H1527" t="n">
         <v>6101</v>
@@ -44797,7 +44797,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.33659505844116</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1532" t="n">
         <v>5544</v>
@@ -44855,7 +44855,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.31741952896118</v>
+        <v>3.3174192905426</v>
       </c>
       <c r="H1534" t="n">
         <v>36387</v>
@@ -44884,7 +44884,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.33659505844116</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1535" t="n">
         <v>43641</v>
@@ -44913,7 +44913,7 @@
         <v>3.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1536" t="n">
         <v>51876</v>
@@ -44942,7 +44942,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.31741952896118</v>
+        <v>3.3174192905426</v>
       </c>
       <c r="H1537" t="n">
         <v>70398</v>
@@ -45058,7 +45058,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.40371060371399</v>
+        <v>3.40371036529541</v>
       </c>
       <c r="H1541" t="n">
         <v>243619</v>
@@ -45087,7 +45087,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.40371060371399</v>
+        <v>3.40371036529541</v>
       </c>
       <c r="H1542" t="n">
         <v>124186</v>
@@ -45145,7 +45145,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.38453435897827</v>
+        <v>3.38453459739685</v>
       </c>
       <c r="H1544" t="n">
         <v>168277</v>
@@ -45174,7 +45174,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.40371060371399</v>
+        <v>3.40371036529541</v>
       </c>
       <c r="H1545" t="n">
         <v>170101</v>
@@ -45232,7 +45232,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.33659505844116</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1547" t="n">
         <v>49104</v>
@@ -45261,7 +45261,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.31741952896118</v>
+        <v>3.3174192905426</v>
       </c>
       <c r="H1548" t="n">
         <v>36917</v>
@@ -45290,7 +45290,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.26947951316833</v>
+        <v>3.26947975158691</v>
       </c>
       <c r="H1549" t="n">
         <v>54152</v>
@@ -45319,7 +45319,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.28865551948547</v>
+        <v>3.28865575790405</v>
       </c>
       <c r="H1550" t="n">
         <v>175383</v>
@@ -45377,7 +45377,7 @@
         <v>3.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1552" t="n">
         <v>28783</v>
@@ -45406,7 +45406,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.40371060371399</v>
+        <v>3.40371036529541</v>
       </c>
       <c r="H1553" t="n">
         <v>114032</v>
@@ -45464,7 +45464,7 @@
         <v>3.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1555" t="n">
         <v>31323</v>
@@ -45522,7 +45522,7 @@
         <v>3.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1557" t="n">
         <v>166597</v>
@@ -45551,7 +45551,7 @@
         <v>3.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1558" t="n">
         <v>5668</v>
@@ -45580,7 +45580,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.33659505844116</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1559" t="n">
         <v>123618</v>
@@ -45609,7 +45609,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.33659505844116</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1560" t="n">
         <v>28599</v>
@@ -45638,7 +45638,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.33659505844116</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1561" t="n">
         <v>3921</v>
@@ -45725,7 +45725,7 @@
         <v>3.5</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1564" t="n">
         <v>20351</v>
@@ -45812,7 +45812,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.28865551948547</v>
+        <v>3.28865575790405</v>
       </c>
       <c r="H1567" t="n">
         <v>52435</v>
@@ -45870,7 +45870,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.26947951316833</v>
+        <v>3.26947975158691</v>
       </c>
       <c r="H1569" t="n">
         <v>10592</v>
@@ -45928,7 +45928,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.25030398368835</v>
+        <v>3.25030374526978</v>
       </c>
       <c r="H1571" t="n">
         <v>125952</v>
@@ -46015,7 +46015,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.31741952896118</v>
+        <v>3.3174192905426</v>
       </c>
       <c r="H1574" t="n">
         <v>43664</v>
@@ -46044,7 +46044,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.33659505844116</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1575" t="n">
         <v>39131</v>
@@ -46102,7 +46102,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.29824328422546</v>
+        <v>3.29824352264404</v>
       </c>
       <c r="H1577" t="n">
         <v>21873</v>
@@ -46276,7 +46276,7 @@
         <v>3.5</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.3557710647583</v>
+        <v>3.35577082633972</v>
       </c>
       <c r="H1583" t="n">
         <v>194038</v>
@@ -46334,7 +46334,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1585" t="n">
         <v>607033</v>
@@ -46363,7 +46363,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74887537956238</v>
+        <v>3.74887561798096</v>
       </c>
       <c r="H1586" t="n">
         <v>275363</v>
@@ -46392,7 +46392,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.74887537956238</v>
+        <v>3.74887561798096</v>
       </c>
       <c r="H1587" t="n">
         <v>64904</v>
@@ -46421,7 +46421,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.74887537956238</v>
+        <v>3.74887561798096</v>
       </c>
       <c r="H1588" t="n">
         <v>136262</v>
@@ -46450,7 +46450,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1589" t="n">
         <v>140695</v>
@@ -46508,7 +46508,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.71052360534668</v>
+        <v>3.71052384376526</v>
       </c>
       <c r="H1591" t="n">
         <v>308703</v>
@@ -46566,7 +46566,7 @@
         <v>4</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.83516693115234</v>
+        <v>3.83516669273376</v>
       </c>
       <c r="H1593" t="n">
         <v>735811</v>
@@ -46595,7 +46595,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.75846362113953</v>
+        <v>3.75846338272095</v>
       </c>
       <c r="H1594" t="n">
         <v>90326</v>
@@ -46624,7 +46624,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.75846362113953</v>
+        <v>3.75846338272095</v>
       </c>
       <c r="H1595" t="n">
         <v>144318</v>
@@ -46653,7 +46653,7 @@
         <v>4</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.83516693115234</v>
+        <v>3.83516669273376</v>
       </c>
       <c r="H1596" t="n">
         <v>238278</v>
@@ -46711,7 +46711,7 @@
         <v>4</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.83516693115234</v>
+        <v>3.83516669273376</v>
       </c>
       <c r="H1598" t="n">
         <v>64736</v>
@@ -46798,7 +46798,7 @@
         <v>4</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.83516693115234</v>
+        <v>3.83516669273376</v>
       </c>
       <c r="H1601" t="n">
         <v>58463</v>
@@ -46827,7 +46827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.79681539535522</v>
+        <v>3.79681515693665</v>
       </c>
       <c r="H1602" t="n">
         <v>87427</v>
@@ -46856,7 +46856,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.79681539535522</v>
+        <v>3.79681515693665</v>
       </c>
       <c r="H1603" t="n">
         <v>9376</v>
@@ -46943,7 +46943,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.7872269153595</v>
+        <v>3.78722715377808</v>
       </c>
       <c r="H1606" t="n">
         <v>26310</v>
@@ -46972,7 +46972,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.80640316009521</v>
+        <v>3.80640292167664</v>
       </c>
       <c r="H1607" t="n">
         <v>422791</v>
@@ -47001,7 +47001,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.79681539535522</v>
+        <v>3.79681515693665</v>
       </c>
       <c r="H1608" t="n">
         <v>76479</v>
@@ -47030,7 +47030,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.7872269153595</v>
+        <v>3.78722715377808</v>
       </c>
       <c r="H1609" t="n">
         <v>22088</v>
@@ -47233,7 +47233,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.7872269153595</v>
+        <v>3.78722715377808</v>
       </c>
       <c r="H1616" t="n">
         <v>1156018</v>
@@ -47262,7 +47262,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.70093560218811</v>
+        <v>3.70093584060669</v>
       </c>
       <c r="H1617" t="n">
         <v>45695</v>
@@ -47291,7 +47291,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1618" t="n">
         <v>47307</v>
@@ -47320,7 +47320,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1619" t="n">
         <v>47852</v>
@@ -47378,7 +47378,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.70093560218811</v>
+        <v>3.70093584060669</v>
       </c>
       <c r="H1621" t="n">
         <v>40181</v>
@@ -47407,7 +47407,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.71052360534668</v>
+        <v>3.71052384376526</v>
       </c>
       <c r="H1622" t="n">
         <v>38232</v>
@@ -47465,7 +47465,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1624" t="n">
         <v>59345</v>
@@ -47581,7 +47581,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1628" t="n">
         <v>42179</v>
@@ -47610,7 +47610,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1629" t="n">
         <v>17568</v>
@@ -47755,7 +47755,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.71052360534668</v>
+        <v>3.71052384376526</v>
       </c>
       <c r="H1634" t="n">
         <v>20041</v>
@@ -47784,7 +47784,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1635" t="n">
         <v>19421</v>
@@ -47813,7 +47813,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.70093560218811</v>
+        <v>3.70093584060669</v>
       </c>
       <c r="H1636" t="n">
         <v>58879</v>
@@ -48016,7 +48016,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.75846362113953</v>
+        <v>3.75846338272095</v>
       </c>
       <c r="H1643" t="n">
         <v>60070</v>
@@ -48074,7 +48074,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.62423229217529</v>
+        <v>3.62423253059387</v>
       </c>
       <c r="H1645" t="n">
         <v>21464</v>
@@ -48103,7 +48103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1646" t="n">
         <v>14045</v>
@@ -48132,7 +48132,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.62423229217529</v>
+        <v>3.62423253059387</v>
       </c>
       <c r="H1647" t="n">
         <v>21215</v>
@@ -48161,7 +48161,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.62423229217529</v>
+        <v>3.62423253059387</v>
       </c>
       <c r="H1648" t="n">
         <v>1946</v>
@@ -48248,7 +48248,7 @@
         <v>3.75</v>
       </c>
       <c r="G1651" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1651" t="n">
         <v>20515</v>
@@ -48277,7 +48277,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1652" t="n">
         <v>46459</v>
@@ -48306,7 +48306,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1653" t="n">
-        <v>3.62423229217529</v>
+        <v>3.62423253059387</v>
       </c>
       <c r="H1653" t="n">
         <v>59408</v>
@@ -48335,7 +48335,7 @@
         <v>3.75</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1654" t="n">
         <v>12044</v>
@@ -48422,7 +48422,7 @@
         <v>3.75</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1657" t="n">
         <v>24610</v>
@@ -48596,7 +48596,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.52835321426392</v>
+        <v>3.5283534526825</v>
       </c>
       <c r="H1663" t="n">
         <v>3365</v>
@@ -48770,7 +48770,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1669" t="n">
-        <v>3.47082614898682</v>
+        <v>3.47082591056824</v>
       </c>
       <c r="H1669" t="n">
         <v>5678</v>
@@ -49118,7 +49118,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.50917744636536</v>
+        <v>3.50917768478394</v>
       </c>
       <c r="H1681" t="n">
         <v>9346</v>
@@ -49147,7 +49147,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.47082614898682</v>
+        <v>3.47082591056824</v>
       </c>
       <c r="H1682" t="n">
         <v>2125</v>
@@ -49234,7 +49234,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.40371060371399</v>
+        <v>3.40371036529541</v>
       </c>
       <c r="H1685" t="n">
         <v>8275</v>
@@ -49292,7 +49292,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.40371060371399</v>
+        <v>3.40371036529541</v>
       </c>
       <c r="H1687" t="n">
         <v>26057</v>
@@ -49408,7 +49408,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.47082614898682</v>
+        <v>3.47082591056824</v>
       </c>
       <c r="H1691" t="n">
         <v>24178</v>
@@ -49495,7 +49495,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.47082614898682</v>
+        <v>3.47082591056824</v>
       </c>
       <c r="H1694" t="n">
         <v>23089</v>
@@ -49756,7 +49756,7 @@
         <v>3.75</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1703" t="n">
         <v>73879</v>
@@ -49785,7 +49785,7 @@
         <v>3.75</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.59546875953674</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1704" t="n">
         <v>42320</v>
@@ -49843,7 +49843,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1706" t="n">
         <v>4431</v>
@@ -49872,7 +49872,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1707" t="n">
         <v>18328</v>
@@ -49901,7 +49901,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1708" t="n">
         <v>32895</v>
@@ -49930,7 +49930,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1709" t="n">
         <v>23972</v>
@@ -49959,7 +49959,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1710" t="n">
         <v>86187</v>
@@ -49988,7 +49988,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1711" t="n">
         <v>61901</v>
@@ -50075,7 +50075,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.62423229217529</v>
+        <v>3.62423253059387</v>
       </c>
       <c r="H1714" t="n">
         <v>20044</v>
@@ -50162,7 +50162,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.64340853691101</v>
+        <v>3.64340829849243</v>
       </c>
       <c r="H1717" t="n">
         <v>83866</v>
@@ -50278,7 +50278,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.50917744636536</v>
+        <v>3.50917768478394</v>
       </c>
       <c r="H1721" t="n">
         <v>5530</v>
@@ -67916,6 +67916,35 @@
         <v>37246</v>
       </c>
       <c r="I2329" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2330" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2330" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="G2330" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="H2330" t="n">
+        <v>37452</v>
+      </c>
+      <c r="I2330" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BFG.MI.xlsx
+++ b/data/BFG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26328444480896</v>
+        <v>2.2632839679718</v>
       </c>
       <c r="H2" t="n">
         <v>10031</v>
@@ -456,7 +456,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G3" t="n">
-        <v>2.27264428138733</v>
+        <v>2.27264451980591</v>
       </c>
       <c r="H3" t="n">
         <v>300</v>
@@ -514,7 +514,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H5" t="n">
         <v>15210</v>
@@ -543,7 +543,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26328444480896</v>
+        <v>2.2632839679718</v>
       </c>
       <c r="H6" t="n">
         <v>636</v>
@@ -572,7 +572,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26328444480896</v>
+        <v>2.2632839679718</v>
       </c>
       <c r="H7" t="n">
         <v>6476</v>
@@ -601,7 +601,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H8" t="n">
         <v>391</v>
@@ -630,7 +630,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H12" t="n">
         <v>1375</v>
@@ -746,7 +746,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H13" t="n">
         <v>2279</v>
@@ -833,7 +833,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H16" t="n">
         <v>1501</v>
@@ -949,7 +949,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G20" t="n">
-        <v>2.27264428138733</v>
+        <v>2.27264451980591</v>
       </c>
       <c r="H20" t="n">
         <v>18228</v>
@@ -1007,7 +1007,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G22" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H22" t="n">
         <v>4060</v>
@@ -1036,7 +1036,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G23" t="n">
-        <v>2.25392436981201</v>
+        <v>2.25392389297485</v>
       </c>
       <c r="H23" t="n">
         <v>1353</v>
@@ -1065,7 +1065,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>2.24456405639648</v>
+        <v>2.24456357955933</v>
       </c>
       <c r="H24" t="n">
         <v>9501</v>
@@ -1094,7 +1094,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G25" t="n">
-        <v>2.24269151687622</v>
+        <v>2.2426917552948</v>
       </c>
       <c r="H25" t="n">
         <v>7695</v>
@@ -1123,7 +1123,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2894926071167</v>
+        <v>2.28949308395386</v>
       </c>
       <c r="H26" t="n">
         <v>6193</v>
@@ -1181,7 +1181,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G28" t="n">
-        <v>2.24456405639648</v>
+        <v>2.24456357955933</v>
       </c>
       <c r="H28" t="n">
         <v>17543</v>
@@ -1268,7 +1268,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>2.27264428138733</v>
+        <v>2.27264451980591</v>
       </c>
       <c r="H31" t="n">
         <v>47973</v>
@@ -1413,7 +1413,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G36" t="n">
-        <v>2.2969810962677</v>
+        <v>2.29698061943054</v>
       </c>
       <c r="H36" t="n">
         <v>3211</v>
@@ -1442,7 +1442,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H37" t="n">
         <v>14451</v>
@@ -1500,7 +1500,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G39" t="n">
-        <v>2.3082127571106</v>
+        <v>2.30821323394775</v>
       </c>
       <c r="H39" t="n">
         <v>1002</v>
@@ -1674,7 +1674,7 @@
         <v>2.5</v>
       </c>
       <c r="G45" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H45" t="n">
         <v>11774</v>
@@ -1703,7 +1703,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28574872016907</v>
+        <v>2.28574848175049</v>
       </c>
       <c r="H46" t="n">
         <v>8211</v>
@@ -1790,7 +1790,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G49" t="n">
-        <v>2.35688543319702</v>
+        <v>2.3568856716156</v>
       </c>
       <c r="H49" t="n">
         <v>17001</v>
@@ -1819,7 +1819,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G50" t="n">
-        <v>2.38122200965881</v>
+        <v>2.38122177124023</v>
       </c>
       <c r="H50" t="n">
         <v>9851</v>
@@ -1877,7 +1877,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G52" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H52" t="n">
         <v>8357</v>
@@ -1906,7 +1906,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G53" t="n">
-        <v>2.37934970855713</v>
+        <v>2.37935018539429</v>
       </c>
       <c r="H53" t="n">
         <v>10960</v>
@@ -1935,7 +1935,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G54" t="n">
-        <v>2.37934970855713</v>
+        <v>2.37935018539429</v>
       </c>
       <c r="H54" t="n">
         <v>18299</v>
@@ -1964,7 +1964,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H55" t="n">
         <v>1111</v>
@@ -1993,7 +1993,7 @@
         <v>2.5</v>
       </c>
       <c r="G56" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H56" t="n">
         <v>4388</v>
@@ -2022,7 +2022,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G57" t="n">
-        <v>2.33442139625549</v>
+        <v>2.33442115783691</v>
       </c>
       <c r="H57" t="n">
         <v>1778</v>
@@ -2051,7 +2051,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G58" t="n">
-        <v>2.33442139625549</v>
+        <v>2.33442115783691</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G59" t="n">
-        <v>2.33442139625549</v>
+        <v>2.33442115783691</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G61" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H61" t="n">
         <v>66171</v>
@@ -2196,7 +2196,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H63" t="n">
         <v>38621</v>
@@ -2225,7 +2225,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G64" t="n">
-        <v>2.25954008102417</v>
+        <v>2.25954031944275</v>
       </c>
       <c r="H64" t="n">
         <v>5491</v>
@@ -2312,7 +2312,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G67" t="n">
-        <v>2.26328444480896</v>
+        <v>2.2632839679718</v>
       </c>
       <c r="H67" t="n">
         <v>68930</v>
@@ -2341,7 +2341,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H68" t="n">
         <v>14180</v>
@@ -2370,7 +2370,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G69" t="n">
-        <v>2.28574872016907</v>
+        <v>2.28574848175049</v>
       </c>
       <c r="H69" t="n">
         <v>262</v>
@@ -2399,7 +2399,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G70" t="n">
-        <v>2.2969810962677</v>
+        <v>2.29698061943054</v>
       </c>
       <c r="H70" t="n">
         <v>1875</v>
@@ -2428,7 +2428,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G71" t="n">
-        <v>2.28762078285217</v>
+        <v>2.28762054443359</v>
       </c>
       <c r="H71" t="n">
         <v>252</v>
@@ -2457,7 +2457,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G72" t="n">
-        <v>2.30446910858154</v>
+        <v>2.30446887016296</v>
       </c>
       <c r="H72" t="n">
         <v>5916</v>
@@ -2486,7 +2486,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G73" t="n">
-        <v>2.29136443138123</v>
+        <v>2.29136490821838</v>
       </c>
       <c r="H73" t="n">
         <v>1111</v>
@@ -2515,7 +2515,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G74" t="n">
-        <v>2.2894926071167</v>
+        <v>2.28949308395386</v>
       </c>
       <c r="H74" t="n">
         <v>6964</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H75" t="n">
         <v>57801</v>
@@ -2573,7 +2573,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G76" t="n">
-        <v>2.3175733089447</v>
+        <v>2.31757307052612</v>
       </c>
       <c r="H76" t="n">
         <v>4672</v>
@@ -2631,7 +2631,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G78" t="n">
-        <v>2.34565329551697</v>
+        <v>2.34565353393555</v>
       </c>
       <c r="H78" t="n">
         <v>1261</v>
@@ -2660,7 +2660,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G79" t="n">
-        <v>2.34752559661865</v>
+        <v>2.34752535820007</v>
       </c>
       <c r="H79" t="n">
         <v>3112</v>
@@ -2689,7 +2689,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G80" t="n">
-        <v>2.3381655216217</v>
+        <v>2.33816528320312</v>
       </c>
       <c r="H80" t="n">
         <v>19198</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H81" t="n">
         <v>20012</v>
@@ -2776,7 +2776,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G83" t="n">
-        <v>2.32506132125854</v>
+        <v>2.32506108283997</v>
       </c>
       <c r="H83" t="n">
         <v>2024</v>
@@ -2834,7 +2834,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G85" t="n">
-        <v>2.33629369735718</v>
+        <v>2.3362934589386</v>
       </c>
       <c r="H85" t="n">
         <v>1012</v>
@@ -2892,7 +2892,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H87" t="n">
         <v>13036</v>
@@ -2921,7 +2921,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G88" t="n">
-        <v>2.3082127571106</v>
+        <v>2.30821323394775</v>
       </c>
       <c r="H88" t="n">
         <v>27925</v>
@@ -2950,7 +2950,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G89" t="n">
-        <v>2.30446910858154</v>
+        <v>2.30446887016296</v>
       </c>
       <c r="H89" t="n">
         <v>5068</v>
@@ -2979,7 +2979,7 @@
         <v>2.5</v>
       </c>
       <c r="G90" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H90" t="n">
         <v>13853</v>
@@ -3008,7 +3008,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>2.32693314552307</v>
+        <v>2.32693338394165</v>
       </c>
       <c r="H91" t="n">
         <v>5575</v>
@@ -3037,7 +3037,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G92" t="n">
-        <v>2.31382894515991</v>
+        <v>2.31382870674133</v>
       </c>
       <c r="H92" t="n">
         <v>9404</v>
@@ -3211,7 +3211,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G98" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H98" t="n">
         <v>20172</v>
@@ -3269,7 +3269,7 @@
         <v>2.5</v>
       </c>
       <c r="G100" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H100" t="n">
         <v>6572</v>
@@ -3298,7 +3298,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G101" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H101" t="n">
         <v>4650</v>
@@ -3327,7 +3327,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H102" t="n">
         <v>8000</v>
@@ -3356,7 +3356,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G103" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.5</v>
       </c>
       <c r="G104" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H104" t="n">
         <v>12001</v>
@@ -3443,7 +3443,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G106" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H106" t="n">
         <v>3950</v>
@@ -3530,7 +3530,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G109" t="n">
-        <v>2.42427849769592</v>
+        <v>2.4242787361145</v>
       </c>
       <c r="H109" t="n">
         <v>51270</v>
@@ -3559,7 +3559,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.48980021476746</v>
+        <v>2.48979997634888</v>
       </c>
       <c r="H110" t="n">
         <v>36853</v>
@@ -3588,7 +3588,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G111" t="n">
-        <v>2.5178804397583</v>
+        <v>2.51788067817688</v>
       </c>
       <c r="H111" t="n">
         <v>50415</v>
@@ -3646,7 +3646,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>2.5178804397583</v>
+        <v>2.51788067817688</v>
       </c>
       <c r="H113" t="n">
         <v>61120</v>
@@ -3675,7 +3675,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>2.59276127815247</v>
+        <v>2.59276151657104</v>
       </c>
       <c r="H114" t="n">
         <v>106846</v>
@@ -3704,7 +3704,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G115" t="n">
-        <v>2.59276127815247</v>
+        <v>2.59276151657104</v>
       </c>
       <c r="H115" t="n">
         <v>42848</v>
@@ -3733,7 +3733,7 @@
         <v>2.75</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57404112815857</v>
+        <v>2.57404088973999</v>
       </c>
       <c r="H116" t="n">
         <v>27141</v>
@@ -3791,7 +3791,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>2.53660082817078</v>
+        <v>2.5366005897522</v>
       </c>
       <c r="H118" t="n">
         <v>26180</v>
@@ -3820,7 +3820,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G119" t="n">
-        <v>2.54596090316772</v>
+        <v>2.54596066474915</v>
       </c>
       <c r="H119" t="n">
         <v>17929</v>
@@ -3878,7 +3878,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>2.53660082817078</v>
+        <v>2.5366005897522</v>
       </c>
       <c r="H121" t="n">
         <v>26346</v>
@@ -3907,7 +3907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H122" t="n">
         <v>27237</v>
@@ -3936,7 +3936,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.53660082817078</v>
+        <v>2.5366005897522</v>
       </c>
       <c r="H123" t="n">
         <v>26213</v>
@@ -3965,7 +3965,7 @@
         <v>2.75</v>
       </c>
       <c r="G124" t="n">
-        <v>2.57404112815857</v>
+        <v>2.57404088973999</v>
       </c>
       <c r="H124" t="n">
         <v>52662</v>
@@ -4023,7 +4023,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="n">
-        <v>2.57404112815857</v>
+        <v>2.57404088973999</v>
       </c>
       <c r="H126" t="n">
         <v>5270</v>
@@ -4110,7 +4110,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H129" t="n">
         <v>42756</v>
@@ -4139,7 +4139,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H135" t="n">
         <v>11472</v>
@@ -4313,7 +4313,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H136" t="n">
         <v>1076</v>
@@ -4342,7 +4342,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G137" t="n">
-        <v>2.4523594379425</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H137" t="n">
         <v>6677</v>
@@ -4371,7 +4371,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>2.41491889953613</v>
+        <v>2.4149181842804</v>
       </c>
       <c r="H138" t="n">
         <v>10600</v>
@@ -4400,7 +4400,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G139" t="n">
-        <v>2.41491889953613</v>
+        <v>2.4149181842804</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>2.5178804397583</v>
+        <v>2.51788067817688</v>
       </c>
       <c r="H143" t="n">
         <v>5968</v>
@@ -4574,7 +4574,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H145" t="n">
         <v>5650</v>
@@ -4632,7 +4632,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>2.41491889953613</v>
+        <v>2.4149181842804</v>
       </c>
       <c r="H147" t="n">
         <v>25743</v>
@@ -4661,7 +4661,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G148" t="n">
-        <v>2.42427849769592</v>
+        <v>2.4242787361145</v>
       </c>
       <c r="H148" t="n">
         <v>2641</v>
@@ -4690,7 +4690,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.42427849769592</v>
+        <v>2.4242787361145</v>
       </c>
       <c r="H149" t="n">
         <v>7041</v>
@@ -4719,7 +4719,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H150" t="n">
         <v>20582</v>
@@ -4748,7 +4748,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H151" t="n">
         <v>2337</v>
@@ -4893,7 +4893,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H156" t="n">
         <v>2000</v>
@@ -4922,7 +4922,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G157" t="n">
-        <v>2.4523594379425</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H157" t="n">
         <v>5630</v>
@@ -4980,7 +4980,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G159" t="n">
-        <v>2.4523594379425</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H159" t="n">
         <v>960</v>
@@ -5009,7 +5009,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H160" t="n">
         <v>4282</v>
@@ -5038,7 +5038,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H161" t="n">
         <v>13050</v>
@@ -5096,7 +5096,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>2.4523594379425</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H163" t="n">
         <v>4386</v>
@@ -5125,7 +5125,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H164" t="n">
         <v>9227</v>
@@ -5241,7 +5241,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H168" t="n">
         <v>3544</v>
@@ -5299,7 +5299,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H170" t="n">
         <v>20489</v>
@@ -5328,7 +5328,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H171" t="n">
         <v>27524</v>
@@ -5357,7 +5357,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H172" t="n">
         <v>7001</v>
@@ -5415,7 +5415,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H174" t="n">
         <v>13277</v>
@@ -5444,7 +5444,7 @@
         <v>2.5</v>
       </c>
       <c r="G175" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H175" t="n">
         <v>8881</v>
@@ -5502,7 +5502,7 @@
         <v>2.5</v>
       </c>
       <c r="G177" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H177" t="n">
         <v>659</v>
@@ -5560,7 +5560,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G179" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H179" t="n">
         <v>11740</v>
@@ -5589,7 +5589,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H180" t="n">
         <v>22206</v>
@@ -5618,7 +5618,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H181" t="n">
         <v>2611</v>
@@ -5647,7 +5647,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G182" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H182" t="n">
         <v>3080</v>
@@ -5734,7 +5734,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H185" t="n">
         <v>18400</v>
@@ -5792,7 +5792,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G187" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H187" t="n">
         <v>2702</v>
@@ -5821,7 +5821,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G188" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H188" t="n">
         <v>3100</v>
@@ -5879,7 +5879,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H190" t="n">
         <v>4060</v>
@@ -5908,7 +5908,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H195" t="n">
         <v>4023</v>
@@ -6053,7 +6053,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H196" t="n">
         <v>11000</v>
@@ -6111,7 +6111,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H198" t="n">
         <v>5503</v>
@@ -6169,7 +6169,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H200" t="n">
         <v>16425</v>
@@ -6372,7 +6372,7 @@
         <v>2.5</v>
       </c>
       <c r="G207" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H207" t="n">
         <v>27406</v>
@@ -6430,7 +6430,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G209" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H209" t="n">
         <v>33132</v>
@@ -6517,7 +6517,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G212" t="n">
-        <v>2.4523594379425</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H212" t="n">
         <v>9809</v>
@@ -6546,7 +6546,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H213" t="n">
         <v>19323</v>
@@ -6633,7 +6633,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H216" t="n">
         <v>31305</v>
@@ -6662,7 +6662,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>2.48043966293335</v>
+        <v>2.48043990135193</v>
       </c>
       <c r="H217" t="n">
         <v>40160</v>
@@ -6691,7 +6691,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H218" t="n">
         <v>33581</v>
@@ -6865,7 +6865,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>2.46171951293945</v>
+        <v>2.46171975135803</v>
       </c>
       <c r="H224" t="n">
         <v>29057</v>
@@ -6894,7 +6894,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>2.41491889953613</v>
+        <v>2.4149181842804</v>
       </c>
       <c r="H225" t="n">
         <v>44619</v>
@@ -6923,7 +6923,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42427849769592</v>
+        <v>2.4242787361145</v>
       </c>
       <c r="H226" t="n">
         <v>4912</v>
@@ -6952,7 +6952,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H227" t="n">
         <v>42691</v>
@@ -6981,7 +6981,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H228" t="n">
         <v>25643</v>
@@ -7010,7 +7010,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>2.18091487884521</v>
+        <v>2.18091440200806</v>
       </c>
       <c r="H229" t="n">
         <v>20208</v>
@@ -7039,7 +7039,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.19963526725769</v>
+        <v>2.19963502883911</v>
       </c>
       <c r="H230" t="n">
         <v>39029</v>
@@ -7068,7 +7068,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>2.18091487884521</v>
+        <v>2.18091440200806</v>
       </c>
       <c r="H231" t="n">
         <v>3460</v>
@@ -7126,7 +7126,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>2.19963526725769</v>
+        <v>2.19963502883911</v>
       </c>
       <c r="H233" t="n">
         <v>3826</v>
@@ -7155,7 +7155,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.19963526725769</v>
+        <v>2.19963502883911</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G236" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H236" t="n">
         <v>12937</v>
@@ -7329,7 +7329,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H240" t="n">
         <v>4063</v>
@@ -7358,7 +7358,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H241" t="n">
         <v>6461</v>
@@ -7416,7 +7416,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G243" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H243" t="n">
         <v>16665</v>
@@ -7503,7 +7503,7 @@
         <v>2.5</v>
       </c>
       <c r="G246" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H246" t="n">
         <v>11889</v>
@@ -7532,7 +7532,7 @@
         <v>2.5</v>
       </c>
       <c r="G247" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H247" t="n">
         <v>14306</v>
@@ -7590,7 +7590,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H249" t="n">
         <v>9734</v>
@@ -7619,7 +7619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H250" t="n">
         <v>2000</v>
@@ -7648,7 +7648,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H251" t="n">
         <v>8381</v>
@@ -7677,7 +7677,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G252" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H252" t="n">
         <v>11500</v>
@@ -7706,7 +7706,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H253" t="n">
         <v>13809</v>
@@ -7735,7 +7735,7 @@
         <v>2.5</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H254" t="n">
         <v>5409</v>
@@ -7764,7 +7764,7 @@
         <v>2.5</v>
       </c>
       <c r="G255" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H255" t="n">
         <v>2978</v>
@@ -7793,7 +7793,7 @@
         <v>2.5</v>
       </c>
       <c r="G256" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H256" t="n">
         <v>3000</v>
@@ -7822,7 +7822,7 @@
         <v>2.5</v>
       </c>
       <c r="G257" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2.5</v>
       </c>
       <c r="G258" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H258" t="n">
         <v>2000</v>
@@ -7880,7 +7880,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G259" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H259" t="n">
         <v>14470</v>
@@ -7938,7 +7938,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H261" t="n">
         <v>11788</v>
@@ -7967,7 +7967,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G262" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H262" t="n">
         <v>28296</v>
@@ -7996,7 +7996,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H263" t="n">
         <v>28276</v>
@@ -8112,7 +8112,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H267" t="n">
         <v>506</v>
@@ -8141,7 +8141,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H268" t="n">
         <v>293</v>
@@ -8170,7 +8170,7 @@
         <v>2.5</v>
       </c>
       <c r="G269" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H269" t="n">
         <v>2669</v>
@@ -8199,7 +8199,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H270" t="n">
         <v>22</v>
@@ -8402,7 +8402,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H277" t="n">
         <v>51182</v>
@@ -8489,7 +8489,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H280" t="n">
         <v>29015</v>
@@ -8518,7 +8518,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H281" t="n">
         <v>16267</v>
@@ -8663,7 +8663,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G286" t="n">
-        <v>2.17155432701111</v>
+        <v>2.17155480384827</v>
       </c>
       <c r="H286" t="n">
         <v>19722</v>
@@ -8692,7 +8692,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>2.14347457885742</v>
+        <v>2.14347434043884</v>
       </c>
       <c r="H287" t="n">
         <v>17670</v>
@@ -8750,7 +8750,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G289" t="n">
-        <v>2.0405125617981</v>
+        <v>2.04051280021667</v>
       </c>
       <c r="H289" t="n">
         <v>300073</v>
@@ -8779,7 +8779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>1.94691133499146</v>
+        <v>1.94691097736359</v>
       </c>
       <c r="H290" t="n">
         <v>57032</v>
@@ -8866,7 +8866,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>2.19963526725769</v>
+        <v>2.19963502883911</v>
       </c>
       <c r="H293" t="n">
         <v>125654</v>
@@ -8895,7 +8895,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H294" t="n">
         <v>39628</v>
@@ -8982,7 +8982,7 @@
         <v>2.5</v>
       </c>
       <c r="G297" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H297" t="n">
         <v>60070</v>
@@ -9214,7 +9214,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G305" t="n">
-        <v>2.17155432701111</v>
+        <v>2.17155480384827</v>
       </c>
       <c r="H305" t="n">
         <v>9053</v>
@@ -9301,7 +9301,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H308" t="n">
         <v>64204</v>
@@ -9388,7 +9388,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H311" t="n">
         <v>10160</v>
@@ -9475,7 +9475,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H314" t="n">
         <v>8050</v>
@@ -9504,7 +9504,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H315" t="n">
         <v>2482</v>
@@ -9533,7 +9533,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H316" t="n">
         <v>750</v>
@@ -9562,7 +9562,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H317" t="n">
         <v>25860</v>
@@ -9591,7 +9591,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>2.19963526725769</v>
+        <v>2.19963502883911</v>
       </c>
       <c r="H318" t="n">
         <v>37670</v>
@@ -9649,7 +9649,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G320" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H320" t="n">
         <v>47122</v>
@@ -9852,7 +9852,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H327" t="n">
         <v>10324</v>
@@ -9881,7 +9881,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H328" t="n">
         <v>28956</v>
@@ -10026,7 +10026,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H333" t="n">
         <v>27881</v>
@@ -10055,7 +10055,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H334" t="n">
         <v>22010</v>
@@ -10113,7 +10113,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G336" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H336" t="n">
         <v>7485</v>
@@ -10142,7 +10142,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G337" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H337" t="n">
         <v>11056</v>
@@ -10229,7 +10229,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H340" t="n">
         <v>55271</v>
@@ -10258,7 +10258,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H341" t="n">
         <v>11651</v>
@@ -10287,7 +10287,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H342" t="n">
         <v>74958</v>
@@ -10374,7 +10374,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H345" t="n">
         <v>7860</v>
@@ -10461,7 +10461,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G348" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H348" t="n">
         <v>30033</v>
@@ -10519,7 +10519,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H350" t="n">
         <v>7329</v>
@@ -10548,7 +10548,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H351" t="n">
         <v>64218</v>
@@ -10693,7 +10693,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G356" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H356" t="n">
         <v>8330</v>
@@ -10722,7 +10722,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G357" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H357" t="n">
         <v>38546</v>
@@ -10809,7 +10809,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H360" t="n">
         <v>55919</v>
@@ -10838,7 +10838,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G361" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H361" t="n">
         <v>4891</v>
@@ -10867,7 +10867,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G362" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G364" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H364" t="n">
         <v>3090</v>
@@ -10954,7 +10954,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G365" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H367" t="n">
         <v>11034</v>
@@ -11099,7 +11099,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G370" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H371" t="n">
         <v>2249</v>
@@ -11157,7 +11157,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H372" t="n">
         <v>1750</v>
@@ -11186,7 +11186,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G374" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H374" t="n">
         <v>4700</v>
@@ -11244,7 +11244,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H376" t="n">
         <v>4839</v>
@@ -11302,7 +11302,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19027495384216</v>
+        <v>2.19027519226074</v>
       </c>
       <c r="H377" t="n">
         <v>50859</v>
@@ -11331,7 +11331,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G378" t="n">
-        <v>2.19027495384216</v>
+        <v>2.19027519226074</v>
       </c>
       <c r="H378" t="n">
         <v>13060</v>
@@ -11360,7 +11360,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G379" t="n">
-        <v>2.19027495384216</v>
+        <v>2.19027519226074</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G380" t="n">
-        <v>2.19027495384216</v>
+        <v>2.19027519226074</v>
       </c>
       <c r="H380" t="n">
         <v>250</v>
@@ -11447,7 +11447,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G382" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H382" t="n">
         <v>4930</v>
@@ -11476,7 +11476,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G385" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H385" t="n">
         <v>14724</v>
@@ -11708,7 +11708,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H391" t="n">
         <v>4002</v>
@@ -11795,7 +11795,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G394" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -11824,7 +11824,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G395" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H395" t="n">
         <v>37806</v>
@@ -11882,7 +11882,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G397" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H397" t="n">
         <v>27047</v>
@@ -11911,7 +11911,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H398" t="n">
         <v>46985</v>
@@ -11969,7 +11969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G400" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H400" t="n">
         <v>38756</v>
@@ -12143,7 +12143,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H406" t="n">
         <v>2775</v>
@@ -12172,7 +12172,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G407" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H407" t="n">
         <v>5002</v>
@@ -12230,7 +12230,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H409" t="n">
         <v>2100</v>
@@ -12288,7 +12288,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G411" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H411" t="n">
         <v>3200</v>
@@ -12317,7 +12317,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H412" t="n">
         <v>4500</v>
@@ -12346,7 +12346,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H413" t="n">
         <v>135</v>
@@ -12375,7 +12375,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H414" t="n">
         <v>7069</v>
@@ -12404,7 +12404,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G415" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H415" t="n">
         <v>25926</v>
@@ -12433,7 +12433,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G416" t="n">
-        <v>2.24643588066101</v>
+        <v>2.24643611907959</v>
       </c>
       <c r="H416" t="n">
         <v>6504</v>
@@ -12578,7 +12578,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G421" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H421" t="n">
         <v>45993</v>
@@ -12607,7 +12607,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H422" t="n">
         <v>108321</v>
@@ -12665,7 +12665,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G424" t="n">
-        <v>2.42427849769592</v>
+        <v>2.4242787361145</v>
       </c>
       <c r="H424" t="n">
         <v>51683</v>
@@ -12694,7 +12694,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.4523594379425</v>
+        <v>2.45235919952393</v>
       </c>
       <c r="H425" t="n">
         <v>151198</v>
@@ -12752,7 +12752,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.41491889953613</v>
+        <v>2.4149181842804</v>
       </c>
       <c r="H427" t="n">
         <v>18500</v>
@@ -12781,7 +12781,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H428" t="n">
         <v>27357</v>
@@ -12868,7 +12868,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G431" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H431" t="n">
         <v>5751</v>
@@ -12897,7 +12897,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G432" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H432" t="n">
         <v>13150</v>
@@ -12926,7 +12926,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G433" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H433" t="n">
         <v>5600</v>
@@ -13100,7 +13100,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G439" t="n">
-        <v>2.23707628250122</v>
+        <v>2.23707580566406</v>
       </c>
       <c r="H439" t="n">
         <v>4275</v>
@@ -13187,7 +13187,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.28387641906738</v>
+        <v>2.28387665748596</v>
       </c>
       <c r="H442" t="n">
         <v>100</v>
@@ -13216,7 +13216,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G443" t="n">
-        <v>2.25579595565796</v>
+        <v>2.25579619407654</v>
       </c>
       <c r="H443" t="n">
         <v>600</v>
@@ -13245,7 +13245,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G444" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H444" t="n">
         <v>12469</v>
@@ -13274,7 +13274,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.31195735931396</v>
+        <v>2.31195712089539</v>
       </c>
       <c r="H445" t="n">
         <v>531</v>
@@ -13332,7 +13332,7 @@
         <v>2.5</v>
       </c>
       <c r="G447" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H447" t="n">
         <v>39433</v>
@@ -13361,7 +13361,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H448" t="n">
         <v>1564637</v>
@@ -13390,7 +13390,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G449" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H449" t="n">
         <v>142747</v>
@@ -13448,7 +13448,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G451" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H451" t="n">
         <v>25684</v>
@@ -13477,7 +13477,7 @@
         <v>2.5</v>
       </c>
       <c r="G452" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H452" t="n">
         <v>28935</v>
@@ -13564,7 +13564,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G455" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H455" t="n">
         <v>148756</v>
@@ -13593,7 +13593,7 @@
         <v>2.5</v>
       </c>
       <c r="G456" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H456" t="n">
         <v>7855</v>
@@ -13622,7 +13622,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H457" t="n">
         <v>2289</v>
@@ -13796,7 +13796,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H463" t="n">
         <v>33833</v>
@@ -13825,7 +13825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G464" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H464" t="n">
         <v>15150</v>
@@ -13854,7 +13854,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H465" t="n">
         <v>55480</v>
@@ -13883,7 +13883,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H466" t="n">
         <v>32485</v>
@@ -13912,7 +13912,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G467" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H467" t="n">
         <v>5472</v>
@@ -13941,7 +13941,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G468" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H468" t="n">
         <v>44500</v>
@@ -13999,7 +13999,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G470" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H470" t="n">
         <v>4743</v>
@@ -14028,7 +14028,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>2.41491889953613</v>
+        <v>2.4149181842804</v>
       </c>
       <c r="H471" t="n">
         <v>36681</v>
@@ -14115,7 +14115,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G474" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H474" t="n">
         <v>15848</v>
@@ -14202,7 +14202,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>2.41491889953613</v>
+        <v>2.4149181842804</v>
       </c>
       <c r="H477" t="n">
         <v>2438</v>
@@ -14231,7 +14231,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G478" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H478" t="n">
         <v>22406</v>
@@ -14289,7 +14289,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H480" t="n">
         <v>33896</v>
@@ -14376,7 +14376,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>2.36811828613281</v>
+        <v>2.36811804771423</v>
       </c>
       <c r="H483" t="n">
         <v>2700</v>
@@ -14405,7 +14405,7 @@
         <v>2.5</v>
       </c>
       <c r="G484" t="n">
-        <v>2.34003710746765</v>
+        <v>2.34003758430481</v>
       </c>
       <c r="H484" t="n">
         <v>8800</v>
@@ -14434,7 +14434,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.34939789772034</v>
+        <v>2.34939742088318</v>
       </c>
       <c r="H485" t="n">
         <v>5500</v>
@@ -14521,7 +14521,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H488" t="n">
         <v>67898</v>
@@ -14608,7 +14608,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H491" t="n">
         <v>8000</v>
@@ -14637,7 +14637,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.3774778842926</v>
+        <v>2.37747812271118</v>
       </c>
       <c r="H493" t="n">
         <v>8491</v>
@@ -14695,7 +14695,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G494" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H494" t="n">
         <v>6500</v>
@@ -14753,7 +14753,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G496" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H496" t="n">
         <v>5000</v>
@@ -14782,7 +14782,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G497" t="n">
-        <v>2.40555858612061</v>
+        <v>2.40555834770203</v>
       </c>
       <c r="H497" t="n">
         <v>26080</v>
@@ -14840,7 +14840,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.38683819770813</v>
+        <v>2.38683843612671</v>
       </c>
       <c r="H499" t="n">
         <v>12500</v>
@@ -14898,7 +14898,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.62084221839905</v>
+        <v>2.62084197998047</v>
       </c>
       <c r="H501" t="n">
         <v>150283</v>
@@ -14985,7 +14985,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G504" t="n">
-        <v>2.54596090316772</v>
+        <v>2.54596066474915</v>
       </c>
       <c r="H504" t="n">
         <v>19600</v>
@@ -15072,7 +15072,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G507" t="n">
-        <v>2.56468105316162</v>
+        <v>2.56468081474304</v>
       </c>
       <c r="H507" t="n">
         <v>60564</v>
@@ -15130,7 +15130,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G509" t="n">
-        <v>2.63020181655884</v>
+        <v>2.63020205497742</v>
       </c>
       <c r="H509" t="n">
         <v>64049</v>
@@ -15159,7 +15159,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.66764259338379</v>
+        <v>2.66764211654663</v>
       </c>
       <c r="H510" t="n">
         <v>271086</v>
@@ -15188,7 +15188,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.75188398361206</v>
+        <v>2.75188422203064</v>
       </c>
       <c r="H511" t="n">
         <v>169365</v>
@@ -15246,7 +15246,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>2.78932499885559</v>
+        <v>2.78932452201843</v>
       </c>
       <c r="H513" t="n">
         <v>169395</v>
@@ -15275,7 +15275,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.78932499885559</v>
+        <v>2.78932452201843</v>
       </c>
       <c r="H514" t="n">
         <v>62277</v>
@@ -15304,7 +15304,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>2.78932499885559</v>
+        <v>2.78932452201843</v>
       </c>
       <c r="H515" t="n">
         <v>19300</v>
@@ -15449,7 +15449,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>2.78932499885559</v>
+        <v>2.78932452201843</v>
       </c>
       <c r="H520" t="n">
         <v>190831</v>
@@ -15478,7 +15478,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>2.79868483543396</v>
+        <v>2.79868459701538</v>
       </c>
       <c r="H521" t="n">
         <v>45690</v>
@@ -15565,7 +15565,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>2.75188398361206</v>
+        <v>2.75188422203064</v>
       </c>
       <c r="H524" t="n">
         <v>30994</v>
@@ -15623,7 +15623,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.79868483543396</v>
+        <v>2.79868459701538</v>
       </c>
       <c r="H526" t="n">
         <v>84209</v>
@@ -15652,7 +15652,7 @@
         <v>3</v>
       </c>
       <c r="G527" t="n">
-        <v>2.80804491043091</v>
+        <v>2.80804467201233</v>
       </c>
       <c r="H527" t="n">
         <v>20167</v>
@@ -15681,7 +15681,7 @@
         <v>3</v>
       </c>
       <c r="G528" t="n">
-        <v>2.80804491043091</v>
+        <v>2.80804467201233</v>
       </c>
       <c r="H528" t="n">
         <v>72688</v>
@@ -15710,7 +15710,7 @@
         <v>3</v>
       </c>
       <c r="G529" t="n">
-        <v>2.80804491043091</v>
+        <v>2.80804467201233</v>
       </c>
       <c r="H529" t="n">
         <v>28000</v>
@@ -15739,7 +15739,7 @@
         <v>3</v>
       </c>
       <c r="G530" t="n">
-        <v>2.80804491043091</v>
+        <v>2.80804467201233</v>
       </c>
       <c r="H530" t="n">
         <v>54379</v>
@@ -15768,7 +15768,7 @@
         <v>3</v>
       </c>
       <c r="G531" t="n">
-        <v>2.80804491043091</v>
+        <v>2.80804467201233</v>
       </c>
       <c r="H531" t="n">
         <v>45350</v>
@@ -15797,7 +15797,7 @@
         <v>3</v>
       </c>
       <c r="G532" t="n">
-        <v>2.80804491043091</v>
+        <v>2.80804467201233</v>
       </c>
       <c r="H532" t="n">
         <v>7510</v>
@@ -15826,7 +15826,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G533" t="n">
-        <v>2.82676553726196</v>
+        <v>2.82676482200623</v>
       </c>
       <c r="H533" t="n">
         <v>54489</v>
@@ -15855,7 +15855,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G534" t="n">
-        <v>2.91100668907166</v>
+        <v>2.91100645065308</v>
       </c>
       <c r="H534" t="n">
         <v>92567</v>
@@ -15884,7 +15884,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.89228630065918</v>
+        <v>2.89228653907776</v>
       </c>
       <c r="H535" t="n">
         <v>80894</v>
@@ -15971,7 +15971,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>3.06076908111572</v>
+        <v>3.06076884269714</v>
       </c>
       <c r="H538" t="n">
         <v>157375</v>
@@ -16000,7 +16000,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>3.0794894695282</v>
+        <v>3.07948899269104</v>
       </c>
       <c r="H539" t="n">
         <v>1328039</v>
@@ -16029,7 +16029,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>3.05140852928162</v>
+        <v>3.05140900611877</v>
       </c>
       <c r="H540" t="n">
         <v>79512</v>
@@ -16058,7 +16058,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>3.00460839271545</v>
+        <v>3.00460815429688</v>
       </c>
       <c r="H541" t="n">
         <v>75422</v>
@@ -16087,7 +16087,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>3.00460839271545</v>
+        <v>3.00460815429688</v>
       </c>
       <c r="H542" t="n">
         <v>37463</v>
@@ -16116,7 +16116,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>3.02332878112793</v>
+        <v>3.02332854270935</v>
       </c>
       <c r="H543" t="n">
         <v>44507</v>
@@ -16203,7 +16203,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G546" t="n">
-        <v>2.95780730247498</v>
+        <v>2.95780754089355</v>
       </c>
       <c r="H546" t="n">
         <v>49091</v>
@@ -16261,7 +16261,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>2.9203667640686</v>
+        <v>2.92036652565002</v>
       </c>
       <c r="H548" t="n">
         <v>203116</v>
@@ -16290,7 +16290,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.92972683906555</v>
+        <v>2.92972707748413</v>
       </c>
       <c r="H549" t="n">
         <v>73170</v>
@@ -16319,7 +16319,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G550" t="n">
-        <v>2.93908715248108</v>
+        <v>2.93908739089966</v>
       </c>
       <c r="H550" t="n">
         <v>20890</v>
@@ -16348,7 +16348,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.95780730247498</v>
+        <v>2.95780754089355</v>
       </c>
       <c r="H551" t="n">
         <v>54196</v>
@@ -16406,7 +16406,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>2.92972683906555</v>
+        <v>2.92972707748413</v>
       </c>
       <c r="H553" t="n">
         <v>156144</v>
@@ -16435,7 +16435,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G554" t="n">
-        <v>2.9203667640686</v>
+        <v>2.92036652565002</v>
       </c>
       <c r="H554" t="n">
         <v>80665</v>
@@ -16493,7 +16493,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>3.00460839271545</v>
+        <v>3.00460815429688</v>
       </c>
       <c r="H556" t="n">
         <v>375672</v>
@@ -16522,7 +16522,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>3.06076908111572</v>
+        <v>3.06076884269714</v>
       </c>
       <c r="H557" t="n">
         <v>65270</v>
@@ -16609,7 +16609,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G560" t="n">
-        <v>2.9203667640686</v>
+        <v>2.92036652565002</v>
       </c>
       <c r="H560" t="n">
         <v>113199</v>
@@ -16638,7 +16638,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G561" t="n">
-        <v>2.93908715248108</v>
+        <v>2.93908739089966</v>
       </c>
       <c r="H561" t="n">
         <v>60237</v>
@@ -16725,7 +16725,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>2.83612561225891</v>
+        <v>2.83612537384033</v>
       </c>
       <c r="H564" t="n">
         <v>116421</v>
@@ -16754,7 +16754,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.80804491043091</v>
+        <v>2.80804467201233</v>
       </c>
       <c r="H565" t="n">
         <v>83854</v>
@@ -16783,7 +16783,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>2.73316359519958</v>
+        <v>2.73316407203674</v>
       </c>
       <c r="H566" t="n">
         <v>267692</v>
@@ -16841,7 +16841,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>2.83612561225891</v>
+        <v>2.83612537384033</v>
       </c>
       <c r="H568" t="n">
         <v>219573</v>
@@ -16870,7 +16870,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>2.83612561225891</v>
+        <v>2.83612537384033</v>
       </c>
       <c r="H569" t="n">
         <v>281137</v>
@@ -16899,7 +16899,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>2.78932499885559</v>
+        <v>2.78932452201843</v>
       </c>
       <c r="H570" t="n">
         <v>78096</v>
@@ -16928,7 +16928,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G571" t="n">
-        <v>2.90164637565613</v>
+        <v>2.90164613723755</v>
       </c>
       <c r="H571" t="n">
         <v>199785</v>
@@ -16957,7 +16957,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.87356615066528</v>
+        <v>2.8735659122467</v>
       </c>
       <c r="H572" t="n">
         <v>336510</v>
@@ -17015,7 +17015,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G574" t="n">
-        <v>3.11692953109741</v>
+        <v>3.11692976951599</v>
       </c>
       <c r="H574" t="n">
         <v>360144</v>
@@ -17044,7 +17044,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G575" t="n">
-        <v>3.28541254997253</v>
+        <v>3.28541302680969</v>
       </c>
       <c r="H575" t="n">
         <v>655278</v>
@@ -17073,7 +17073,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G576" t="n">
-        <v>3.33221364021301</v>
+        <v>3.33221316337585</v>
       </c>
       <c r="H576" t="n">
         <v>274523</v>
@@ -17102,7 +17102,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>3.40709471702576</v>
+        <v>3.40709447860718</v>
       </c>
       <c r="H577" t="n">
         <v>229155</v>
@@ -17131,7 +17131,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="n">
-        <v>3.40709471702576</v>
+        <v>3.40709447860718</v>
       </c>
       <c r="H578" t="n">
         <v>68184</v>
@@ -17160,7 +17160,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G579" t="n">
-        <v>3.39773440361023</v>
+        <v>3.39773464202881</v>
       </c>
       <c r="H579" t="n">
         <v>74160</v>
@@ -17189,7 +17189,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G580" t="n">
-        <v>3.40709471702576</v>
+        <v>3.40709447860718</v>
       </c>
       <c r="H580" t="n">
         <v>160619</v>
@@ -17218,7 +17218,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>3.40709471702576</v>
+        <v>3.40709447860718</v>
       </c>
       <c r="H581" t="n">
         <v>41943</v>
@@ -17305,7 +17305,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>3.45389533042908</v>
+        <v>3.4538950920105</v>
       </c>
       <c r="H584" t="n">
         <v>150576</v>
@@ -17363,7 +17363,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G586" t="n">
-        <v>3.42581486701965</v>
+        <v>3.42581510543823</v>
       </c>
       <c r="H586" t="n">
         <v>29415</v>
@@ -17421,7 +17421,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G588" t="n">
-        <v>3.45389533042908</v>
+        <v>3.4538950920105</v>
       </c>
       <c r="H588" t="n">
         <v>37524</v>
@@ -17450,7 +17450,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G589" t="n">
-        <v>3.38837385177612</v>
+        <v>3.3883740901947</v>
       </c>
       <c r="H589" t="n">
         <v>37431</v>
@@ -17508,7 +17508,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G591" t="n">
-        <v>3.38837385177612</v>
+        <v>3.3883740901947</v>
       </c>
       <c r="H591" t="n">
         <v>140103</v>
@@ -17537,7 +17537,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>3.38837385177612</v>
+        <v>3.3883740901947</v>
       </c>
       <c r="H592" t="n">
         <v>48927</v>
@@ -17566,7 +17566,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G593" t="n">
-        <v>3.35093355178833</v>
+        <v>3.35093379020691</v>
       </c>
       <c r="H593" t="n">
         <v>34076</v>
@@ -17595,7 +17595,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>3.37901401519775</v>
+        <v>3.37901425361633</v>
       </c>
       <c r="H594" t="n">
         <v>41694</v>
@@ -17682,7 +17682,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>3.70661926269531</v>
+        <v>3.70661878585815</v>
       </c>
       <c r="H597" t="n">
         <v>36651</v>
@@ -17711,7 +17711,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G598" t="n">
-        <v>3.55685663223267</v>
+        <v>3.55685710906982</v>
       </c>
       <c r="H598" t="n">
         <v>19889</v>
@@ -17740,7 +17740,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G599" t="n">
-        <v>3.57557725906372</v>
+        <v>3.57557702064514</v>
       </c>
       <c r="H599" t="n">
         <v>37016</v>
@@ -17769,7 +17769,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G600" t="n">
-        <v>3.61301755905151</v>
+        <v>3.61301803588867</v>
       </c>
       <c r="H600" t="n">
         <v>72018</v>
@@ -17798,7 +17798,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>3.63173842430115</v>
+        <v>3.63173866271973</v>
       </c>
       <c r="H601" t="n">
         <v>91801</v>
@@ -17827,7 +17827,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G602" t="n">
-        <v>3.53813672065735</v>
+        <v>3.53813695907593</v>
       </c>
       <c r="H602" t="n">
         <v>26633</v>
@@ -17885,7 +17885,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.53813672065735</v>
+        <v>3.53813695907593</v>
       </c>
       <c r="H604" t="n">
         <v>8079</v>
@@ -17914,7 +17914,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48197603225708</v>
+        <v>3.48197555541992</v>
       </c>
       <c r="H605" t="n">
         <v>1648</v>
@@ -17943,7 +17943,7 @@
         <v>3.75</v>
       </c>
       <c r="G606" t="n">
-        <v>3.51005601882935</v>
+        <v>3.51005625724792</v>
       </c>
       <c r="H606" t="n">
         <v>27586</v>
@@ -17972,7 +17972,7 @@
         <v>3.75</v>
       </c>
       <c r="G607" t="n">
-        <v>3.51005601882935</v>
+        <v>3.51005625724792</v>
       </c>
       <c r="H607" t="n">
         <v>5945</v>
@@ -18059,7 +18059,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>3.47261548042297</v>
+        <v>3.47261524200439</v>
       </c>
       <c r="H610" t="n">
         <v>2001</v>
@@ -18117,7 +18117,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>3.38837385177612</v>
+        <v>3.3883740901947</v>
       </c>
       <c r="H612" t="n">
         <v>29302</v>
@@ -18146,7 +18146,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>3.40709471702576</v>
+        <v>3.40709447860718</v>
       </c>
       <c r="H613" t="n">
         <v>20068</v>
@@ -18175,7 +18175,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G614" t="n">
-        <v>3.40709471702576</v>
+        <v>3.40709447860718</v>
       </c>
       <c r="H614" t="n">
         <v>11798</v>
@@ -18233,7 +18233,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>3.34157299995422</v>
+        <v>3.34157347679138</v>
       </c>
       <c r="H616" t="n">
         <v>39898</v>
@@ -18262,7 +18262,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.60365748405457</v>
+        <v>3.60365772247314</v>
       </c>
       <c r="H617" t="n">
         <v>129761</v>
@@ -18291,7 +18291,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>3.66917896270752</v>
+        <v>3.66917872428894</v>
       </c>
       <c r="H618" t="n">
         <v>33184</v>
@@ -18378,7 +18378,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G621" t="n">
-        <v>3.57557725906372</v>
+        <v>3.57557702064514</v>
       </c>
       <c r="H621" t="n">
         <v>1414</v>
@@ -18436,7 +18436,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>3.35093355178833</v>
+        <v>3.35093379020691</v>
       </c>
       <c r="H623" t="n">
         <v>26603</v>
@@ -18465,7 +18465,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>3.38837385177612</v>
+        <v>3.3883740901947</v>
       </c>
       <c r="H624" t="n">
         <v>8687</v>
@@ -18494,7 +18494,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>3.39773440361023</v>
+        <v>3.39773464202881</v>
       </c>
       <c r="H625" t="n">
         <v>16296</v>
@@ -18523,7 +18523,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>3.40709471702576</v>
+        <v>3.40709447860718</v>
       </c>
       <c r="H626" t="n">
         <v>2276</v>
@@ -18552,7 +18552,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G627" t="n">
-        <v>3.37901401519775</v>
+        <v>3.37901425361633</v>
       </c>
       <c r="H627" t="n">
         <v>48267</v>
@@ -18610,7 +18610,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.39773440361023</v>
+        <v>3.39773464202881</v>
       </c>
       <c r="H629" t="n">
         <v>2495</v>
@@ -18639,7 +18639,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G630" t="n">
-        <v>3.33221364021301</v>
+        <v>3.33221316337585</v>
       </c>
       <c r="H630" t="n">
         <v>10750</v>
@@ -18668,7 +18668,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G631" t="n">
-        <v>3.37901401519775</v>
+        <v>3.37901425361633</v>
       </c>
       <c r="H631" t="n">
         <v>27218</v>
@@ -18726,7 +18726,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G633" t="n">
-        <v>3.24797224998474</v>
+        <v>3.24797177314758</v>
       </c>
       <c r="H633" t="n">
         <v>13590</v>
@@ -18813,7 +18813,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G636" t="n">
-        <v>3.39773440361023</v>
+        <v>3.39773464202881</v>
       </c>
       <c r="H636" t="n">
         <v>36700</v>
@@ -18929,7 +18929,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.12629008293152</v>
+        <v>3.12628984451294</v>
       </c>
       <c r="H640" t="n">
         <v>8567</v>
@@ -18958,7 +18958,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>3.11692953109741</v>
+        <v>3.11692976951599</v>
       </c>
       <c r="H641" t="n">
         <v>42079</v>
@@ -18987,7 +18987,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.90164637565613</v>
+        <v>2.90164613723755</v>
       </c>
       <c r="H642" t="n">
         <v>47794</v>
@@ -19016,7 +19016,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G643" t="n">
-        <v>2.79868483543396</v>
+        <v>2.79868459701538</v>
       </c>
       <c r="H643" t="n">
         <v>69535</v>
@@ -19103,7 +19103,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>2.53660082817078</v>
+        <v>2.5366005897522</v>
       </c>
       <c r="H646" t="n">
         <v>3417</v>
@@ -19161,7 +19161,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>2.90164637565613</v>
+        <v>2.90164613723755</v>
       </c>
       <c r="H648" t="n">
         <v>34907</v>
@@ -19190,7 +19190,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G649" t="n">
-        <v>2.89228630065918</v>
+        <v>2.89228653907776</v>
       </c>
       <c r="H649" t="n">
         <v>10055</v>
@@ -19219,7 +19219,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G650" t="n">
-        <v>2.87356615066528</v>
+        <v>2.8735659122467</v>
       </c>
       <c r="H650" t="n">
         <v>17053</v>
@@ -19248,7 +19248,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G651" t="n">
-        <v>2.89228630065918</v>
+        <v>2.89228653907776</v>
       </c>
       <c r="H651" t="n">
         <v>13310</v>
@@ -19422,7 +19422,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G657" t="n">
-        <v>3.22925186157227</v>
+        <v>3.22925162315369</v>
       </c>
       <c r="H657" t="n">
         <v>36711</v>
@@ -19538,7 +19538,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G661" t="n">
-        <v>3.26669239997864</v>
+        <v>3.26669263839722</v>
       </c>
       <c r="H661" t="n">
         <v>18230</v>
@@ -19596,7 +19596,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H663" t="n">
         <v>58774</v>
@@ -19625,7 +19625,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G664" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H664" t="n">
         <v>67083</v>
@@ -19654,7 +19654,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G665" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H665" t="n">
         <v>100055</v>
@@ -19683,7 +19683,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H666" t="n">
         <v>128114</v>
@@ -19712,7 +19712,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H667" t="n">
         <v>16853</v>
@@ -19741,7 +19741,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H668" t="n">
         <v>52203</v>
@@ -19770,7 +19770,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G669" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H669" t="n">
         <v>22324</v>
@@ -19799,7 +19799,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H670" t="n">
         <v>73577</v>
@@ -19828,7 +19828,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G671" t="n">
-        <v>3.39773440361023</v>
+        <v>3.39773464202881</v>
       </c>
       <c r="H671" t="n">
         <v>48966</v>
@@ -19857,7 +19857,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G672" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H672" t="n">
         <v>37214</v>
@@ -19886,7 +19886,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H673" t="n">
         <v>5984</v>
@@ -19915,7 +19915,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H674" t="n">
         <v>500</v>
@@ -19944,7 +19944,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G675" t="n">
-        <v>3.36965394020081</v>
+        <v>3.36965370178223</v>
       </c>
       <c r="H675" t="n">
         <v>15715</v>
@@ -19973,7 +19973,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>3.48197603225708</v>
+        <v>3.48197555541992</v>
       </c>
       <c r="H676" t="n">
         <v>143284</v>
@@ -20002,7 +20002,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G677" t="n">
-        <v>3.55685663223267</v>
+        <v>3.55685710906982</v>
       </c>
       <c r="H677" t="n">
         <v>74533</v>
@@ -20031,7 +20031,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>3.59429693222046</v>
+        <v>3.59429740905762</v>
       </c>
       <c r="H678" t="n">
         <v>117936</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.63173842430115</v>
+        <v>3.63173866271973</v>
       </c>
       <c r="H679" t="n">
         <v>81544</v>
@@ -20118,7 +20118,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>3.56621718406677</v>
+        <v>3.56621694564819</v>
       </c>
       <c r="H681" t="n">
         <v>19560</v>
@@ -20205,7 +20205,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>3.47261548042297</v>
+        <v>3.47261524200439</v>
       </c>
       <c r="H684" t="n">
         <v>8456</v>
@@ -20234,7 +20234,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G685" t="n">
-        <v>3.48197603225708</v>
+        <v>3.48197555541992</v>
       </c>
       <c r="H685" t="n">
         <v>4903</v>
@@ -20292,7 +20292,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>3.60365748405457</v>
+        <v>3.60365772247314</v>
       </c>
       <c r="H687" t="n">
         <v>87568</v>
@@ -20321,7 +20321,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G688" t="n">
-        <v>3.55685663223267</v>
+        <v>3.55685710906982</v>
       </c>
       <c r="H688" t="n">
         <v>193567</v>
@@ -20350,7 +20350,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>3.53813672065735</v>
+        <v>3.53813695907593</v>
       </c>
       <c r="H689" t="n">
         <v>157462</v>
@@ -20379,7 +20379,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>3.60365748405457</v>
+        <v>3.60365772247314</v>
       </c>
       <c r="H690" t="n">
         <v>390324</v>
@@ -20408,7 +20408,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G691" t="n">
-        <v>3.37901401519775</v>
+        <v>3.37901425361633</v>
       </c>
       <c r="H691" t="n">
         <v>736934</v>
@@ -20437,7 +20437,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.33221364021301</v>
+        <v>3.33221316337585</v>
       </c>
       <c r="H692" t="n">
         <v>140706</v>
@@ -20553,7 +20553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>3.03268814086914</v>
+        <v>3.03268885612488</v>
       </c>
       <c r="H696" t="n">
         <v>83216</v>
@@ -20582,7 +20582,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G697" t="n">
-        <v>2.9858877658844</v>
+        <v>2.98588800430298</v>
       </c>
       <c r="H697" t="n">
         <v>74009</v>
@@ -20640,7 +20640,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>3.17309069633484</v>
+        <v>3.17309093475342</v>
       </c>
       <c r="H699" t="n">
         <v>657362</v>
@@ -20669,7 +20669,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.18245124816895</v>
+        <v>3.18245100975037</v>
       </c>
       <c r="H700" t="n">
         <v>74409</v>
@@ -20727,7 +20727,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G702" t="n">
-        <v>3.18245124816895</v>
+        <v>3.18245100975037</v>
       </c>
       <c r="H702" t="n">
         <v>56321</v>
@@ -20872,7 +20872,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>3.11692953109741</v>
+        <v>3.11692976951599</v>
       </c>
       <c r="H707" t="n">
         <v>52725</v>
@@ -20901,7 +20901,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.9858877658844</v>
+        <v>2.98588800430298</v>
       </c>
       <c r="H708" t="n">
         <v>81677</v>
@@ -20930,7 +20930,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>2.94844722747803</v>
+        <v>2.94844746589661</v>
       </c>
       <c r="H709" t="n">
         <v>51596</v>
@@ -20959,7 +20959,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G710" t="n">
-        <v>2.95780730247498</v>
+        <v>2.95780754089355</v>
       </c>
       <c r="H710" t="n">
         <v>72904</v>
@@ -20988,7 +20988,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G711" t="n">
-        <v>3.05140852928162</v>
+        <v>3.05140900611877</v>
       </c>
       <c r="H711" t="n">
         <v>57500</v>
@@ -21046,7 +21046,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>3.00460839271545</v>
+        <v>3.00460815429688</v>
       </c>
       <c r="H713" t="n">
         <v>126043</v>
@@ -21133,7 +21133,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>3.25088334083557</v>
+        <v>3.25088310241699</v>
       </c>
       <c r="H716" t="n">
         <v>82513</v>
@@ -21191,7 +21191,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G718" t="n">
-        <v>3.17593479156494</v>
+        <v>3.17593502998352</v>
       </c>
       <c r="H718" t="n">
         <v>25259</v>
@@ -21394,7 +21394,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G725" t="n">
-        <v>3.17593479156494</v>
+        <v>3.17593502998352</v>
       </c>
       <c r="H725" t="n">
         <v>13863</v>
@@ -21481,7 +21481,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G728" t="n">
-        <v>3.15719771385193</v>
+        <v>3.15719747543335</v>
       </c>
       <c r="H728" t="n">
         <v>4805</v>
@@ -21945,7 +21945,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H744" t="n">
         <v>454803</v>
@@ -21974,7 +21974,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G745" t="n">
-        <v>3.41951680183411</v>
+        <v>3.41951704025269</v>
       </c>
       <c r="H745" t="n">
         <v>33489</v>
@@ -22003,7 +22003,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G746" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H746" t="n">
         <v>45840</v>
@@ -22032,7 +22032,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G747" t="n">
-        <v>3.41014814376831</v>
+        <v>3.41014838218689</v>
       </c>
       <c r="H747" t="n">
         <v>493111</v>
@@ -22061,7 +22061,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H748" t="n">
         <v>75973</v>
@@ -22090,7 +22090,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.33520007133484</v>
+        <v>3.33519983291626</v>
       </c>
       <c r="H749" t="n">
         <v>25439</v>
@@ -22119,7 +22119,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H750" t="n">
         <v>5946</v>
@@ -22148,7 +22148,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>3.39141130447388</v>
+        <v>3.3914110660553</v>
       </c>
       <c r="H751" t="n">
         <v>29900</v>
@@ -22177,7 +22177,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G752" t="n">
-        <v>3.4288854598999</v>
+        <v>3.42888569831848</v>
       </c>
       <c r="H752" t="n">
         <v>24007</v>
@@ -22235,7 +22235,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H754" t="n">
         <v>58210</v>
@@ -22264,7 +22264,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H755" t="n">
         <v>13024</v>
@@ -22293,7 +22293,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G756" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H756" t="n">
         <v>134364</v>
@@ -22409,7 +22409,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H760" t="n">
         <v>128477</v>
@@ -22438,7 +22438,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.45699095726013</v>
+        <v>3.45699071884155</v>
       </c>
       <c r="H761" t="n">
         <v>110692</v>
@@ -22554,7 +22554,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G765" t="n">
-        <v>3.41951680183411</v>
+        <v>3.41951704025269</v>
       </c>
       <c r="H765" t="n">
         <v>34441</v>
@@ -22612,7 +22612,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G767" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H767" t="n">
         <v>56135</v>
@@ -22641,7 +22641,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G768" t="n">
-        <v>3.4288854598999</v>
+        <v>3.42888569831848</v>
       </c>
       <c r="H768" t="n">
         <v>13075</v>
@@ -22670,7 +22670,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G769" t="n">
-        <v>3.38204264640808</v>
+        <v>3.38204288482666</v>
       </c>
       <c r="H769" t="n">
         <v>3003</v>
@@ -22786,7 +22786,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G773" t="n">
-        <v>3.4288854598999</v>
+        <v>3.42888569831848</v>
       </c>
       <c r="H773" t="n">
         <v>98798</v>
@@ -22844,7 +22844,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G775" t="n">
-        <v>3.38204264640808</v>
+        <v>3.38204288482666</v>
       </c>
       <c r="H775" t="n">
         <v>9585</v>
@@ -22873,7 +22873,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H776" t="n">
         <v>55090</v>
@@ -22902,7 +22902,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H777" t="n">
         <v>8145</v>
@@ -22960,7 +22960,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H779" t="n">
         <v>22658</v>
@@ -22989,7 +22989,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>3.41014814376831</v>
+        <v>3.41014838218689</v>
       </c>
       <c r="H780" t="n">
         <v>22131</v>
@@ -23018,7 +23018,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>3.35393738746643</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H781" t="n">
         <v>10208</v>
@@ -23047,7 +23047,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H782" t="n">
         <v>16574</v>
@@ -23076,7 +23076,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H783" t="n">
         <v>2367</v>
@@ -23105,7 +23105,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G784" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H784" t="n">
         <v>11723</v>
@@ -23134,7 +23134,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G785" t="n">
-        <v>3.41951680183411</v>
+        <v>3.41951704025269</v>
       </c>
       <c r="H785" t="n">
         <v>34035</v>
@@ -23221,7 +23221,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G788" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H788" t="n">
         <v>5065</v>
@@ -23250,7 +23250,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>3.35393738746643</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H789" t="n">
         <v>109072</v>
@@ -23279,7 +23279,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G790" t="n">
-        <v>3.40077972412109</v>
+        <v>3.40078020095825</v>
       </c>
       <c r="H790" t="n">
         <v>22544</v>
@@ -23308,7 +23308,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G791" t="n">
-        <v>3.28835725784302</v>
+        <v>3.28835773468018</v>
       </c>
       <c r="H791" t="n">
         <v>25264</v>
@@ -23366,7 +23366,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G793" t="n">
-        <v>3.31646299362183</v>
+        <v>3.31646275520325</v>
       </c>
       <c r="H793" t="n">
         <v>35556</v>
@@ -23395,7 +23395,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G794" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H794" t="n">
         <v>8999</v>
@@ -23424,7 +23424,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G795" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H795" t="n">
         <v>14337</v>
@@ -23569,7 +23569,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H800" t="n">
         <v>10366</v>
@@ -23598,7 +23598,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G801" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H801" t="n">
         <v>1507</v>
@@ -23627,7 +23627,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>3.39141130447388</v>
+        <v>3.3914110660553</v>
       </c>
       <c r="H802" t="n">
         <v>40518</v>
@@ -23656,7 +23656,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G803" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H803" t="n">
         <v>280592</v>
@@ -23685,7 +23685,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H804" t="n">
         <v>134798</v>
@@ -23743,7 +23743,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.41951680183411</v>
+        <v>3.41951704025269</v>
       </c>
       <c r="H806" t="n">
         <v>89100</v>
@@ -23801,7 +23801,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>3.33520007133484</v>
+        <v>3.33519983291626</v>
       </c>
       <c r="H808" t="n">
         <v>10492</v>
@@ -23830,7 +23830,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G809" t="n">
-        <v>3.41951680183411</v>
+        <v>3.41951704025269</v>
       </c>
       <c r="H809" t="n">
         <v>61251</v>
@@ -23859,7 +23859,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.41951680183411</v>
+        <v>3.41951704025269</v>
       </c>
       <c r="H810" t="n">
         <v>114614</v>
@@ -23888,7 +23888,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G811" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H811" t="n">
         <v>83805</v>
@@ -23946,7 +23946,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>3.35393738746643</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H813" t="n">
         <v>77134</v>
@@ -23975,7 +23975,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>3.33520007133484</v>
+        <v>3.33519983291626</v>
       </c>
       <c r="H814" t="n">
         <v>26587</v>
@@ -24062,7 +24062,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H817" t="n">
         <v>16389</v>
@@ -24091,7 +24091,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.35393738746643</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H818" t="n">
         <v>12874</v>
@@ -24120,7 +24120,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H819" t="n">
         <v>39306</v>
@@ -24207,7 +24207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G822" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H822" t="n">
         <v>17770</v>
@@ -24236,7 +24236,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H823" t="n">
         <v>70262</v>
@@ -24265,7 +24265,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H824" t="n">
         <v>15100</v>
@@ -24294,7 +24294,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H825" t="n">
         <v>32231</v>
@@ -24323,7 +24323,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H826" t="n">
         <v>37605</v>
@@ -24352,7 +24352,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G827" t="n">
-        <v>3.38204264640808</v>
+        <v>3.38204288482666</v>
       </c>
       <c r="H827" t="n">
         <v>16230</v>
@@ -24410,7 +24410,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.31646299362183</v>
+        <v>3.31646275520325</v>
       </c>
       <c r="H829" t="n">
         <v>6640</v>
@@ -24439,7 +24439,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G830" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H830" t="n">
         <v>48136</v>
@@ -24497,7 +24497,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G832" t="n">
-        <v>3.37267422676086</v>
+        <v>3.37267374992371</v>
       </c>
       <c r="H832" t="n">
         <v>17409</v>
@@ -24526,7 +24526,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G833" t="n">
-        <v>3.33520007133484</v>
+        <v>3.33519983291626</v>
       </c>
       <c r="H833" t="n">
         <v>51306</v>
@@ -24584,7 +24584,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H835" t="n">
         <v>4670</v>
@@ -24613,7 +24613,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>3.35393738746643</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H836" t="n">
         <v>41</v>
@@ -24642,7 +24642,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G837" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H837" t="n">
         <v>6979</v>
@@ -24671,7 +24671,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H838" t="n">
         <v>6632</v>
@@ -24700,7 +24700,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>3.35393738746643</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H839" t="n">
         <v>1914</v>
@@ -24758,7 +24758,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>3.31646299362183</v>
+        <v>3.31646275520325</v>
       </c>
       <c r="H841" t="n">
         <v>15368</v>
@@ -24787,7 +24787,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G842" t="n">
-        <v>3.32583141326904</v>
+        <v>3.32583165168762</v>
       </c>
       <c r="H842" t="n">
         <v>45487</v>
@@ -24874,7 +24874,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G845" t="n">
-        <v>3.41951680183411</v>
+        <v>3.41951704025269</v>
       </c>
       <c r="H845" t="n">
         <v>60753</v>
@@ -24903,7 +24903,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>3.35393738746643</v>
+        <v>3.35393714904785</v>
       </c>
       <c r="H846" t="n">
         <v>37415</v>
@@ -24961,7 +24961,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>3.31646299362183</v>
+        <v>3.31646275520325</v>
       </c>
       <c r="H848" t="n">
         <v>634236</v>
@@ -24990,7 +24990,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G849" t="n">
-        <v>3.38204264640808</v>
+        <v>3.38204288482666</v>
       </c>
       <c r="H849" t="n">
         <v>39489</v>
@@ -25019,7 +25019,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G850" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H850" t="n">
         <v>143468</v>
@@ -25048,7 +25048,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572779655457</v>
       </c>
       <c r="H851" t="n">
         <v>7970</v>
@@ -25106,7 +25106,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H853" t="n">
         <v>6614</v>
@@ -25193,7 +25193,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H856" t="n">
         <v>13170</v>
@@ -25222,7 +25222,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H857" t="n">
         <v>16223</v>
@@ -25251,7 +25251,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H858" t="n">
         <v>3076</v>
@@ -25425,7 +25425,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G864" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H864" t="n">
         <v>72576</v>
@@ -25454,7 +25454,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G865" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509645462036</v>
       </c>
       <c r="H865" t="n">
         <v>47730</v>
@@ -25483,7 +25483,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G866" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509645462036</v>
       </c>
       <c r="H866" t="n">
         <v>29971</v>
@@ -25570,7 +25570,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572779655457</v>
       </c>
       <c r="H869" t="n">
         <v>31615</v>
@@ -25715,7 +25715,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>3.63499331474304</v>
+        <v>3.6349937915802</v>
       </c>
       <c r="H874" t="n">
         <v>25969</v>
@@ -25744,7 +25744,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G875" t="n">
-        <v>3.66309928894043</v>
+        <v>3.66309881210327</v>
       </c>
       <c r="H875" t="n">
         <v>31745</v>
@@ -25773,7 +25773,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994114875793</v>
       </c>
       <c r="H876" t="n">
         <v>33432</v>
@@ -25802,7 +25802,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994114875793</v>
       </c>
       <c r="H877" t="n">
         <v>44786</v>
@@ -25831,7 +25831,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G878" t="n">
-        <v>3.7380473613739</v>
+        <v>3.73804712295532</v>
       </c>
       <c r="H878" t="n">
         <v>23690</v>
@@ -25889,7 +25889,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G880" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H880" t="n">
         <v>24326</v>
@@ -25947,7 +25947,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G882" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H882" t="n">
         <v>13442</v>
@@ -25976,7 +25976,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H883" t="n">
         <v>3909</v>
@@ -26063,7 +26063,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G886" t="n">
-        <v>3.61625599861145</v>
+        <v>3.61625647544861</v>
       </c>
       <c r="H886" t="n">
         <v>48674</v>
@@ -26092,7 +26092,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G887" t="n">
-        <v>3.66309928894043</v>
+        <v>3.66309881210327</v>
       </c>
       <c r="H887" t="n">
         <v>21941</v>
@@ -26121,7 +26121,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994114875793</v>
       </c>
       <c r="H888" t="n">
         <v>4653</v>
@@ -26150,7 +26150,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994114875793</v>
       </c>
       <c r="H889" t="n">
         <v>12975</v>
@@ -26179,7 +26179,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994114875793</v>
       </c>
       <c r="H890" t="n">
         <v>11433</v>
@@ -26266,7 +26266,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G893" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H893" t="n">
         <v>13934</v>
@@ -26295,7 +26295,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>3.71931028366089</v>
+        <v>3.71931004524231</v>
       </c>
       <c r="H894" t="n">
         <v>9115</v>
@@ -26324,7 +26324,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H895" t="n">
         <v>13337</v>
@@ -26353,7 +26353,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G896" t="n">
-        <v>3.71931028366089</v>
+        <v>3.71931004524231</v>
       </c>
       <c r="H896" t="n">
         <v>10204</v>
@@ -26382,7 +26382,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G897" t="n">
-        <v>3.71931028366089</v>
+        <v>3.71931004524231</v>
       </c>
       <c r="H897" t="n">
         <v>17345</v>
@@ -26498,7 +26498,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H901" t="n">
         <v>102888</v>
@@ -26556,7 +26556,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994114875793</v>
       </c>
       <c r="H903" t="n">
         <v>7500</v>
@@ -26643,7 +26643,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H906" t="n">
         <v>6442</v>
@@ -26759,7 +26759,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G910" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H910" t="n">
         <v>7756</v>
@@ -26788,7 +26788,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G911" t="n">
-        <v>3.69120454788208</v>
+        <v>3.6912043094635</v>
       </c>
       <c r="H911" t="n">
         <v>1036</v>
@@ -26817,7 +26817,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G912" t="n">
-        <v>3.66309928894043</v>
+        <v>3.66309881210327</v>
       </c>
       <c r="H912" t="n">
         <v>15979</v>
@@ -26875,7 +26875,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>3.70994138717651</v>
+        <v>3.70994114875793</v>
       </c>
       <c r="H914" t="n">
         <v>7713</v>
@@ -26962,7 +26962,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>3.66309928894043</v>
+        <v>3.66309881210327</v>
       </c>
       <c r="H917" t="n">
         <v>8568</v>
@@ -27020,7 +27020,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G919" t="n">
-        <v>3.70057320594788</v>
+        <v>3.7005729675293</v>
       </c>
       <c r="H919" t="n">
         <v>7593</v>
@@ -27078,7 +27078,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G921" t="n">
-        <v>3.69120454788208</v>
+        <v>3.6912043094635</v>
       </c>
       <c r="H921" t="n">
         <v>16172</v>
@@ -27107,7 +27107,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>3.60688781738281</v>
+        <v>3.60688757896423</v>
       </c>
       <c r="H922" t="n">
         <v>21416</v>
@@ -27136,7 +27136,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>3.66309928894043</v>
+        <v>3.66309881210327</v>
       </c>
       <c r="H923" t="n">
         <v>18984</v>
@@ -27165,7 +27165,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>3.61625599861145</v>
+        <v>3.61625647544861</v>
       </c>
       <c r="H924" t="n">
         <v>3704</v>
@@ -27194,7 +27194,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>3.57878184318542</v>
+        <v>3.578782081604</v>
       </c>
       <c r="H925" t="n">
         <v>24002</v>
@@ -27252,7 +27252,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.60688781738281</v>
+        <v>3.60688757896423</v>
       </c>
       <c r="H927" t="n">
         <v>22410</v>
@@ -27310,7 +27310,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G929" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509645462036</v>
       </c>
       <c r="H929" t="n">
         <v>10522</v>
@@ -27339,7 +27339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G930" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H930" t="n">
         <v>32650</v>
@@ -27368,7 +27368,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G931" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509645462036</v>
       </c>
       <c r="H931" t="n">
         <v>26777</v>
@@ -27484,7 +27484,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572779655457</v>
       </c>
       <c r="H935" t="n">
         <v>4902</v>
@@ -27513,7 +27513,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46635937690735</v>
+        <v>3.46635961532593</v>
       </c>
       <c r="H936" t="n">
         <v>16767</v>
@@ -27600,7 +27600,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>3.5413076877594</v>
+        <v>3.54130816459656</v>
       </c>
       <c r="H939" t="n">
         <v>10462</v>
@@ -27629,7 +27629,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>3.53193950653076</v>
+        <v>3.53193926811218</v>
       </c>
       <c r="H940" t="n">
         <v>44151</v>
@@ -27716,7 +27716,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509645462036</v>
       </c>
       <c r="H943" t="n">
         <v>23604</v>
@@ -27745,7 +27745,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>3.56004476547241</v>
+        <v>3.56004524230957</v>
       </c>
       <c r="H944" t="n">
         <v>16909</v>
@@ -27774,7 +27774,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G945" t="n">
-        <v>3.48509693145752</v>
+        <v>3.48509645462036</v>
       </c>
       <c r="H945" t="n">
         <v>13661</v>
@@ -27803,7 +27803,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>3.47572803497314</v>
+        <v>3.47572779655457</v>
       </c>
       <c r="H946" t="n">
         <v>9434</v>
@@ -28006,7 +28006,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.4990553855896</v>
+        <v>3.49905562400818</v>
       </c>
       <c r="H953" t="n">
         <v>15835</v>
@@ -28267,7 +28267,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G962" t="n">
-        <v>3.4614315032959</v>
+        <v>3.46143102645874</v>
       </c>
       <c r="H962" t="n">
         <v>9986</v>
@@ -28325,7 +28325,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G964" t="n">
-        <v>3.42380714416504</v>
+        <v>3.42380738258362</v>
       </c>
       <c r="H964" t="n">
         <v>80061</v>
@@ -28354,7 +28354,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G965" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H965" t="n">
         <v>15852</v>
@@ -28383,7 +28383,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G966" t="n">
-        <v>3.4614315032959</v>
+        <v>3.46143102645874</v>
       </c>
       <c r="H966" t="n">
         <v>6216</v>
@@ -28412,7 +28412,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G967" t="n">
-        <v>3.4614315032959</v>
+        <v>3.46143102645874</v>
       </c>
       <c r="H967" t="n">
         <v>7483</v>
@@ -28470,7 +28470,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G969" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H969" t="n">
         <v>1955</v>
@@ -28499,7 +28499,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G970" t="n">
-        <v>3.42380714416504</v>
+        <v>3.42380738258362</v>
       </c>
       <c r="H970" t="n">
         <v>6934</v>
@@ -28528,7 +28528,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G971" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H971" t="n">
         <v>7052</v>
@@ -28557,7 +28557,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H972" t="n">
         <v>10374</v>
@@ -28702,7 +28702,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G977" t="n">
-        <v>3.4990553855896</v>
+        <v>3.49905562400818</v>
       </c>
       <c r="H977" t="n">
         <v>8957</v>
@@ -28934,7 +28934,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H985" t="n">
         <v>16634</v>
@@ -28963,7 +28963,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G986" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H986" t="n">
         <v>25665</v>
@@ -28992,7 +28992,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>3.27331042289734</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H987" t="n">
         <v>4720</v>
@@ -29050,7 +29050,7 @@
         <v>3.5</v>
       </c>
       <c r="G989" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H989" t="n">
         <v>15262</v>
@@ -29079,7 +29079,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G990" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H990" t="n">
         <v>17255</v>
@@ -29108,7 +29108,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G991" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H991" t="n">
         <v>5729</v>
@@ -29137,7 +29137,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G992" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H992" t="n">
         <v>11237</v>
@@ -29166,7 +29166,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G993" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H993" t="n">
         <v>17975</v>
@@ -29282,7 +29282,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G997" t="n">
-        <v>3.4990553855896</v>
+        <v>3.49905562400818</v>
       </c>
       <c r="H997" t="n">
         <v>10969</v>
@@ -29311,7 +29311,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G998" t="n">
-        <v>3.4990553855896</v>
+        <v>3.49905562400818</v>
       </c>
       <c r="H998" t="n">
         <v>24716</v>
@@ -29572,7 +29572,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H1007" t="n">
         <v>22863</v>
@@ -29601,7 +29601,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1008" t="n">
         <v>28103</v>
@@ -29630,7 +29630,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1009" t="n">
         <v>12327</v>
@@ -29659,7 +29659,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.42380714416504</v>
+        <v>3.42380738258362</v>
       </c>
       <c r="H1010" t="n">
         <v>8209</v>
@@ -29688,7 +29688,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H1011" t="n">
         <v>19917</v>
@@ -29717,7 +29717,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1012" t="n">
         <v>15052</v>
@@ -29833,7 +29833,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1016" t="n">
         <v>17274</v>
@@ -29862,7 +29862,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1017" t="n">
         <v>31009</v>
@@ -29891,7 +29891,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1018" t="n">
         <v>21367</v>
@@ -29920,7 +29920,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1019" t="n">
         <v>6494</v>
@@ -29949,7 +29949,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.27331042289734</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H1020" t="n">
         <v>11369</v>
@@ -29978,7 +29978,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.25449776649475</v>
+        <v>3.25449800491333</v>
       </c>
       <c r="H1021" t="n">
         <v>22089</v>
@@ -30036,7 +30036,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.25449776649475</v>
+        <v>3.25449800491333</v>
       </c>
       <c r="H1023" t="n">
         <v>6804</v>
@@ -30123,7 +30123,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.42380714416504</v>
+        <v>3.42380738258362</v>
       </c>
       <c r="H1026" t="n">
         <v>7964</v>
@@ -30297,7 +30297,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.4990553855896</v>
+        <v>3.49905562400818</v>
       </c>
       <c r="H1032" t="n">
         <v>16451</v>
@@ -30500,7 +30500,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1039" t="n">
         <v>13704</v>
@@ -30529,7 +30529,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1040" t="n">
         <v>6370</v>
@@ -30703,7 +30703,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.39558863639832</v>
+        <v>3.39558887481689</v>
       </c>
       <c r="H1046" t="n">
         <v>7488</v>
@@ -30732,7 +30732,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1047" t="n">
         <v>28501</v>
@@ -30790,7 +30790,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1049" t="n">
         <v>6837</v>
@@ -30964,7 +30964,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1055" t="n">
         <v>12115</v>
@@ -30993,7 +30993,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1056" t="n">
         <v>12337</v>
@@ -31022,7 +31022,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1057" t="n">
         <v>3523</v>
@@ -31051,7 +31051,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1058" t="n">
         <v>6685</v>
@@ -31080,7 +31080,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.39558863639832</v>
+        <v>3.39558887481689</v>
       </c>
       <c r="H1059" t="n">
         <v>17685</v>
@@ -31138,7 +31138,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1061" t="n">
         <v>5923</v>
@@ -31167,7 +31167,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1062" t="n">
         <v>4441</v>
@@ -31196,7 +31196,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.39558863639832</v>
+        <v>3.39558887481689</v>
       </c>
       <c r="H1063" t="n">
         <v>14861</v>
@@ -31225,7 +31225,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1064" t="n">
         <v>6163</v>
@@ -31254,7 +31254,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1065" t="n">
         <v>5109</v>
@@ -31283,7 +31283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1066" t="n">
         <v>9447</v>
@@ -31370,7 +31370,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1069" t="n">
         <v>8548</v>
@@ -31486,7 +31486,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1073" t="n">
         <v>9850</v>
@@ -31515,7 +31515,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1074" t="n">
         <v>10350</v>
@@ -31602,7 +31602,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1077" t="n">
         <v>13572</v>
@@ -31660,7 +31660,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1079" t="n">
         <v>114960</v>
@@ -31747,7 +31747,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1082" t="n">
         <v>39684</v>
@@ -31805,7 +31805,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1084" t="n">
         <v>31241</v>
@@ -31834,7 +31834,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.42380714416504</v>
+        <v>3.42380738258362</v>
       </c>
       <c r="H1085" t="n">
         <v>203058</v>
@@ -31892,7 +31892,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1087" t="n">
         <v>37589</v>
@@ -31921,7 +31921,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1088" t="n">
         <v>40835</v>
@@ -31950,7 +31950,7 @@
         <v>3.5</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1089" t="n">
         <v>6814</v>
@@ -32037,7 +32037,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1092" t="n">
         <v>11230</v>
@@ -32066,7 +32066,7 @@
         <v>3.5</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1093" t="n">
         <v>42910</v>
@@ -32095,7 +32095,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1094" t="n">
         <v>46387</v>
@@ -32153,7 +32153,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.27331042289734</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H1096" t="n">
         <v>36379</v>
@@ -32182,7 +32182,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1097" t="n">
         <v>31606</v>
@@ -32298,7 +32298,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.25449776649475</v>
+        <v>3.25449800491333</v>
       </c>
       <c r="H1101" t="n">
         <v>70766</v>
@@ -32327,7 +32327,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1102" t="n">
         <v>27333</v>
@@ -32443,7 +32443,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.4614315032959</v>
+        <v>3.46143102645874</v>
       </c>
       <c r="H1106" t="n">
         <v>101164</v>
@@ -32501,7 +32501,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.42380714416504</v>
+        <v>3.42380738258362</v>
       </c>
       <c r="H1108" t="n">
         <v>25419</v>
@@ -32559,7 +32559,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.39558863639832</v>
+        <v>3.39558887481689</v>
       </c>
       <c r="H1110" t="n">
         <v>8178</v>
@@ -32617,7 +32617,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1112" t="n">
         <v>69565</v>
@@ -32733,7 +32733,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.39558863639832</v>
+        <v>3.39558887481689</v>
       </c>
       <c r="H1116" t="n">
         <v>9977</v>
@@ -32762,7 +32762,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.39558863639832</v>
+        <v>3.39558887481689</v>
       </c>
       <c r="H1117" t="n">
         <v>5011</v>
@@ -32791,7 +32791,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1118" t="n">
         <v>6265</v>
@@ -32878,7 +32878,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1121" t="n">
         <v>9350</v>
@@ -32907,7 +32907,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1122" t="n">
         <v>21895</v>
@@ -32936,7 +32936,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1123" t="n">
         <v>8305</v>
@@ -32965,7 +32965,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1124" t="n">
         <v>594</v>
@@ -32994,7 +32994,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1125" t="n">
         <v>479318</v>
@@ -33052,7 +33052,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1127" t="n">
         <v>20813</v>
@@ -33110,7 +33110,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1129" t="n">
         <v>4340</v>
@@ -33168,7 +33168,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1131" t="n">
         <v>3010</v>
@@ -33226,7 +33226,7 @@
         <v>3.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1133" t="n">
         <v>13100</v>
@@ -33255,7 +33255,7 @@
         <v>3.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1134" t="n">
         <v>10219</v>
@@ -33284,7 +33284,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1135" t="n">
         <v>25851</v>
@@ -33313,7 +33313,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.27331042289734</v>
+        <v>3.27331018447876</v>
       </c>
       <c r="H1136" t="n">
         <v>34900</v>
@@ -33342,7 +33342,7 @@
         <v>3.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1137" t="n">
         <v>12331</v>
@@ -33400,7 +33400,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1139" t="n">
         <v>17496</v>
@@ -33429,7 +33429,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1140" t="n">
         <v>13001</v>
@@ -33458,7 +33458,7 @@
         <v>3.5</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1141" t="n">
         <v>16864</v>
@@ -33487,7 +33487,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.24509191513062</v>
+        <v>3.24509239196777</v>
       </c>
       <c r="H1142" t="n">
         <v>10849</v>
@@ -33603,7 +33603,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.08518862724304</v>
+        <v>3.08518886566162</v>
       </c>
       <c r="H1146" t="n">
         <v>19787</v>
@@ -33632,7 +33632,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.1698431968689</v>
+        <v>3.16984295845032</v>
       </c>
       <c r="H1147" t="n">
         <v>14261</v>
@@ -33748,7 +33748,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.28271627426147</v>
+        <v>3.2827160358429</v>
       </c>
       <c r="H1151" t="n">
         <v>33153</v>
@@ -33777,7 +33777,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.24509191513062</v>
+        <v>3.24509239196777</v>
       </c>
       <c r="H1152" t="n">
         <v>57910</v>
@@ -33806,7 +33806,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.25449776649475</v>
+        <v>3.25449800491333</v>
       </c>
       <c r="H1153" t="n">
         <v>8355</v>
@@ -33835,7 +33835,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.39558863639832</v>
+        <v>3.39558887481689</v>
       </c>
       <c r="H1154" t="n">
         <v>17565</v>
@@ -33864,7 +33864,7 @@
         <v>3.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1155" t="n">
         <v>27404</v>
@@ -33893,7 +33893,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1156" t="n">
         <v>14999</v>
@@ -33922,7 +33922,7 @@
         <v>3.5</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1157" t="n">
         <v>28053</v>
@@ -33980,7 +33980,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1159" t="n">
         <v>22763</v>
@@ -34009,7 +34009,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1160" t="n">
         <v>6945</v>
@@ -34067,7 +34067,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H1162" t="n">
         <v>17267</v>
@@ -34154,7 +34154,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1165" t="n">
         <v>31537</v>
@@ -34183,7 +34183,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1166" t="n">
         <v>12895</v>
@@ -34212,7 +34212,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1167" t="n">
         <v>4153</v>
@@ -34270,7 +34270,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1169" t="n">
         <v>15267</v>
@@ -34357,7 +34357,7 @@
         <v>3.5</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1172" t="n">
         <v>7570</v>
@@ -34386,7 +34386,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1173" t="n">
         <v>26219</v>
@@ -34415,7 +34415,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1174" t="n">
         <v>11204</v>
@@ -34444,7 +34444,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.30152797698975</v>
+        <v>3.30152821540833</v>
       </c>
       <c r="H1175" t="n">
         <v>9316</v>
@@ -34618,7 +34618,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.41440105438232</v>
+        <v>3.41440153121948</v>
       </c>
       <c r="H1181" t="n">
         <v>43268</v>
@@ -34763,7 +34763,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.38618278503418</v>
+        <v>3.3861825466156</v>
       </c>
       <c r="H1186" t="n">
         <v>5085</v>
@@ -34792,7 +34792,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1187" t="n">
         <v>14232</v>
@@ -34850,7 +34850,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1189" t="n">
         <v>4017</v>
@@ -34966,7 +34966,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1193" t="n">
         <v>11019</v>
@@ -34995,7 +34995,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1194" t="n">
         <v>3525</v>
@@ -35053,7 +35053,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.33915257453918</v>
+        <v>3.33915209770203</v>
       </c>
       <c r="H1196" t="n">
         <v>19669</v>
@@ -35082,7 +35082,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.34855842590332</v>
+        <v>3.3485586643219</v>
       </c>
       <c r="H1197" t="n">
         <v>5453</v>
@@ -35169,7 +35169,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.24509191513062</v>
+        <v>3.24509239196777</v>
       </c>
       <c r="H1200" t="n">
         <v>123001</v>
@@ -35198,7 +35198,7 @@
         <v>3.5</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.29212212562561</v>
+        <v>3.29212188720703</v>
       </c>
       <c r="H1201" t="n">
         <v>17101</v>
@@ -35227,7 +35227,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1202" t="n">
         <v>33897</v>
@@ -35256,7 +35256,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.32034063339233</v>
+        <v>3.32034039497375</v>
       </c>
       <c r="H1203" t="n">
         <v>8482</v>
@@ -35517,7 +35517,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1212" t="n">
         <v>3165</v>
@@ -35575,7 +35575,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1214" t="n">
         <v>11801</v>
@@ -35604,7 +35604,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1215" t="n">
         <v>12584</v>
@@ -35633,7 +35633,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1216" t="n">
         <v>8782</v>
@@ -35749,7 +35749,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.42461085319519</v>
+        <v>3.42461109161377</v>
       </c>
       <c r="H1220" t="n">
         <v>533</v>
@@ -35836,7 +35836,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1223" t="n">
         <v>19479</v>
@@ -35865,7 +35865,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1224" t="n">
         <v>181783</v>
@@ -35894,7 +35894,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.52896213531494</v>
+        <v>3.52896189689636</v>
       </c>
       <c r="H1225" t="n">
         <v>53624</v>
@@ -35952,7 +35952,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.40563797950745</v>
+        <v>3.40563821792603</v>
       </c>
       <c r="H1227" t="n">
         <v>4286</v>
@@ -36010,7 +36010,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1229" t="n">
         <v>6507</v>
@@ -36039,7 +36039,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1230" t="n">
         <v>1283</v>
@@ -36097,7 +36097,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1232" t="n">
         <v>3015</v>
@@ -36155,7 +36155,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1234" t="n">
         <v>7222</v>
@@ -36184,7 +36184,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1235" t="n">
         <v>12401</v>
@@ -36271,7 +36271,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.39615154266357</v>
+        <v>3.39615178108215</v>
       </c>
       <c r="H1238" t="n">
         <v>7536</v>
@@ -36329,7 +36329,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.40563797950745</v>
+        <v>3.40563821792603</v>
       </c>
       <c r="H1240" t="n">
         <v>7266</v>
@@ -36387,7 +36387,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1242" t="n">
         <v>3091</v>
@@ -36677,7 +36677,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.39615154266357</v>
+        <v>3.39615178108215</v>
       </c>
       <c r="H1252" t="n">
         <v>1883</v>
@@ -36706,7 +36706,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1253" t="n">
         <v>4000</v>
@@ -36764,7 +36764,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1255" t="n">
         <v>5425</v>
@@ -36967,7 +36967,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.39615154266357</v>
+        <v>3.39615178108215</v>
       </c>
       <c r="H1262" t="n">
         <v>15155</v>
@@ -37054,7 +37054,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1265" t="n">
         <v>3014</v>
@@ -37170,7 +37170,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1269" t="n">
         <v>7300</v>
@@ -37199,7 +37199,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1270" t="n">
         <v>3113</v>
@@ -37228,7 +37228,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1271" t="n">
         <v>306</v>
@@ -37315,7 +37315,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>3.40563797950745</v>
+        <v>3.40563821792603</v>
       </c>
       <c r="H1274" t="n">
         <v>3593</v>
@@ -37431,7 +37431,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1278" t="n">
         <v>19303</v>
@@ -37489,7 +37489,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1280" t="n">
         <v>3868</v>
@@ -37692,7 +37692,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.28231406211853</v>
+        <v>3.28231430053711</v>
       </c>
       <c r="H1287" t="n">
         <v>17850</v>
@@ -37837,7 +37837,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1292" t="n">
         <v>6737</v>
@@ -37924,7 +37924,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.28231406211853</v>
+        <v>3.28231430053711</v>
       </c>
       <c r="H1295" t="n">
         <v>900</v>
@@ -37982,7 +37982,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1297" t="n">
         <v>23272</v>
@@ -38040,7 +38040,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.40563797950745</v>
+        <v>3.40563821792603</v>
       </c>
       <c r="H1299" t="n">
         <v>15089</v>
@@ -38069,7 +38069,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1300" t="n">
         <v>6137</v>
@@ -38127,7 +38127,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.44358396530151</v>
+        <v>3.44358420372009</v>
       </c>
       <c r="H1302" t="n">
         <v>5259</v>
@@ -38156,7 +38156,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.40563797950745</v>
+        <v>3.40563821792603</v>
       </c>
       <c r="H1303" t="n">
         <v>6381</v>
@@ -38185,7 +38185,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1304" t="n">
         <v>9749</v>
@@ -38214,7 +38214,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.44358396530151</v>
+        <v>3.44358420372009</v>
       </c>
       <c r="H1305" t="n">
         <v>5513</v>
@@ -38243,7 +38243,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1306" t="n">
         <v>2109</v>
@@ -38330,7 +38330,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1309" t="n">
         <v>2649</v>
@@ -38359,7 +38359,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1310" t="n">
         <v>3116</v>
@@ -38388,7 +38388,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1311" t="n">
         <v>54</v>
@@ -38417,7 +38417,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1312" t="n">
         <v>0</v>
@@ -38475,7 +38475,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.34871959686279</v>
+        <v>3.34871935844421</v>
       </c>
       <c r="H1314" t="n">
         <v>13661</v>
@@ -38504,7 +38504,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.40563797950745</v>
+        <v>3.40563821792603</v>
       </c>
       <c r="H1315" t="n">
         <v>29993</v>
@@ -38533,7 +38533,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.44358396530151</v>
+        <v>3.44358420372009</v>
       </c>
       <c r="H1316" t="n">
         <v>3324</v>
@@ -38562,7 +38562,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.47204327583313</v>
+        <v>3.47204351425171</v>
       </c>
       <c r="H1317" t="n">
         <v>5915</v>
@@ -38591,7 +38591,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.42461085319519</v>
+        <v>3.42461109161377</v>
       </c>
       <c r="H1318" t="n">
         <v>1301</v>
@@ -38620,7 +38620,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.4151246547699</v>
+        <v>3.41512441635132</v>
       </c>
       <c r="H1319" t="n">
         <v>1500</v>
@@ -38649,7 +38649,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.40563797950745</v>
+        <v>3.40563821792603</v>
       </c>
       <c r="H1320" t="n">
         <v>4882</v>
@@ -38678,7 +38678,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1321" t="n">
         <v>3244</v>
@@ -38707,7 +38707,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.3866651058197</v>
+        <v>3.38666534423828</v>
       </c>
       <c r="H1322" t="n">
         <v>1092</v>
@@ -38736,7 +38736,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.42461085319519</v>
+        <v>3.42461109161377</v>
       </c>
       <c r="H1323" t="n">
         <v>7333</v>
@@ -38765,7 +38765,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.42461085319519</v>
+        <v>3.42461109161377</v>
       </c>
       <c r="H1324" t="n">
         <v>0</v>
@@ -38823,7 +38823,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.42461085319519</v>
+        <v>3.42461109161377</v>
       </c>
       <c r="H1326" t="n">
         <v>13297</v>
@@ -38881,7 +38881,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.69971823692322</v>
+        <v>3.6997184753418</v>
       </c>
       <c r="H1328" t="n">
         <v>148742</v>
@@ -38910,7 +38910,7 @@
         <v>4</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.79458260536194</v>
+        <v>3.79458284378052</v>
       </c>
       <c r="H1329" t="n">
         <v>228117</v>
@@ -38939,7 +38939,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.78509664535522</v>
+        <v>3.78509640693665</v>
       </c>
       <c r="H1330" t="n">
         <v>43721</v>
@@ -38968,7 +38968,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.69971823692322</v>
+        <v>3.6997184753418</v>
       </c>
       <c r="H1331" t="n">
         <v>27325</v>
@@ -39026,7 +39026,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.69971823692322</v>
+        <v>3.6997184753418</v>
       </c>
       <c r="H1333" t="n">
         <v>30168</v>
@@ -39171,7 +39171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1338" t="n">
         <v>3276</v>
@@ -39287,7 +39287,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1342" t="n">
         <v>4223</v>
@@ -39316,7 +39316,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.68074560165405</v>
+        <v>3.68074584007263</v>
       </c>
       <c r="H1343" t="n">
         <v>2986</v>
@@ -39345,7 +39345,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1344" t="n">
         <v>4146</v>
@@ -39374,7 +39374,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1345" t="n">
         <v>11667</v>
@@ -39432,7 +39432,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1347" t="n">
         <v>4380</v>
@@ -39490,7 +39490,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1349" t="n">
         <v>9385</v>
@@ -39519,7 +39519,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1350" t="n">
         <v>9534</v>
@@ -39664,7 +39664,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1355" t="n">
         <v>4918</v>
@@ -39722,7 +39722,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1357" t="n">
         <v>3436</v>
@@ -39780,7 +39780,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1359" t="n">
         <v>2648</v>
@@ -39809,7 +39809,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.56690812110901</v>
+        <v>3.56690764427185</v>
       </c>
       <c r="H1360" t="n">
         <v>11798</v>
@@ -39838,7 +39838,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1361" t="n">
         <v>9755</v>
@@ -39867,7 +39867,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1362" t="n">
         <v>29179</v>
@@ -39896,7 +39896,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.68074560165405</v>
+        <v>3.68074584007263</v>
       </c>
       <c r="H1363" t="n">
         <v>15379</v>
@@ -39925,7 +39925,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.68074560165405</v>
+        <v>3.68074584007263</v>
       </c>
       <c r="H1364" t="n">
         <v>14343</v>
@@ -39954,7 +39954,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1365" t="n">
         <v>18108</v>
@@ -40012,7 +40012,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1367" t="n">
         <v>11540</v>
@@ -40041,7 +40041,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1368" t="n">
         <v>15221</v>
@@ -40070,7 +40070,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.74715042114258</v>
+        <v>3.74715065956116</v>
       </c>
       <c r="H1369" t="n">
         <v>229363</v>
@@ -40099,7 +40099,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.74715042114258</v>
+        <v>3.74715065956116</v>
       </c>
       <c r="H1370" t="n">
         <v>72359</v>
@@ -40128,7 +40128,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.68074560165405</v>
+        <v>3.68074584007263</v>
       </c>
       <c r="H1371" t="n">
         <v>55589</v>
@@ -40157,7 +40157,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1372" t="n">
         <v>11860</v>
@@ -40186,7 +40186,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1373" t="n">
         <v>51194</v>
@@ -40273,7 +40273,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1376" t="n">
         <v>14833</v>
@@ -40302,7 +40302,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1377" t="n">
         <v>14571</v>
@@ -40360,7 +40360,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1379" t="n">
         <v>331</v>
@@ -40389,7 +40389,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1380" t="n">
         <v>3220</v>
@@ -40418,7 +40418,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1381" t="n">
         <v>22839</v>
@@ -40447,7 +40447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.68074560165405</v>
+        <v>3.68074584007263</v>
       </c>
       <c r="H1382" t="n">
         <v>4422</v>
@@ -40476,7 +40476,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1383" t="n">
         <v>3965</v>
@@ -40505,7 +40505,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1384" t="n">
         <v>15858</v>
@@ -40534,7 +40534,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1385" t="n">
         <v>1270</v>
@@ -40563,7 +40563,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1386" t="n">
         <v>14648</v>
@@ -40650,7 +40650,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1389" t="n">
         <v>8881</v>
@@ -40679,7 +40679,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1390" t="n">
         <v>5051</v>
@@ -40708,7 +40708,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1391" t="n">
         <v>2025</v>
@@ -40882,7 +40882,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1397" t="n">
         <v>32862</v>
@@ -40969,7 +40969,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1400" t="n">
         <v>25238</v>
@@ -41027,7 +41027,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1402" t="n">
         <v>5050</v>
@@ -41143,7 +41143,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1406" t="n">
         <v>555</v>
@@ -41172,7 +41172,7 @@
         <v>3.75</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.55742144584656</v>
+        <v>3.55742120742798</v>
       </c>
       <c r="H1407" t="n">
         <v>3149</v>
@@ -41201,7 +41201,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1408" t="n">
         <v>1334</v>
@@ -41288,7 +41288,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1411" t="n">
         <v>7026</v>
@@ -41375,7 +41375,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1414" t="n">
         <v>1585</v>
@@ -41491,7 +41491,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1418" t="n">
         <v>21864</v>
@@ -41578,7 +41578,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1421" t="n">
         <v>13561</v>
@@ -41607,7 +41607,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1422" t="n">
         <v>4756</v>
@@ -41636,7 +41636,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1423" t="n">
         <v>4350</v>
@@ -41694,7 +41694,7 @@
         <v>3.75</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.55742144584656</v>
+        <v>3.55742120742798</v>
       </c>
       <c r="H1425" t="n">
         <v>9214</v>
@@ -41839,7 +41839,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.67125868797302</v>
+        <v>3.6712589263916</v>
       </c>
       <c r="H1430" t="n">
         <v>9372</v>
@@ -41868,7 +41868,7 @@
         <v>3.75</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.55742144584656</v>
+        <v>3.55742120742798</v>
       </c>
       <c r="H1431" t="n">
         <v>14726</v>
@@ -41897,7 +41897,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1432" t="n">
         <v>1886</v>
@@ -41926,7 +41926,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1433" t="n">
         <v>5181</v>
@@ -41955,7 +41955,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1434" t="n">
         <v>0</v>
@@ -41984,7 +41984,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1435" t="n">
         <v>1851</v>
@@ -42013,7 +42013,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1436" t="n">
         <v>59</v>
@@ -42042,7 +42042,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1437" t="n">
         <v>9602</v>
@@ -42274,7 +42274,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.56690812110901</v>
+        <v>3.56690764427185</v>
       </c>
       <c r="H1445" t="n">
         <v>4228</v>
@@ -42332,7 +42332,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.56690812110901</v>
+        <v>3.56690764427185</v>
       </c>
       <c r="H1447" t="n">
         <v>2668</v>
@@ -42361,7 +42361,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.6048538684845</v>
+        <v>3.60485363006592</v>
       </c>
       <c r="H1448" t="n">
         <v>1576</v>
@@ -42390,7 +42390,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.57639408111572</v>
+        <v>3.5763943195343</v>
       </c>
       <c r="H1449" t="n">
         <v>12494</v>
@@ -42419,7 +42419,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.54793500900269</v>
+        <v>3.54793477058411</v>
       </c>
       <c r="H1450" t="n">
         <v>1226</v>
@@ -42448,7 +42448,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.52896213531494</v>
+        <v>3.52896189689636</v>
       </c>
       <c r="H1451" t="n">
         <v>4674</v>
@@ -42477,7 +42477,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.61434030532837</v>
+        <v>3.61434006690979</v>
       </c>
       <c r="H1452" t="n">
         <v>6393</v>
@@ -42564,7 +42564,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.65228605270386</v>
+        <v>3.65228581428528</v>
       </c>
       <c r="H1455" t="n">
         <v>40095</v>
@@ -42680,7 +42680,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1459" t="n">
         <v>68342</v>
@@ -42709,7 +42709,7 @@
         <v>3.75</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1460" t="n">
         <v>30425</v>
@@ -42738,7 +42738,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1461" t="n">
         <v>10285</v>
@@ -42796,7 +42796,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1463" t="n">
         <v>6816</v>
@@ -42825,7 +42825,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1464" t="n">
         <v>7463</v>
@@ -42912,7 +42912,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.65299606323242</v>
+        <v>3.652996301651</v>
       </c>
       <c r="H1467" t="n">
         <v>7810</v>
@@ -42941,7 +42941,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1468" t="n">
         <v>535</v>
@@ -42970,7 +42970,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1469" t="n">
         <v>0</v>
@@ -42999,7 +42999,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1470" t="n">
         <v>20214</v>
@@ -43115,7 +43115,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.60505676269531</v>
+        <v>3.60505652427673</v>
       </c>
       <c r="H1474" t="n">
         <v>7283</v>
@@ -43144,7 +43144,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1475" t="n">
         <v>900</v>
@@ -43173,7 +43173,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1476" t="n">
         <v>2526</v>
@@ -43231,7 +43231,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1478" t="n">
         <v>4516</v>
@@ -43347,7 +43347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1482" t="n">
         <v>9208</v>
@@ -43376,7 +43376,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.53794145584106</v>
+        <v>3.53794121742249</v>
       </c>
       <c r="H1483" t="n">
         <v>13033</v>
@@ -43405,7 +43405,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1484" t="n">
         <v>7246</v>
@@ -43434,7 +43434,7 @@
         <v>3.75</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1485" t="n">
         <v>915</v>
@@ -43550,7 +43550,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.65299606323242</v>
+        <v>3.652996301651</v>
       </c>
       <c r="H1489" t="n">
         <v>28588</v>
@@ -43666,7 +43666,7 @@
         <v>3.75</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1493" t="n">
         <v>2701</v>
@@ -43724,7 +43724,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.58588099479675</v>
+        <v>3.58588075637817</v>
       </c>
       <c r="H1495" t="n">
         <v>3611</v>
@@ -43840,7 +43840,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.60505676269531</v>
+        <v>3.60505652427673</v>
       </c>
       <c r="H1499" t="n">
         <v>4079</v>
@@ -43869,7 +43869,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.60505676269531</v>
+        <v>3.60505652427673</v>
       </c>
       <c r="H1500" t="n">
         <v>4614</v>
@@ -43927,7 +43927,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1502" t="n">
         <v>34693</v>
@@ -43956,7 +43956,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.65299606323242</v>
+        <v>3.652996301651</v>
       </c>
       <c r="H1503" t="n">
         <v>28920</v>
@@ -43985,7 +43985,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.65299606323242</v>
+        <v>3.652996301651</v>
       </c>
       <c r="H1504" t="n">
         <v>22196</v>
@@ -44014,7 +44014,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.65299606323242</v>
+        <v>3.652996301651</v>
       </c>
       <c r="H1505" t="n">
         <v>249890</v>
@@ -44188,7 +44188,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1511" t="n">
         <v>22887</v>
@@ -44333,7 +44333,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.44206190109253</v>
+        <v>3.44206213951111</v>
       </c>
       <c r="H1516" t="n">
         <v>82297</v>
@@ -44391,7 +44391,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.37494683265686</v>
+        <v>3.37494659423828</v>
       </c>
       <c r="H1518" t="n">
         <v>893150</v>
@@ -44623,7 +44623,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.38453483581543</v>
+        <v>3.38453459739685</v>
       </c>
       <c r="H1526" t="n">
         <v>9125</v>
@@ -44768,7 +44768,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.36535859107971</v>
+        <v>3.36535882949829</v>
       </c>
       <c r="H1531" t="n">
         <v>235487</v>
@@ -44797,7 +44797,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.33659482002258</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1532" t="n">
         <v>5544</v>
@@ -44884,7 +44884,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.33659482002258</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1535" t="n">
         <v>43641</v>
@@ -45000,7 +45000,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.37494683265686</v>
+        <v>3.37494659423828</v>
       </c>
       <c r="H1539" t="n">
         <v>354177</v>
@@ -45029,7 +45029,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.37494683265686</v>
+        <v>3.37494659423828</v>
       </c>
       <c r="H1540" t="n">
         <v>675629</v>
@@ -45116,7 +45116,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.44206190109253</v>
+        <v>3.44206213951111</v>
       </c>
       <c r="H1543" t="n">
         <v>35330</v>
@@ -45145,7 +45145,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.38453483581543</v>
+        <v>3.38453459739685</v>
       </c>
       <c r="H1544" t="n">
         <v>168277</v>
@@ -45232,7 +45232,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.33659482002258</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1547" t="n">
         <v>49104</v>
@@ -45319,7 +45319,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.28865551948547</v>
+        <v>3.28865575790405</v>
       </c>
       <c r="H1550" t="n">
         <v>175383</v>
@@ -45580,7 +45580,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.33659482002258</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1559" t="n">
         <v>123618</v>
@@ -45609,7 +45609,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.33659482002258</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1560" t="n">
         <v>28599</v>
@@ -45638,7 +45638,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.33659482002258</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1561" t="n">
         <v>3921</v>
@@ -45812,7 +45812,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.28865551948547</v>
+        <v>3.28865575790405</v>
       </c>
       <c r="H1567" t="n">
         <v>52435</v>
@@ -46044,7 +46044,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.33659482002258</v>
+        <v>3.33659529685974</v>
       </c>
       <c r="H1575" t="n">
         <v>39131</v>
@@ -46131,7 +46131,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1578" t="n">
-        <v>3.36535859107971</v>
+        <v>3.36535882949829</v>
       </c>
       <c r="H1578" t="n">
         <v>154194</v>
@@ -46334,7 +46334,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1585" t="n">
         <v>607033</v>
@@ -46450,7 +46450,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1589" t="n">
         <v>140695</v>
@@ -46479,7 +46479,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.6913480758667</v>
+        <v>3.69134783744812</v>
       </c>
       <c r="H1590" t="n">
         <v>112960</v>
@@ -46508,7 +46508,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.71052360534668</v>
+        <v>3.71052384376526</v>
       </c>
       <c r="H1591" t="n">
         <v>308703</v>
@@ -46537,7 +46537,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.76805114746094</v>
+        <v>3.76805138587952</v>
       </c>
       <c r="H1592" t="n">
         <v>520527</v>
@@ -46827,7 +46827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.79681491851807</v>
+        <v>3.79681515693665</v>
       </c>
       <c r="H1602" t="n">
         <v>87427</v>
@@ -46856,7 +46856,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.79681491851807</v>
+        <v>3.79681515693665</v>
       </c>
       <c r="H1603" t="n">
         <v>9376</v>
@@ -46972,7 +46972,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.80640316009521</v>
+        <v>3.80640292167664</v>
       </c>
       <c r="H1607" t="n">
         <v>422791</v>
@@ -47001,7 +47001,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.79681491851807</v>
+        <v>3.79681515693665</v>
       </c>
       <c r="H1608" t="n">
         <v>76479</v>
@@ -47175,7 +47175,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.76805114746094</v>
+        <v>3.76805138587952</v>
       </c>
       <c r="H1614" t="n">
         <v>109924</v>
@@ -47291,7 +47291,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1618" t="n">
         <v>47307</v>
@@ -47320,7 +47320,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1619" t="n">
         <v>47852</v>
@@ -47349,7 +47349,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.6913480758667</v>
+        <v>3.69134783744812</v>
       </c>
       <c r="H1620" t="n">
         <v>66472</v>
@@ -47407,7 +47407,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.71052360534668</v>
+        <v>3.71052384376526</v>
       </c>
       <c r="H1622" t="n">
         <v>38232</v>
@@ -47465,7 +47465,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1624" t="n">
         <v>59345</v>
@@ -47552,7 +47552,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.72011184692383</v>
+        <v>3.72011208534241</v>
       </c>
       <c r="H1627" t="n">
         <v>53294</v>
@@ -47581,7 +47581,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1628" t="n">
         <v>42179</v>
@@ -47610,7 +47610,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1629" t="n">
         <v>17568</v>
@@ -47668,7 +47668,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.72011184692383</v>
+        <v>3.72011208534241</v>
       </c>
       <c r="H1631" t="n">
         <v>23792</v>
@@ -47755,7 +47755,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.71052360534668</v>
+        <v>3.71052384376526</v>
       </c>
       <c r="H1634" t="n">
         <v>20041</v>
@@ -47784,7 +47784,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.7296998500824</v>
+        <v>3.72969961166382</v>
       </c>
       <c r="H1635" t="n">
         <v>19421</v>
@@ -47958,7 +47958,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.76805114746094</v>
+        <v>3.76805138587952</v>
       </c>
       <c r="H1641" t="n">
         <v>107946</v>
@@ -47987,7 +47987,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.76805114746094</v>
+        <v>3.76805138587952</v>
       </c>
       <c r="H1642" t="n">
         <v>33426</v>
@@ -48103,7 +48103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.68176007270813</v>
+        <v>3.68175983428955</v>
       </c>
       <c r="H1646" t="n">
         <v>14045</v>
@@ -48248,7 +48248,7 @@
         <v>3.75</v>
       </c>
       <c r="G1651" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1651" t="n">
         <v>20515</v>
@@ -48335,7 +48335,7 @@
         <v>3.75</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1654" t="n">
         <v>12044</v>
@@ -48422,7 +48422,7 @@
         <v>3.75</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1657" t="n">
         <v>24610</v>
@@ -48538,7 +48538,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.53794145584106</v>
+        <v>3.53794121742249</v>
       </c>
       <c r="H1661" t="n">
         <v>6378</v>
@@ -48654,7 +48654,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.53794145584106</v>
+        <v>3.53794121742249</v>
       </c>
       <c r="H1665" t="n">
         <v>26897</v>
@@ -48799,7 +48799,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1670" t="n">
         <v>7951</v>
@@ -48857,7 +48857,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1672" t="n">
         <v>28080</v>
@@ -48973,7 +48973,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1676" t="n">
         <v>28220</v>
@@ -49031,7 +49031,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1678" t="n">
         <v>321</v>
@@ -49060,7 +49060,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1679" t="n">
         <v>16039</v>
@@ -49089,7 +49089,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1680" t="n">
         <v>8626</v>
@@ -49176,7 +49176,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1683" t="n">
         <v>587</v>
@@ -49321,7 +49321,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1688" t="n">
         <v>5749</v>
@@ -49379,7 +49379,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.43247413635254</v>
+        <v>3.43247437477112</v>
       </c>
       <c r="H1690" t="n">
         <v>24266</v>
@@ -49466,7 +49466,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.46123766899109</v>
+        <v>3.46123790740967</v>
       </c>
       <c r="H1693" t="n">
         <v>3742</v>
@@ -49524,7 +49524,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.44206190109253</v>
+        <v>3.44206213951111</v>
       </c>
       <c r="H1695" t="n">
         <v>1855</v>
@@ -49756,7 +49756,7 @@
         <v>3.75</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1703" t="n">
         <v>73879</v>
@@ -49785,7 +49785,7 @@
         <v>3.75</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.59546899795532</v>
+        <v>3.59546852111816</v>
       </c>
       <c r="H1704" t="n">
         <v>42320</v>
@@ -49843,7 +49843,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1706" t="n">
         <v>4431</v>
@@ -49872,7 +49872,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.63382053375244</v>
+        <v>3.63382029533386</v>
       </c>
       <c r="H1707" t="n">
         <v>18328</v>
@@ -50017,7 +50017,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.65299606323242</v>
+        <v>3.652996301651</v>
       </c>
       <c r="H1712" t="n">
         <v>53435</v>
@@ -50133,7 +50133,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.6913480758667</v>
+        <v>3.69134783744812</v>
       </c>
       <c r="H1716" t="n">
         <v>84169</v>
@@ -50191,7 +50191,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.60505676269531</v>
+        <v>3.60505652427673</v>
       </c>
       <c r="H1718" t="n">
         <v>59021</v>
@@ -50307,7 +50307,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.53794145584106</v>
+        <v>3.53794121742249</v>
       </c>
       <c r="H1722" t="n">
         <v>28900</v>
@@ -50365,7 +50365,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.58063745498657</v>
+        <v>3.58063721656799</v>
       </c>
       <c r="H1724" t="n">
         <v>45595</v>
@@ -50568,7 +50568,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.48360085487366</v>
+        <v>3.48360109329224</v>
       </c>
       <c r="H1731" t="n">
         <v>17735</v>
@@ -50829,7 +50829,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.53211951255798</v>
+        <v>3.5321192741394</v>
       </c>
       <c r="H1740" t="n">
         <v>4529</v>
@@ -50916,7 +50916,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.58063745498657</v>
+        <v>3.58063721656799</v>
       </c>
       <c r="H1743" t="n">
         <v>59557</v>
@@ -50974,7 +50974,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.73589539527893</v>
+        <v>3.73589515686035</v>
       </c>
       <c r="H1745" t="n">
         <v>110088</v>
@@ -51003,7 +51003,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.79411721229553</v>
+        <v>3.79411697387695</v>
       </c>
       <c r="H1746" t="n">
         <v>159571</v>
@@ -51119,7 +51119,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.1434473991394</v>
+        <v>4.14344787597656</v>
       </c>
       <c r="H1750" t="n">
         <v>188636</v>
@@ -51264,7 +51264,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1755" t="n">
-        <v>4.0561146736145</v>
+        <v>4.05611515045166</v>
       </c>
       <c r="H1755" t="n">
         <v>62913</v>
@@ -51351,7 +51351,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.97848606109619</v>
+        <v>3.97848582267761</v>
       </c>
       <c r="H1758" t="n">
         <v>87124</v>
@@ -51380,7 +51380,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.94937539100647</v>
+        <v>3.94937491416931</v>
       </c>
       <c r="H1759" t="n">
         <v>71907</v>
@@ -51438,7 +51438,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1761" t="n">
-        <v>3.9299681186676</v>
+        <v>3.92996788024902</v>
       </c>
       <c r="H1761" t="n">
         <v>119358</v>
@@ -51612,7 +51612,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.04641151428223</v>
+        <v>4.04641103744507</v>
       </c>
       <c r="H1767" t="n">
         <v>16526</v>
@@ -51670,7 +51670,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.9299681186676</v>
+        <v>3.92996788024902</v>
       </c>
       <c r="H1769" t="n">
         <v>42082</v>
@@ -51786,7 +51786,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1773" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1773" t="n">
         <v>65598</v>
@@ -51844,7 +51844,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1775" t="n">
         <v>122730</v>
@@ -51902,7 +51902,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1777" t="n">
-        <v>4.13374376296997</v>
+        <v>4.13374423980713</v>
       </c>
       <c r="H1777" t="n">
         <v>68837</v>
@@ -51989,7 +51989,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.13374376296997</v>
+        <v>4.13374423980713</v>
       </c>
       <c r="H1780" t="n">
         <v>22574</v>
@@ -52018,7 +52018,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1781" t="n">
-        <v>4.1434473991394</v>
+        <v>4.14344787597656</v>
       </c>
       <c r="H1781" t="n">
         <v>9035</v>
@@ -52047,7 +52047,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1782" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1782" t="n">
         <v>17699</v>
@@ -52134,7 +52134,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.04641151428223</v>
+        <v>4.04641103744507</v>
       </c>
       <c r="H1785" t="n">
         <v>34349</v>
@@ -52192,7 +52192,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1787" t="n">
-        <v>4.0561146736145</v>
+        <v>4.05611515045166</v>
       </c>
       <c r="H1787" t="n">
         <v>78761</v>
@@ -52308,7 +52308,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.1434473991394</v>
+        <v>4.14344787597656</v>
       </c>
       <c r="H1791" t="n">
         <v>41248</v>
@@ -52482,7 +52482,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1797" t="n">
         <v>58569</v>
@@ -52598,7 +52598,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1801" t="n">
-        <v>4.27929830551147</v>
+        <v>4.27929782867432</v>
       </c>
       <c r="H1801" t="n">
         <v>77174</v>
@@ -52627,7 +52627,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1802" t="n">
         <v>170350</v>
@@ -52714,7 +52714,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1805" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1805" t="n">
         <v>24854</v>
@@ -52772,7 +52772,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.20166873931885</v>
+        <v>4.20166921615601</v>
       </c>
       <c r="H1807" t="n">
         <v>23361</v>
@@ -52859,7 +52859,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1810" t="n">
         <v>20880</v>
@@ -52888,7 +52888,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1811" t="n">
         <v>21726</v>
@@ -52975,7 +52975,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.0561146736145</v>
+        <v>4.05611515045166</v>
       </c>
       <c r="H1814" t="n">
         <v>10726</v>
@@ -53091,7 +53091,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>4.04641151428223</v>
+        <v>4.04641103744507</v>
       </c>
       <c r="H1818" t="n">
         <v>20596</v>
@@ -53178,7 +53178,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1821" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1821" t="n">
         <v>6788</v>
@@ -53207,7 +53207,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1822" t="n">
         <v>9092</v>
@@ -53294,7 +53294,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.04641151428223</v>
+        <v>4.04641103744507</v>
       </c>
       <c r="H1825" t="n">
         <v>29508</v>
@@ -53381,7 +53381,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.04641151428223</v>
+        <v>4.04641103744507</v>
       </c>
       <c r="H1828" t="n">
         <v>4762</v>
@@ -53439,7 +53439,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1830" t="n">
         <v>10001</v>
@@ -53468,7 +53468,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1831" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1831" t="n">
         <v>628</v>
@@ -53497,7 +53497,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1832" t="n">
         <v>4713</v>
@@ -53526,7 +53526,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1833" t="n">
         <v>881</v>
@@ -53555,7 +53555,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.13374376296997</v>
+        <v>4.13374423980713</v>
       </c>
       <c r="H1834" t="n">
         <v>18404</v>
@@ -53613,7 +53613,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1836" t="n">
         <v>57744</v>
@@ -53932,7 +53932,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.04641151428223</v>
+        <v>4.04641103744507</v>
       </c>
       <c r="H1847" t="n">
         <v>23899</v>
@@ -54019,7 +54019,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1850" t="n">
         <v>9000</v>
@@ -54077,7 +54077,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.11433601379395</v>
+        <v>4.1143364906311</v>
       </c>
       <c r="H1852" t="n">
         <v>30199</v>
@@ -54106,7 +54106,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.97848606109619</v>
+        <v>3.97848582267761</v>
       </c>
       <c r="H1853" t="n">
         <v>18316</v>
@@ -54164,7 +54164,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.97848606109619</v>
+        <v>3.97848582267761</v>
       </c>
       <c r="H1855" t="n">
         <v>53146</v>
@@ -54222,7 +54222,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.97848606109619</v>
+        <v>3.97848582267761</v>
       </c>
       <c r="H1857" t="n">
         <v>15526</v>
@@ -54309,7 +54309,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.92026424407959</v>
+        <v>3.92026448249817</v>
       </c>
       <c r="H1860" t="n">
         <v>62250</v>
@@ -54425,7 +54425,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.97848606109619</v>
+        <v>3.97848582267761</v>
       </c>
       <c r="H1864" t="n">
         <v>30339</v>
@@ -54483,7 +54483,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.92026424407959</v>
+        <v>3.92026448249817</v>
       </c>
       <c r="H1866" t="n">
         <v>46741</v>
@@ -54541,7 +54541,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1868" t="n">
-        <v>4.13374376296997</v>
+        <v>4.13374423980713</v>
       </c>
       <c r="H1868" t="n">
         <v>41834</v>
@@ -54686,7 +54686,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.43455648422241</v>
+        <v>4.43455600738525</v>
       </c>
       <c r="H1873" t="n">
         <v>105924</v>
@@ -55527,7 +55527,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.27929830551147</v>
+        <v>4.27929782867432</v>
       </c>
       <c r="H1902" t="n">
         <v>6005</v>
@@ -55556,7 +55556,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1903" t="n">
         <v>8000</v>
@@ -55759,7 +55759,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.33751964569092</v>
+        <v>4.33752012252808</v>
       </c>
       <c r="H1910" t="n">
         <v>2266</v>
@@ -55962,7 +55962,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.32781648635864</v>
+        <v>4.32781600952148</v>
       </c>
       <c r="H1917" t="n">
         <v>2975</v>
@@ -55991,7 +55991,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1918" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1918" t="n">
         <v>40359</v>
@@ -56078,7 +56078,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.31811237335205</v>
+        <v>4.31811285018921</v>
       </c>
       <c r="H1921" t="n">
         <v>9032</v>
@@ -56136,7 +56136,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1923" t="n">
-        <v>4.31811237335205</v>
+        <v>4.31811285018921</v>
       </c>
       <c r="H1923" t="n">
         <v>19804</v>
@@ -56165,7 +56165,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1924" t="n">
-        <v>4.31811237335205</v>
+        <v>4.31811285018921</v>
       </c>
       <c r="H1924" t="n">
         <v>2874</v>
@@ -56252,7 +56252,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.28900241851807</v>
+        <v>4.28900194168091</v>
       </c>
       <c r="H1927" t="n">
         <v>2850</v>
@@ -56310,7 +56310,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1929" t="n">
         <v>6399</v>
@@ -56368,7 +56368,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1931" t="n">
         <v>1636</v>
@@ -56397,7 +56397,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1932" t="n">
         <v>15172</v>
@@ -56455,7 +56455,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1934" t="n">
         <v>3948</v>
@@ -56484,7 +56484,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1935" t="n">
         <v>5329</v>
@@ -56513,7 +56513,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1936" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1936" t="n">
         <v>18624</v>
@@ -56542,7 +56542,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1937" t="n">
         <v>20128</v>
@@ -56600,7 +56600,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1939" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1939" t="n">
         <v>1</v>
@@ -56687,7 +56687,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1942" t="n">
         <v>4452</v>
@@ -56745,7 +56745,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.20166873931885</v>
+        <v>4.20166921615601</v>
       </c>
       <c r="H1944" t="n">
         <v>793</v>
@@ -56774,7 +56774,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.20166873931885</v>
+        <v>4.20166921615601</v>
       </c>
       <c r="H1945" t="n">
         <v>174</v>
@@ -56803,7 +56803,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1946" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1946" t="n">
         <v>4613</v>
@@ -56832,7 +56832,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1947" t="n">
         <v>1331</v>
@@ -56890,7 +56890,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1949" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1949" t="n">
         <v>14232</v>
@@ -56919,7 +56919,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1950" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1950" t="n">
         <v>6681</v>
@@ -56948,7 +56948,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1951" t="n">
         <v>4775</v>
@@ -56977,7 +56977,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1952" t="n">
         <v>3626</v>
@@ -57006,7 +57006,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1953" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1953" t="n">
         <v>2090</v>
@@ -57035,7 +57035,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1954" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1954" t="n">
         <v>12316</v>
@@ -57064,7 +57064,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1955" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1955" t="n">
         <v>12585</v>
@@ -57093,7 +57093,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1956" t="n">
         <v>2000</v>
@@ -57122,7 +57122,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1957" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1957" t="n">
         <v>704</v>
@@ -57180,7 +57180,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1959" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1959" t="n">
         <v>5485</v>
@@ -57209,7 +57209,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1960" t="n">
         <v>1060</v>
@@ -57238,7 +57238,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1961" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1961" t="n">
         <v>1465</v>
@@ -57267,7 +57267,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1962" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1962" t="n">
         <v>3262</v>
@@ -57296,7 +57296,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1963" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1963" t="n">
         <v>3</v>
@@ -57325,7 +57325,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1964" t="n">
         <v>2755</v>
@@ -57383,7 +57383,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1966" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1966" t="n">
         <v>1311788</v>
@@ -57412,7 +57412,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1967" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1967" t="n">
         <v>5122</v>
@@ -57470,7 +57470,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1969" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1969" t="n">
         <v>2008</v>
@@ -57499,7 +57499,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1970" t="n">
         <v>59452</v>
@@ -57528,7 +57528,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.27929830551147</v>
+        <v>4.27929782867432</v>
       </c>
       <c r="H1971" t="n">
         <v>4655</v>
@@ -57557,7 +57557,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1972" t="n">
-        <v>4.25989103317261</v>
+        <v>4.25989055633545</v>
       </c>
       <c r="H1972" t="n">
         <v>5188</v>
@@ -57586,7 +57586,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1973" t="n">
         <v>18255</v>
@@ -57644,7 +57644,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1975" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1975" t="n">
         <v>13733</v>
@@ -57673,7 +57673,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1976" t="n">
-        <v>4.25018787384033</v>
+        <v>4.25018739700317</v>
       </c>
       <c r="H1976" t="n">
         <v>26671</v>
@@ -57731,7 +57731,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1978" t="n">
-        <v>4.20166873931885</v>
+        <v>4.20166921615601</v>
       </c>
       <c r="H1978" t="n">
         <v>47039</v>
@@ -57760,7 +57760,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1979" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1979" t="n">
         <v>10397</v>
@@ -57789,7 +57789,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1980" t="n">
         <v>308</v>
@@ -57905,7 +57905,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1984" t="n">
-        <v>4.20166873931885</v>
+        <v>4.20166921615601</v>
       </c>
       <c r="H1984" t="n">
         <v>1817</v>
@@ -57963,7 +57963,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1986" t="n">
         <v>7752</v>
@@ -57992,7 +57992,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1987" t="n">
-        <v>4.20166873931885</v>
+        <v>4.20166921615601</v>
       </c>
       <c r="H1987" t="n">
         <v>401</v>
@@ -58021,7 +58021,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1988" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1988" t="n">
         <v>11122</v>
@@ -58050,7 +58050,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1989" t="n">
-        <v>4.16285467147827</v>
+        <v>4.16285514831543</v>
       </c>
       <c r="H1989" t="n">
         <v>3156</v>
@@ -58137,7 +58137,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.22107648849487</v>
+        <v>4.22107601165771</v>
       </c>
       <c r="H1992" t="n">
         <v>2183</v>
@@ -58311,7 +58311,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.20166873931885</v>
+        <v>4.20166921615601</v>
       </c>
       <c r="H1998" t="n">
         <v>500</v>
@@ -58369,7 +58369,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2000" t="n">
         <v>4265</v>
@@ -58601,7 +58601,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2008" t="n">
         <v>174</v>
@@ -58862,7 +58862,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2017" t="n">
         <v>4195</v>
@@ -59036,7 +59036,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.20759534835815</v>
+        <v>4.20759582519531</v>
       </c>
       <c r="H2023" t="n">
         <v>21282</v>
@@ -59326,7 +59326,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.37550401687622</v>
+        <v>4.37550449371338</v>
       </c>
       <c r="H2033" t="n">
         <v>23629</v>
@@ -59587,7 +59587,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2042" t="n">
         <v>1222</v>
@@ -59906,7 +59906,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.26685762405396</v>
+        <v>4.2668571472168</v>
       </c>
       <c r="H2053" t="n">
         <v>4126</v>
@@ -60022,7 +60022,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.20759534835815</v>
+        <v>4.20759582519531</v>
       </c>
       <c r="H2057" t="n">
         <v>3444</v>
@@ -60080,7 +60080,7 @@
         <v>4.25</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.19771862030029</v>
+        <v>4.19771814346313</v>
       </c>
       <c r="H2059" t="n">
         <v>25814</v>
@@ -60109,7 +60109,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.15821075439453</v>
+        <v>4.15821027755737</v>
       </c>
       <c r="H2060" t="n">
         <v>16634</v>
@@ -60167,7 +60167,7 @@
         <v>4.25</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.19771862030029</v>
+        <v>4.19771814346313</v>
       </c>
       <c r="H2062" t="n">
         <v>13480</v>
@@ -60370,7 +60370,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.14833307266235</v>
+        <v>4.14833354949951</v>
       </c>
       <c r="H2069" t="n">
         <v>8188</v>
@@ -60399,7 +60399,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.14833307266235</v>
+        <v>4.14833354949951</v>
       </c>
       <c r="H2070" t="n">
         <v>9225</v>
@@ -60428,7 +60428,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.14833307266235</v>
+        <v>4.14833354949951</v>
       </c>
       <c r="H2071" t="n">
         <v>4558</v>
@@ -60486,7 +60486,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.20759534835815</v>
+        <v>4.20759582519531</v>
       </c>
       <c r="H2073" t="n">
         <v>6392</v>
@@ -60573,7 +60573,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.13845682144165</v>
+        <v>4.13845634460449</v>
       </c>
       <c r="H2076" t="n">
         <v>7110</v>
@@ -60602,7 +60602,7 @@
         <v>4.25</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.19771862030029</v>
+        <v>4.19771814346313</v>
       </c>
       <c r="H2077" t="n">
         <v>10347</v>
@@ -60776,7 +60776,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2083" t="n">
         <v>2190</v>
@@ -60805,7 +60805,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2084" t="n">
         <v>9066</v>
@@ -60892,7 +60892,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2087" t="n">
         <v>28339</v>
@@ -61211,7 +61211,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.20759534835815</v>
+        <v>4.20759582519531</v>
       </c>
       <c r="H2098" t="n">
         <v>6390</v>
@@ -61356,7 +61356,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2103" t="n">
-        <v>4.20759534835815</v>
+        <v>4.20759582519531</v>
       </c>
       <c r="H2103" t="n">
         <v>11551</v>
@@ -61530,7 +61530,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.14833307266235</v>
+        <v>4.14833354949951</v>
       </c>
       <c r="H2109" t="n">
         <v>12513</v>
@@ -61559,7 +61559,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2110" t="n">
-        <v>4.13845682144165</v>
+        <v>4.13845634460449</v>
       </c>
       <c r="H2110" t="n">
         <v>13271</v>
@@ -61588,7 +61588,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2111" t="n">
-        <v>4.10882568359375</v>
+        <v>4.10882520675659</v>
       </c>
       <c r="H2111" t="n">
         <v>26274</v>
@@ -61646,7 +61646,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2113" t="n">
-        <v>4.06931781768799</v>
+        <v>4.06931734085083</v>
       </c>
       <c r="H2113" t="n">
         <v>55768</v>
@@ -61675,7 +61675,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2114" t="n">
-        <v>4.05944061279297</v>
+        <v>4.05944108963013</v>
       </c>
       <c r="H2114" t="n">
         <v>111850</v>
@@ -61733,7 +61733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2116" t="n">
-        <v>3.98042511940002</v>
+        <v>3.98042488098145</v>
       </c>
       <c r="H2116" t="n">
         <v>1227491</v>
@@ -61762,7 +61762,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2117" t="n">
-        <v>3.98042511940002</v>
+        <v>3.98042488098145</v>
       </c>
       <c r="H2117" t="n">
         <v>1690224</v>
@@ -61791,7 +61791,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2118" t="n">
-        <v>4.14833307266235</v>
+        <v>4.14833354949951</v>
       </c>
       <c r="H2118" t="n">
         <v>109012</v>
@@ -61907,7 +61907,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2122" t="n">
-        <v>4.15821075439453</v>
+        <v>4.15821027755737</v>
       </c>
       <c r="H2122" t="n">
         <v>100732</v>
@@ -61994,7 +61994,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2125" t="n">
-        <v>4.10882568359375</v>
+        <v>4.10882520675659</v>
       </c>
       <c r="H2125" t="n">
         <v>53202</v>
@@ -62139,7 +62139,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2130" t="n">
-        <v>4.11870241165161</v>
+        <v>4.11870288848877</v>
       </c>
       <c r="H2130" t="n">
         <v>72699</v>
@@ -62168,7 +62168,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2131" t="n">
-        <v>4.11870241165161</v>
+        <v>4.11870288848877</v>
       </c>
       <c r="H2131" t="n">
         <v>74240</v>
@@ -62197,7 +62197,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2132" t="n">
-        <v>4.13845682144165</v>
+        <v>4.13845634460449</v>
       </c>
       <c r="H2132" t="n">
         <v>111714</v>
@@ -62255,7 +62255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2134" t="n">
-        <v>4.14833307266235</v>
+        <v>4.14833354949951</v>
       </c>
       <c r="H2134" t="n">
         <v>102202</v>
@@ -63096,7 +63096,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2163" t="n">
-        <v>4.37550401687622</v>
+        <v>4.37550449371338</v>
       </c>
       <c r="H2163" t="n">
         <v>21313</v>
@@ -63212,7 +63212,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2167" t="n">
-        <v>4.26685762405396</v>
+        <v>4.2668571472168</v>
       </c>
       <c r="H2167" t="n">
         <v>18475</v>
@@ -63241,7 +63241,7 @@
         <v>4.25</v>
       </c>
       <c r="G2168" t="n">
-        <v>4.19771862030029</v>
+        <v>4.19771814346313</v>
       </c>
       <c r="H2168" t="n">
         <v>14797</v>
@@ -63502,7 +63502,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2177" t="n">
-        <v>4.26685762405396</v>
+        <v>4.2668571472168</v>
       </c>
       <c r="H2177" t="n">
         <v>16690</v>
@@ -63531,7 +63531,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2178" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2178" t="n">
         <v>12106</v>
@@ -63618,7 +63618,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2181" t="n">
-        <v>4.15821075439453</v>
+        <v>4.15821027755737</v>
       </c>
       <c r="H2181" t="n">
         <v>233348</v>
@@ -63647,7 +63647,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2182" t="n">
-        <v>4.10882568359375</v>
+        <v>4.10882520675659</v>
       </c>
       <c r="H2182" t="n">
         <v>33218</v>
@@ -63705,7 +63705,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2184" t="n">
-        <v>4.15821075439453</v>
+        <v>4.15821027755737</v>
       </c>
       <c r="H2184" t="n">
         <v>128662</v>
@@ -63734,7 +63734,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2185" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2185" t="n">
         <v>221106</v>
@@ -63763,7 +63763,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2186" t="n">
-        <v>4.28661155700684</v>
+        <v>4.28661108016968</v>
       </c>
       <c r="H2186" t="n">
         <v>242903</v>
@@ -63850,7 +63850,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2189" t="n">
-        <v>4.20759534835815</v>
+        <v>4.20759582519531</v>
       </c>
       <c r="H2189" t="n">
         <v>422001</v>
@@ -64082,7 +64082,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2197" t="n">
-        <v>4.86935329437256</v>
+        <v>4.8693528175354</v>
       </c>
       <c r="H2197" t="n">
         <v>3891710</v>
@@ -64140,7 +64140,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2199" t="n">
-        <v>4.86935329437256</v>
+        <v>4.8693528175354</v>
       </c>
       <c r="H2199" t="n">
         <v>878680</v>
@@ -64169,7 +64169,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2200" t="n">
-        <v>4.87923002243042</v>
+        <v>4.87923049926758</v>
       </c>
       <c r="H2200" t="n">
         <v>408906</v>
@@ -64198,7 +64198,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2201" t="n">
-        <v>4.87923002243042</v>
+        <v>4.87923049926758</v>
       </c>
       <c r="H2201" t="n">
         <v>746825</v>
@@ -64227,7 +64227,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2202" t="n">
-        <v>4.86935329437256</v>
+        <v>4.8693528175354</v>
       </c>
       <c r="H2202" t="n">
         <v>86164</v>
@@ -64749,7 +64749,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2220" t="n">
-        <v>4.87923002243042</v>
+        <v>4.87923049926758</v>
       </c>
       <c r="H2220" t="n">
         <v>111846</v>
@@ -64778,7 +64778,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2221" t="n">
-        <v>4.86935329437256</v>
+        <v>4.8693528175354</v>
       </c>
       <c r="H2221" t="n">
         <v>394977</v>
@@ -65561,7 +65561,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2248" t="n">
-        <v>4.87923002243042</v>
+        <v>4.87923049926758</v>
       </c>
       <c r="H2248" t="n">
         <v>18121</v>
@@ -65619,7 +65619,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2250" t="n">
-        <v>4.86935329437256</v>
+        <v>4.8693528175354</v>
       </c>
       <c r="H2250" t="n">
         <v>61238</v>
@@ -65938,7 +65938,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2261" t="n">
-        <v>4.87923002243042</v>
+        <v>4.87923049926758</v>
       </c>
       <c r="H2261" t="n">
         <v>14372</v>
@@ -65996,7 +65996,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2263" t="n">
-        <v>4.87923002243042</v>
+        <v>4.87923049926758</v>
       </c>
       <c r="H2263" t="n">
         <v>73199</v>
@@ -66083,7 +66083,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2266" t="n">
-        <v>4.97800016403198</v>
+        <v>4.97800064086914</v>
       </c>
       <c r="H2266" t="n">
         <v>14627</v>
@@ -66112,7 +66112,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2267" t="n">
-        <v>4.97800016403198</v>
+        <v>4.97800064086914</v>
       </c>
       <c r="H2267" t="n">
         <v>123494</v>
@@ -66170,7 +66170,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2269" t="n">
-        <v>5.09652423858643</v>
+        <v>5.09652376174927</v>
       </c>
       <c r="H2269" t="n">
         <v>8310</v>
@@ -68003,6 +68003,35 @@
         <v>24138</v>
       </c>
       <c r="I2332" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2333" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2333" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D2333" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="E2333" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="F2333" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="G2333" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="H2333" t="n">
+        <v>17203</v>
+      </c>
+      <c r="I2333" t="s">
         <v>9</v>
       </c>
     </row>
